--- a/Dataset/Cleaned_Word_sense.xlsx
+++ b/Dataset/Cleaned_Word_sense.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J157"/>
+  <dimension ref="A1:K143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,6 +476,11 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Corrected - Verbs</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Cleaned Word Sense</t>
         </is>
       </c>
@@ -510,13 +515,12 @@
       <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
         <is>
           <t>said to self or someone when the meal includes mung beans</t>
         </is>
@@ -552,13 +556,12 @@
       <c r="G3" t="n">
         <v>1</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
         <is>
           <t>used to tell someone that he is a liar or you can tell another is lying</t>
         </is>
@@ -594,13 +597,12 @@
       <c r="G4" t="n">
         <v>1</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
         <is>
           <t>used to tell someone not to criticize or hate what one is doing</t>
         </is>
@@ -609,54 +611,57 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ayaw pagbuot kay lain-lain ta og lubot</t>
+          <t>atoms check</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ayaw pagbuot kay lain-lain ta og lubot, respetaray lang ta sa atong mga opinion.; Bisan unsa ka kapugos, ayaw pagbuot kay lain-lain ta og lubot.; Dili ta angay maghusga, kay lain-lain ta og lubot.; Ang matag usa lain-lain og gusto, mao nga ayaw pagbuot kay lain-lain ta og lubot.; Dili tanan magkauyon, kay lain-lain ta og lubot.</t>
+          <t>Human sa klase, atoms check para sigurado nga walay nakalimtan.; Kada biyahe namo, atoms check usa aron kompleto ang gamit.; Sa dihang nagprepare para sa event, permi mi mag atoms check.; Atoms check una sa exam para walay nakalimtan nga notes.; Sa wala pa moalis, atoms check aron masiguro nga kumpleto ang mga dokumento.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>don't tell me what to do</t>
+          <t>(slang, humorous) used to tell a person or a group of people to check their eyes for gound</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[(b'ayaw', 'VERB'), (b'pagbuot', 'NOUN'), (b'kay', 'CONJ'), (b'lain-lain', 'ADJ'), (b'ta', 'PRON'), (b'og', 'CONJ'), (b'lubot', 'VERB')]</t>
+          <t>[(b'atoms', 'NOUN'), (b'check', 'OTH')]</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>don't tell me what to do</t>
+          <t>check</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>used to tell a person or a group of people to check their eyes for gound</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ayaw pagbuot, lain-lain tag lubot</t>
+          <t>ayaw pagbuot kay lain-lain ta og lubot</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ayaw pagbuot, lain-lain tag lubot, tanan kita adunay lain-lain nga kinabuhi nga gipili.; Ayaw ipugos imong gusto, lain-lain tag lubot.; Lain-lain tag lubot, mao nga kinahanglan respetuhon ang desisyon sa uban.; Ang tanan dili magkasama sa opinyon kay lain-lain tag lubot.; Ang pagsinabtanay kinahanglan aron malikayan ang away kay lain-lain tag lubot.</t>
+          <t>Ayaw pagbuot kay lain-lain ta og lubot, respetaray lang ta sa atong mga opinion.; Bisan unsa ka kapugos, ayaw pagbuot kay lain-lain ta og lubot.; Dili ta angay maghusga, kay lain-lain ta og lubot.; Ang matag usa lain-lain og gusto, mao nga ayaw pagbuot kay lain-lain ta og lubot.; Dili tanan magkauyon, kay lain-lain ta og lubot.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -666,7 +671,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[(b'ayaw', 'VERB'), (b'pagbuot', 'NOUN'), (b',', 'SYM'), (b'lain-lain', 'ADJ'), (b'tag', 'NOUN'), (b'lubot', 'VERB')]</t>
+          <t>[(b'ayaw', 'VERB'), (b'pagbuot', 'NOUN'), (b'kay', 'CONJ'), (b'lain-lain', 'ADJ'), (b'ta', 'PRON'), (b'og', 'CONJ'), (b'lubot', 'VERB')]</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -678,13 +683,16 @@
       <c r="G6" t="n">
         <v>1</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>pagbuot</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>don't tell me what to do</t>
         </is>
@@ -693,12 +701,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ayaw pagbuot, tagsa-tagsa tag lubot</t>
+          <t>ayaw pagbuot, lain-lain tag lubot</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ayaw pagbuot, tagsa-tagsa tag lubot, respetaray lang ta sa atong mga opinion.; Bisan unsa ka kapugos, ayaw pagbuot, tagsa-tagsa tag lubot.; Dili ta angay maghusga, kay tagsa-tagsa tag lubot.; Ang matag usa lain-lain og gusto, mao nga ayaw pagbuot, tagsa-tagsa tag lubot.; Dili tanan magkauyon, kay tagsa-tagsa tag lubot.</t>
+          <t>Ayaw pagbuot, lain-lain tag lubot, tanan kita adunay lain-lain nga kinabuhi nga gipili.; Ayaw ipugos imong gusto, lain-lain tag lubot.; Lain-lain tag lubot, mao nga kinahanglan respetuhon ang desisyon sa uban.; Ang tanan dili magkasama sa opinyon kay lain-lain tag lubot.; Ang pagsinabtanay kinahanglan aron malikayan ang away kay lain-lain tag lubot.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -708,7 +716,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[(b'ayaw', 'VERB'), (b'pagbuot', 'NOUN'), (b',', 'SYM'), (b'tagsa-tagsa', 'NOUN'), (b'tag', 'NOUN'), (b'lubot', 'VERB')]</t>
+          <t>[(b'ayaw', 'VERB'), (b'pagbuot', 'NOUN'), (b',', 'SYM'), (b'lain-lain', 'ADJ'), (b'tag', 'NOUN'), (b'lubot', 'VERB')]</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -720,13 +728,16 @@
       <c r="G7" t="n">
         <v>1</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>pagbuot</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>don't tell me what to do</t>
         </is>
@@ -735,148 +746,157 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ipanabi na sa clouds</t>
+          <t>ayaw pagbuot, tagsa-tagsa tag lubot</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ang imong mga pangandoy, ipanabi na sa clouds aron matinuod.; Kung gusto ka maabot ang imong damgo, ipanabi na sa clouds.; Ang imong mga plano, ipanabi na sa clouds kay maabot ra na.; Bisan unsa ka lisod, ipanabi na sa clouds ang imong mga pag-ampo.; Ipanabi na sa clouds ang imong mga tinguha ug siguroha nga mo-trabaho ka para ana.; Ayaw na lang pagsabot ana, ipanabi na sa clouds.; Si Juan pirmi lang magpangatarungan nga ipanabi na sa clouds.; Ang iyang mga istorya pirmi ipanabi na sa clouds kay dili tinuod.; Si Maria dili mutuo kay ang iyang nadungog ipanabi na sa clouds ra.; Ang mga tawo nga magbuot-buot pirmi lang ipanabi na sa clouds ang ilang mga rason.</t>
+          <t>Ayaw pagbuot, tagsa-tagsa tag lubot, respetaray lang ta sa atong mga opinion.; Bisan unsa ka kapugos, ayaw pagbuot, tagsa-tagsa tag lubot.; Dili ta angay maghusga, kay tagsa-tagsa tag lubot.; Ang matag usa lain-lain og gusto, mao nga ayaw pagbuot, tagsa-tagsa tag lubot.; Dili tanan magkauyon, kay tagsa-tagsa tag lubot.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>tell it to the marines</t>
+          <t>don't tell me what to do</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[(b'ipanabi', 'VERB'), (b'na', 'ADV'), (b'sa', 'PART'), (b'clouds', 'OTH')]</t>
+          <t>[(b'ayaw', 'VERB'), (b'pagbuot', 'NOUN'), (b',', 'SYM'), (b'tagsa-tagsa', 'NOUN'), (b'tag', 'NOUN'), (b'lubot', 'VERB')]</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>tell it to the marines</t>
+          <t>pagbuot</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>don't tell me what to do</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kalas og bugo</t>
+          <t>aykog labda</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ayaw pag-kalas og bugo, kay sayang lang ang imong panahon.; Kalas og bugo ning pagsulay nga wala’y klaro.; Ang pagsunod-sunod nimo niya, kalas og bugo ra.; Kalas og bugo ang magdiskusyon ug walay resulta.; Ang pagduwa ug mga walay pulos nga games, kalas og bugo ra.</t>
+          <t>Aykog labda, kay dili ko gusto magkasakit.; Kung naay problema, aykog labda ug labad sa ulo.; Aykog labda sa imong mga reklamo, kay busy ko.; Aykog labda sa mga butang nga dili importante.; Aykog labda, kay nagtuon ko para sa exam.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>a phrase used to tell someone that he or she is taking too long to comprehend what one is saying, used to express annoyance for failing or taking too long to get the message across</t>
+          <t>used to tell someone that he or she is annoying</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[(b'kalas', 'VERB'), (b'og', 'CONJ'), (b'bugo', 'ADJ')]</t>
+          <t>[(b'aykog', 'ADJ'), (b'labda', 'OTH')]</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>a phrase used to tell someone that he or she is taking too long to comprehend what one is saying</t>
+          <t>labda</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>used to tell someone that he or she is annoying</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kang kinsa man na imong sala</t>
+          <t>I don't care, imong mama dancer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kang kinsa man na imong sala nga gipangandaman kaayo?; Nganong kang kinsa man na imong sala nga grabe kaayo ka?; Naa ba ka sa problema? Kang kinsa man na imong sala?; Kang kinsa man na imong sala nga nagdako ka ug kalit?; Kang kinsa man na imong sala nga gipaninguha nimo?</t>
+          <t>Sige lang, I don't care, imong mama dancer man kaha.; Pagbinuang lang diha, I don't care, imong mama dancer bitaw.; Maski unsa imong isulti, I don't care, imong mama dancer.; Ingna lang ko og unsay imong gusto, I don't care, imong mama dancer man kaha.; Mo-comment lang ko, I don't care, imong mama dancer.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>used to tell someone that they only have themselves to blame for their own problems, situation, etc.</t>
+          <t>(childish) I don't care</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[(b'kang', 'DET'), (b'kinsa', 'PRON'), (b'man', 'PART'), (b'na', 'ADV'), (b'imong', 'PRON'), (b'sala', 'VERB')]</t>
+          <t>[(b'I', 'NOUN'), (b'do', 'NOUN'), (b"n't", 'OTH'), (b'care', 'OTH'), (b',', 'SYM'), (b'imong', 'PRON'), (b'mama', 'ADJ'), (b'dancer', 'OTH')]</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>used to tell someone that they only have themselves to blame for their own problems</t>
+          <t>care</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>I don't care</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kinsa man na imong sala</t>
+          <t>ipanabi na sa clouds</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kinsa man na imong sala nga nimo gipangutana?; Kinsa man na imong sala nga naghulat sa gawas?; Kinsa man na imong sala nga imong giatubang?; Kinsa man na imong sala nga permi ka kuyog?; Kinsa man na imong sala nga permi nimo giistoryahan?</t>
+          <t>Ang imong mga pangandoy, ipanabi na sa clouds aron matinuod.; Kung gusto ka maabot ang imong damgo, ipanabi na sa clouds.; Ang imong mga plano, ipanabi na sa clouds kay maabot ra na.; Bisan unsa ka lisod, ipanabi na sa clouds ang imong mga pag-ampo.; Ipanabi na sa clouds ang imong mga tinguha ug siguroha nga mo-trabaho ka para ana.; Ayaw na lang pagsabot ana, ipanabi na sa clouds.; Si Juan pirmi lang magpangatarungan nga ipanabi na sa clouds.; Ang iyang mga istorya pirmi ipanabi na sa clouds kay dili tinuod.; Si Maria dili mutuo kay ang iyang nadungog ipanabi na sa clouds ra.; Ang mga tawo nga magbuot-buot pirmi lang ipanabi na sa clouds ang ilang mga rason.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>used to tell someone that they only have themselves to blame for their own problems, situation, etc.</t>
+          <t>tell it to the marines</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[(b'kinsa', 'PRON'), (b'man', 'PART'), (b'na', 'ADV'), (b'imong', 'PRON'), (b'sala', 'VERB')]</t>
+          <t>[(b'ipanabi', 'VERB'), (b'na', 'ADV'), (b'sa', 'PART'), (b'clouds', 'OTH')]</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -888,69 +908,71 @@
       <c r="G11" t="n">
         <v>1</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>used to tell someone that they only have themselves to blame for their own problems</t>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>tell it to the marines</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kung wala kay lingaw sa kinabuhi, dakpa akong utot</t>
+          <t>kung na-s ka, just follow</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kung wala kay lingaw sa kinabuhi, dakpa akong utot kay mao ra na akong ikahatag nimo.; Kung wala kay lingaw sa kinabuhi, dakpa akong utot, tan-awon nato unsay imong mahimo.; Kung wala kay lingaw sa kinabuhi, dakpa akong utot, basi malingaw ka.; Kung wala kay lingaw sa kinabuhi, dakpa akong utot, kay walay lain maka-entertain nimo.; Kung wala kay lingaw sa kinabuhi, dakpa akong utot, aron malingaw ka sa kinabuhi.</t>
+          <t>Kung na-s ka, just follow sa mga instructions para dili masayop.; Kung na-s ka, just follow sa process aron madali ang trabaho.; Kung na-s ka, just follow sa mga steps nga gi-provide.; Kung na-s ka, just follow sa mga guidelines nga giingon sa trainer.; Kung na-s ka, just follow sa flow aron di ka malibog.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>used to dismiss an attention seeker</t>
+          <t>a phrase used to dismiss someone's criticisms of one's actions or attitude</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[(b'kung', 'CONJ'), (b'wala', 'ADV'), (b'kay', 'CONJ'), (b'lingaw', 'VERB'), (b'sa', 'PART'), (b'kinabuhi', 'ADJ'), (b',', 'SYM'), (b'dakpa', 'VERB'), (b'akong', 'PRON'), (b'utot', 'NOUN')]</t>
+          <t>[(b'kung', 'CONJ'), (b'na-s', 'VERB'), (b'ka', 'PRON'), (b',', 'SYM'), (b'just', 'OTH'), (b'follow', 'OTH')]</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>used to dismiss an attention seeker</t>
+          <t>follow</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>a phrase used to dismiss someone's criticisms of one's actions or attitude</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kung wala kay lingaw, dakpa akong utot</t>
+          <t>kung wala kay lingaw sa kinabuhi, dakpa akong utot</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kung wala kay lingaw, dakpa akong utot aron ma-testing nimo imong abilidad.; Kung wala kay lingaw, dakpa akong utot aron malingaw ka gamay.; Kung wala kay lingaw, dakpa akong utot aron dili ka magbagotbot.; Kung wala kay lingaw, dakpa akong utot kay wala na koy lain mahuna-hunaan.; Kung wala kay lingaw, dakpa akong utot kay aron dili ka mabored.</t>
+          <t>Kung wala kay lingaw sa kinabuhi, dakpa akong utot kay mao ra na akong ikahatag nimo.; Kung wala kay lingaw sa kinabuhi, dakpa akong utot, tan-awon nato unsay imong mahimo.; Kung wala kay lingaw sa kinabuhi, dakpa akong utot, basi malingaw ka.; Kung wala kay lingaw sa kinabuhi, dakpa akong utot, kay walay lain maka-entertain nimo.; Kung wala kay lingaw sa kinabuhi, dakpa akong utot, aron malingaw ka sa kinabuhi.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -960,7 +982,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[(b'kung', 'CONJ'), (b'wala', 'ADV'), (b'kay', 'CONJ'), (b'lingaw', 'VERB'), (b',', 'SYM'), (b'dakpa', 'VERB'), (b'akong', 'PRON'), (b'utot', 'NOUN')]</t>
+          <t>[(b'kung', 'CONJ'), (b'wala', 'ADV'), (b'kay', 'CONJ'), (b'lingaw', 'VERB'), (b'sa', 'PART'), (b'kinabuhi', 'ADJ'), (b',', 'SYM'), (b'dakpa', 'VERB'), (b'akong', 'PRON'), (b'utot', 'NOUN')]</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -972,13 +994,16 @@
       <c r="G13" t="n">
         <v>1</v>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>dakpa</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>used to dismiss an attention seeker</t>
         </is>
@@ -987,22 +1012,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>lisod pukawon ang gamata</t>
+          <t>kung wala kay lingaw, dakpa akong utot</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lisod pukawon ang gamata, labi na kung bugnaw ang panahon.; Sa dihang human og night shift, lisod pukawon ang gamata sa buntag.; Ang mga estudyante nga late na matulog, lisod pukawon ang gamata.; Bisan unsaon, lisod pukawon ang gamata kung kapoy ang lawas.; Lisod pukawon ang gamata sa mga bata kung aduna'y bag-ong gadget.</t>
+          <t>Kung wala kay lingaw, dakpa akong utot aron ma-testing nimo imong abilidad.; Kung wala kay lingaw, dakpa akong utot aron malingaw ka gamay.; Kung wala kay lingaw, dakpa akong utot aron dili ka magbagotbot.; Kung wala kay lingaw, dakpa akong utot kay wala na koy lain mahuna-hunaan.; Kung wala kay lingaw, dakpa akong utot kay aron dili ka mabored.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>used to tell the waker or someone who refuses to wake</t>
+          <t>used to dismiss an attention seeker</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[(b'lisod', 'ADJ'), (b'pukawon', 'VERB'), (b'ang', 'DET'), (b'gamata', 'VERB')]</t>
+          <t>[(b'kung', 'CONJ'), (b'wala', 'ADV'), (b'kay', 'CONJ'), (b'lingaw', 'VERB'), (b',', 'SYM'), (b'dakpa', 'VERB'), (b'akong', 'PRON'), (b'utot', 'NOUN')]</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1014,37 +1039,40 @@
       <c r="G14" t="n">
         <v>1</v>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>used to tell the waker or someone who refuses to wake</t>
+          <t>dakpa</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>used to dismiss an attention seeker</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mogawas ang pari nga walay ulo</t>
+          <t>lisod pukawon ang gamata</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ayaw og kahadlok kay mogawas ang pari nga walay ulo kung magpabilin ka dinha.; Sa dihang mag-istorya sila og mga horror stories, mogawas ang pari nga walay ulo ang giingon.; Mogawas ang pari nga walay ulo kuno kung aduna'y mamatay sa baryo.; Kung magtuyok-tuyok ka sa kadalanan, mogawas ang pari nga walay ulo.; Mogawas ang pari nga walay ulo kung ang balay walay suga.</t>
+          <t>Lisod pukawon ang gamata, labi na kung bugnaw ang panahon.; Sa dihang human og night shift, lisod pukawon ang gamata sa buntag.; Ang mga estudyante nga late na matulog, lisod pukawon ang gamata.; Bisan unsaon, lisod pukawon ang gamata kung kapoy ang lawas.; Lisod pukawon ang gamata sa mga bata kung aduna'y bag-ong gadget.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>used to scare children from injuries</t>
+          <t>used to tell the waker or someone who refuses to wake</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[(b'mogawas', 'VERB'), (b'ang', 'DET'), (b'pari', 'NOUN'), (b'nga', 'PART'), (b'walay', 'ADV'), (b'ulo', 'NOUN')]</t>
+          <t>[(b'lisod', 'ADJ'), (b'pukawon', 'VERB'), (b'ang', 'DET'), (b'gamata', 'VERB')]</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1056,79 +1084,85 @@
       <c r="G15" t="n">
         <v>1</v>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>used to scare children from injuries</t>
+          <t>pukawon</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>used to tell the waker or someone who refuses to wake</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>nadakpan na</t>
+          <t>long time no see but now, sinaw</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nadakpan na ang kawatan nga dugay na nilang gipangita.; Nadakpan na si Pedro nga nagsige ug pangawat sa tindahan.; Nadakpan na ang mga illegal nga nagbaligya sa merkado.; Nadakpan na ang mga bata nga nagsige ug cutting classes.; Nadakpan na si Juan nga nagcheat sa exam.</t>
+          <t>Long time no see but now, sinaw na kaayo siya ug nawong.; Dugay kaayo ko wala kakita niya, pero long time no see but now, sinaw na siya ug porma.; Long time no see but now, sinaw na kaayo iyang awto.; Kadugay na nga wala ta magkita, long time no see but now, sinaw na kaayo ka ug sanina.; Long time no see but now, sinaw na kaayo iyang buhok.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>(often humorous) said to someone with a new haircut</t>
+          <t>long time no see</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[(b'nadakpan', 'OTH'), (b'na', 'ADV')]</t>
+          <t>[(b'long', 'OTH'), (b'time', 'OTH'), (b'no', 'PART'), (b'see', 'OTH'), (b'but', 'VERB'), (b'now', 'OTH'), (b',', 'SYM'), (b'sinaw', 'VERB')]</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>said to someone with a new haircut</t>
+          <t>see</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>long time no see</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>nadakpan na ba ang nagtupi nimo</t>
+          <t>mogawas ang pari nga walay ulo</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nadakpan na ba ang nagtupi nimo nga wala man nindot imong buhok?; Nadakpan na ba ang nagtupi nimo kay bati man gihapon ug resulta?; Nagtan-aw ko sa imong buhok, nadakpan na ba ang nagtupi nimo?; Nadakpan na ba ang nagtupi nimo kay gubot man gihapon ang buhok nimo?; Nadakpan na ba ang nagtupi nimo kay murag wa man nasunod imong gusto?</t>
+          <t>Ayaw og kahadlok kay mogawas ang pari nga walay ulo kung magpabilin ka dinha.; Sa dihang mag-istorya sila og mga horror stories, mogawas ang pari nga walay ulo ang giingon.; Mogawas ang pari nga walay ulo kuno kung aduna'y mamatay sa baryo.; Kung magtuyok-tuyok ka sa kadalanan, mogawas ang pari nga walay ulo.; Mogawas ang pari nga walay ulo kung ang balay walay suga.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>(often humorous) said to someone with a new haircut</t>
+          <t>used to scare children from injuries</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[(b'nadakpan', 'OTH'), (b'na', 'ADV'), (b'ba', 'PART'), (b'ang', 'DET'), (b'nagtupi', 'VERB'), (b'nimo', 'PRON')]</t>
+          <t>[(b'mogawas', 'VERB'), (b'ang', 'DET'), (b'pari', 'NOUN'), (b'nga', 'PART'), (b'walay', 'ADV'), (b'ulo', 'NOUN')]</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1140,79 +1174,81 @@
       <c r="G17" t="n">
         <v>1</v>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>said to someone with a new haircut</t>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>used to scare children from injuries</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>nakalugsong</t>
+          <t>nadakpan na</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nakalugsong na sila gikan sa bukid ug nagdala ug daghang prutas.; Sa dihang nakalugsong na, gihatod dayon nila ang mga tanom sa merkado.; Nakalugsong na mi ug gidalit ang among mga ani sa lungsod.; Ang mga trabahante nakalugsong gikan sa taas ug giuli ang mga gamit.; Bisan ug bagyo, nakalugsong gihapon ang mga mag-uuma aron magbaligya.</t>
+          <t>Nadakpan na ang kawatan nga dugay na nilang gipangita.; Nadakpan na si Pedro nga nagsige ug pangawat sa tindahan.; Nadakpan na ang mga illegal nga nagbaligya sa merkado.; Nadakpan na ang mga bata nga nagsige ug cutting classes.; Nadakpan na si Juan nga nagcheat sa exam.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>to go down from (a hill or mountain), canned sardines, used as a reply when one mentions sardines</t>
+          <t>(often humorous) said to someone with a new haircut</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[(b'nakalugsong', 'VERB')]</t>
+          <t>[(b'nadakpan', 'OTH'), (b'na', 'ADV')]</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>to go down from</t>
+          <t>nadakpan</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>said to someone with a new haircut</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ninja ray mopatay ninjo</t>
+          <t>nadakpan na ba ang nagtupi nimo</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ayaw mo pag-away, ninja ray mopatay ninjo nga wala'y saba.; Kung magpadayon mo ug binuang, ninja ray mopatay ninjo.; Sa kalit nga pag-agi, ninja ray mopatay ninjo nga wala moy kalibutan.; Bantay mo kay ninja ray mopatay ninjo kung magpadayon mo ug binuang.; Sa dihang nahimong komprontasyon, ninja ray mopatay ninjo.</t>
+          <t>Nadakpan na ba ang nagtupi nimo nga wala man nindot imong buhok?; Nadakpan na ba ang nagtupi nimo kay bati man gihapon ug resulta?; Nagtan-aw ko sa imong buhok, nadakpan na ba ang nagtupi nimo?; Nadakpan na ba ang nagtupi nimo kay gubot man gihapon ang buhok nimo?; Nadakpan na ba ang nagtupi nimo kay murag wa man nasunod imong gusto?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>(humorous) a phrase poking fun at the Leyte and Boholano dialects of Cebuano</t>
+          <t>(often humorous) said to someone with a new haircut</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[(b'ninja', 'OTH'), (b'ray', 'ADV'), (b'mopatay', 'VERB'), (b'ninjo', 'OTH')]</t>
+          <t>[(b'nadakpan', 'OTH'), (b'na', 'ADV'), (b'ba', 'PART'), (b'ang', 'DET'), (b'nagtupi', 'VERB'), (b'nimo', 'PRON')]</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1224,205 +1260,212 @@
       <c r="G19" t="n">
         <v>1</v>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>a phrase poking fun at the Leyte and Boholano dialects of Cebuano</t>
+          <t>nadakpan, nagtupi</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>said to someone with a new haircut</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pagtan-aw, kitkit langaw; paglingi, kitkit bungi</t>
+          <t>nakalugsong</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pagtan-aw nako sa iyang nawong, kitkit langaw; paglingi, kitkit bungi.; Pagtan-aw, kitkit langaw; paglingi, kitkit bungi sa kadaghan sa problema.; Ang iyang kinabuhi kay pagtan-aw, kitkit langaw; paglingi, kitkit bungi nga walay kapadulngan.; Sa kadaghan sa imong giatubang, pagtan-aw, kitkit langaw; paglingi, kitkit bungi na lang.; Pagtrabaho nila nga walay klaro, pagtan-aw, kitkit langaw; paglingi, kitkit bungi na lang.</t>
+          <t>Nakalugsong na sila gikan sa bukid ug nagdala ug daghang prutas.; Sa dihang nakalugsong na, gihatod dayon nila ang mga tanom sa merkado.; Nakalugsong na mi ug gidalit ang among mga ani sa lungsod.; Ang mga trabahante nakalugsong gikan sa taas ug giuli ang mga gamit.; Bisan ug bagyo, nakalugsong gihapon ang mga mag-uuma aron magbaligya.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>used to tell someone that you tricked them to look at a particular direction</t>
+          <t>to go down from (a hill or mountain), canned sardines, used as a reply when one mentions sardines</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[(b'pagtan-aw', 'NOUN'), (b',', 'SYM'), (b'kitkit', 'VERB'), (b'langaw', 'NOUN'), (b';', 'SYM'), (b'paglingi', 'OTH'), (b',', 'SYM'), (b'kitkit', 'VERB'), (b'bungi', 'VERB')]</t>
+          <t>[(b'nakalugsong', 'VERB')]</t>
         </is>
       </c>
       <c r="E20" t="n">
         <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>used to tell someone that you tricked them to look at a particular direction</t>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>to go down from</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pangatulig luwag</t>
+          <t>ninja ray mopatay ninjo</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ayaw na pangatulig luwag sa imong desisyon, kinahanglan klaro ka.; Ang iyang giingon kay murag pangatulig luwag, dili ko kasabot.; Pangatulig luwag nga mga istorya ang giabot sa among opisina.; Kung magpadayon ka ug pangatulig luwag, wala’y motuo nimo.; Ang iyang plano kay murag pangatulig luwag, walay klaro nga direksyon.; "Pangatulig luwag kaayo imong mga istorya, walay klaro."; "Si Pedro, sige lang pangatulig luwag walay unod."; "Pangatulig luwag imong mga ideas, kinahanglan pa nimo ug focus."; "Ayaw pag pangatulig luwag, klaroha imong mga desisyon."; "Pangatulig luwag imong mga plano, walay klaro."</t>
+          <t>Ayaw mo pag-away, ninja ray mopatay ninjo nga wala'y saba.; Kung magpadayon mo ug binuang, ninja ray mopatay ninjo.; Sa kalit nga pag-agi, ninja ray mopatay ninjo nga wala moy kalibutan.; Bantay mo kay ninja ray mopatay ninjo kung magpadayon mo ug binuang.; Sa dihang nahimong komprontasyon, ninja ray mopatay ninjo.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>used to dismiss someone who misquoted or misheard what one said</t>
+          <t>(humorous) a phrase poking fun at the Leyte and Boholano dialects of Cebuano</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[(b'pangatulig', 'NOUN'), (b'luwag', 'NOUN')]</t>
+          <t>[(b'ninja', 'OTH'), (b'ray', 'ADV'), (b'mopatay', 'VERB'), (b'ninjo', 'OTH')]</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>used to dismiss someone who misquoted or misheard what one said</t>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>a phrase poking fun at the Leyte and Boholano dialects of Cebuano</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pasok, Luningning</t>
+          <t>pagtan-aw, kitkit langaw; paglingi, kitkit bungi</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pasok, Luningning, ug ipakita ang imong talento.; Pagdali, pasok, Luningning, kay magsugod na ang programa.; Pasok, Luningning, ug paminawa ang mga instructions.; Pasok, Luningning, kay daghan pa ta ug buhaton.; Pasok, Luningning, kay andam na ang tanan para nimo.</t>
+          <t>Pagtan-aw nako sa iyang nawong, kitkit langaw; paglingi, kitkit bungi.; Pagtan-aw, kitkit langaw; paglingi, kitkit bungi sa kadaghan sa problema.; Ang iyang kinabuhi kay pagtan-aw, kitkit langaw; paglingi, kitkit bungi nga walay kapadulngan.; Sa kadaghan sa imong giatubang, pagtan-aw, kitkit langaw; paglingi, kitkit bungi na lang.; Pagtrabaho nila nga walay klaro, pagtan-aw, kitkit langaw; paglingi, kitkit bungi na lang.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>(slang) said to self when pocketing one's winnings in a game of cards, mahjong, etc.</t>
+          <t>used to tell someone that you tricked them to look at a particular direction</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>[(b'pasok', 'VERB'), (b',', 'SYM'), (b'Luningning', 'NOUN')]</t>
+          <t>[(b'pagtan-aw', 'NOUN'), (b',', 'SYM'), (b'kitkit', 'VERB'), (b'langaw', 'NOUN'), (b';', 'SYM'), (b'paglingi', 'OTH'), (b',', 'SYM'), (b'kitkit', 'VERB'), (b'bungi', 'VERB')]</t>
         </is>
       </c>
       <c r="E22" t="n">
         <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>said to self when pocketing one's winnings in a game of cards</t>
+          <t>pagtan-aw, kitkit, paglingi</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>used to tell someone that you tricked them to look at a particular direction</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>batil</t>
+          <t>pangatulig luwag</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ang batil sa mga karaan nga barko kay gipulihan na ug moderno nga makina.; Sa karaang panahon, ang batil kay gigamit sa mga tawo sa pagbiyahe sa dagat.; Ang mga mangangalakal sa una kay nagsakay sa batil aron makabaligya sa ilang mga produkto.; Ang batil nga gipanag-iya sa akong lolo kay isa ka klasik nga pamanhon.; Ang mga libro sa kasaysayan naghisgot bahin sa mga batil nga nagsuroy sa laing-laing lugar.</t>
+          <t>Ayaw na pangatulig luwag sa imong desisyon, kinahanglan klaro ka.; Ang iyang giingon kay murag pangatulig luwag, dili ko kasabot.; Pangatulig luwag nga mga istorya ang giabot sa among opisina.; Kung magpadayon ka ug pangatulig luwag, wala’y motuo nimo.; Ang iyang plano kay murag pangatulig luwag, walay klaro nga direksyon.; "Pangatulig luwag kaayo imong mga istorya, walay klaro."; "Si Pedro, sige lang pangatulig luwag walay unod."; "Pangatulig luwag imong mga ideas, kinahanglan pa nimo ug focus."; "Ayaw pag pangatulig luwag, klaroha imong mga desisyon."; "Pangatulig luwag imong mga plano, walay klaro."</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>A type of traditional sailing vessel used in the Arabian Sea.</t>
+          <t>used to dismiss someone who misquoted or misheard what one said</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>[(b'batil', 'VERB')]</t>
+          <t>[(b'pangatulig', 'NOUN'), (b'luwag', 'NOUN')]</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>A type of traditional sailing vessel used in the Arabian Sea</t>
+          <t>pangatulig</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>used to dismiss someone who misquoted or misheard what one said</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>binatilay</t>
+          <t>pasok, Luningning</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ang mga batan-on nga nagdula og binatilay sa eskwelahan kay gipahimangnoan sa mga maestro.; Ang binatilay nga mga tawo kay kasagaran mag-uban-uban sa ilang mga barkada.; Dili maayo nga magsige ug binatilay kay makadaot kini sa imong panglawas.; Ang binatilay nga binuhatan kay kinahanglan pugngan aron malikayan ang mga problema.; Ang mga binatilay nga istorya kay kasagaran giistoryahan sa mga batan-on.</t>
+          <t>Pasok, Luningning, ug ipakita ang imong talento.; Pagdali, pasok, Luningning, kay magsugod na ang programa.; Pasok, Luningning, ug paminawa ang mga instructions.; Pasok, Luningning, kay daghan pa ta ug buhaton.; Pasok, Luningning, kay andam na ang tanan para nimo.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>(euphemistic) to stimulate each other's penises mutually; to perform mutual masturbation</t>
+          <t>(slang) said to self when pocketing one's winnings in a game of cards, mahjong, etc.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>[(b'binatilay', 'VERB')]</t>
+          <t>[(b'pasok', 'VERB'), (b',', 'SYM'), (b'Luningning', 'NOUN')]</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1434,37 +1477,36 @@
       <c r="G24" t="n">
         <v>1</v>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>to stimulate each other's penises mutually</t>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>said to self when pocketing one's winnings in a game of cards</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>binuhi</t>
+          <t>paunaha ko para dili ka bungoton</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Si Pedro kay nagbuhi ug mga manok nga pangsabong.; Ang iyang mga binuhi kay mga kabaw nga gamiton sa umahan.; Ang mga binuhi nga iro sa ilang balay kay puro mga pure breed.; Ang pagbuhi ug isda sa aquarium kay isa ka relaxing nga hobby.; Ang mga binuhi nga baboy sa ilang farm kay maayo ug pag-atiman.</t>
+          <t>Paunaha ko para dili ka bungoton, ate, aron dili ka maglagot.; Sa dihang naningil siya, paunaha ko para dili ka bungoton, kuya.; Paunaha ko para dili ka bungoton, lola, kay hinaot ra ba ko mudagan.; Paunaha ko para dili ka bungoton, sir, kay nagdali man ko.; Paunaha ko para dili ka bungoton, miss, kay basin unya magkaproblema.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>(euphemistic) a man's penis, something or someone being raised or bred; a ward; a pet</t>
+          <t>said to allow older people to go before younger ones</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[(b'binuhi', 'ADJ')]</t>
+          <t>[(b'paunaha', 'ADV'), (b'ko', 'PRON'), (b'para', 'CONJ'), (b'dili', 'ADV'), (b'ka', 'PRON'), (b'bungoton', 'NOUN')]</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1474,83 +1516,84 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>a man's penis</t>
+          <t>paunaha</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>said to allow older people to go before younger ones</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>bunal</t>
+          <t>maghilawas</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Gidala niya ang bunal aron mapugngan ang mga kawatan.; Ang mga ginikanan sa una kay permi magdala ug bunal aron displinahon ang mga anak.; Sa panahon sa gubat, ang mga sundalo kay naggamit ug bunal isip armas.; Ang mga bunal sa mga dula sa elementarya kay kasagaran gihimo ug kahoy.; Ang mga estudyante nga gahi ug ulo kay giingnan nga mag-amping kay basin mabunalan.</t>
+          <t>Ang maghilawas nga mga tawo kasagaran wala'y klaro nga relasyon.; Dili maayo nga magsige ug maghilawas kay makadaot kini sa imong lawas ug isip.; Ang mga maghilawas nga binuhatan makaguba sa maayong reputasyon.; Ang mga tambag sa mga ginikanan kasagaran naglikay sa maghilawas nga binuhatan.; Ang maghilawas nga kinaiya sa uban makapalayo sa ilang mga higala ug pamilya.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>stick used in beating or whipping an animal or person, club; bat; baton; a billy club, (euphemistic, slang) penis, to hit or spank with a stick or other similar weapon or instrument; to club, right, true</t>
+          <t>(euphemistic) to have sex; to fuck
+Synonyms: mag-iyot, magkayat</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>[(b'bunal', 'VERB')]</t>
+          <t>[(b'maghilawas', 'OTH')]</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stick used in beating or whipping an animal or person</t>
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>to have sex</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>gibuhi</t>
+          <t>magtagay sa kalipay</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Gibuhi niya ang iyang mga tanom nga permi niyang ginatiman.; Ang iyang mga binuhi nga hayop kay giatiman gyud niya ug maayo.; Ang mga isda sa aquarium kay gibuhi niya pinaagi sa paghatag ug saktong pagkaon ug paglimpyo sa tubig.; Ang iyang mga tanom nga gibuhi kay nagbunga ug daghan.; Ang mga bata nga iyang gibuhi kay nagdako nga maayong laki.</t>
+          <t>Ang mga magtagay sa kalipay kasagaran makita sa mga parties ug celebrations.; Ang ilang magtagay sa kalipay nakaingon ug dakong kalipay sa tanan nga niapil.; Sa birthday ni Juan, nagmagtagay sa kalipay ang mga bisita hangtod sa kadlawn.; Ang mga magbarkada nagmagtagay sa kalipay human sa ilang reunion.; Ang mga mag-asawa nagmagtagay sa kalipay sa ilang anniversary celebration.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>(euphemistic) a man's penis, something or someone being raised or bred, a pet, to rear, to raise, breed
-Apan ang kabus nga tawo walay bisan unsa, gawas sa usa ka diyutay nga bayeng carnero nga nati, nga iyang pinalit ug gibuhi: ug kini mitubo ipon kaniya,but the poor man had nothing except one little ewe lamb he had bought. He raised it, and it grew up with him, raise someone from the dead
-Gibuhi og balik ni Jesus si LazaroJesus raises Lazarus from the dead.</t>
+          <t>(euphemistic) to have sexual intercourse</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>[(b'gibuhi', 'VERB')]</t>
+          <t>[(b'magtagay', 'VERB'), (b'sa', 'PART'), (b'kalipay', 'ADJ')]</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1562,241 +1605,156 @@
       <c r="G27" t="n">
         <v>1</v>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>a man's penis</t>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>to have sexual intercourse</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>hilawas</t>
+          <t>molayag sa kalipay</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ang hilawas nga relasyon sa diha nga walay commitment kay lisod.; Ang mga istorya nga hilawas kay kasagaran nagdani sa mga tawo.; Ang hilawas nga kinabuhi kay wala'y klaro nga padulngan.; Ang mga tawo nga maghilawas kay kasagaran mahadlok magcommit.; Ang hilawas nga binuhatan kay kasagaran nagdala ug problema sa kinabuhi.</t>
+          <t>Ang mga magkauban nagmolayag sa kalipay sa ilang outing sa beach.; Sa dihang nagmolayag sa kalipay ang grupo, nakalimot sila sa ilang mga problema.; Ang mga kabatan-onan nagmolayag sa kalipay human sa ilang graduation.; Ang pamilya nagmolayag sa kalipay sa ilang bakasyon sa probinsya.; Ang mga amigo nagmolayag sa kalipay sa ilang road trip.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>(euphemistic) coitus; sexual intercourse
-Synonyms: iyot, habal, kayat</t>
+          <t>(euphemistic) to have sexual intercourse</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>[(b'hilawas', 'NOUN')]</t>
+          <t>[(b'molayag', 'VERB'), (b'sa', 'PART'), (b'kalipay', 'ADJ')]</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>coitus</t>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>to have sexual intercourse</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>magtagay sa kalipay</t>
+          <t>paabang</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ang mga magtagay sa kalipay kasagaran makita sa mga parties ug celebrations.; Ang ilang magtagay sa kalipay nakaingon ug dakong kalipay sa tanan nga niapil.; Sa birthday ni Juan, nagmagtagay sa kalipay ang mga bisita hangtod sa kadlawn.; Ang mga magbarkada nagmagtagay sa kalipay human sa ilang reunion.; Ang mga mag-asawa nagmagtagay sa kalipay sa ilang anniversary celebration.</t>
+          <t>Gipahimutang ang iyang balay aron ipaabang sa mga bakasyonista.; Ang mga kwartong ipaabang kay dali ra kaayo mahurot ug ma-book.; Gipangita ang mga paabang nga balay nga duol sa eskwelahan.; Ang ilang negosyo nga paabang og sakyanan kay booming na kaayo karon.; Nagpaabang ug mga bisikleta ang resort para sa ilang mga bisita.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>(euphemistic) to have sexual intercourse</t>
+          <t>to rent out, (euphemistic, somewhat offensive) to prostitute</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>[(b'magtagay', 'VERB'), (b'sa', 'PART'), (b'kalipay', 'ADJ')]</t>
+          <t>[(b'paabang', 'NOUN')]</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>to have sexual intercourse</t>
+          <t>paabang</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>to rent out</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>molayag sa kalipay</t>
+          <t>pagkababaye</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ang mga magkauban nagmolayag sa kalipay sa ilang outing sa beach.; Sa dihang nagmolayag sa kalipay ang grupo, nakalimot sila sa ilang mga problema.; Ang mga kabatan-onan nagmolayag sa kalipay human sa ilang graduation.; Ang pamilya nagmolayag sa kalipay sa ilang bakasyon sa probinsya.; Ang mga amigo nagmolayag sa kalipay sa ilang road trip.</t>
+          <t>Ang iyang pagkababaye makita sa iyang pag-atiman sa pamilya.; Ang pagkababaye ni Maria nagpakita sa iyang pagka-mapinanggaon ug malumo.; Si Ana kay nagpakita sa tinuod niyang pagkababaye pinaagi sa iyang mga buhat.; Ang tinuod nga pagkababaye makita sa iyang pag-atiman ug pagpasabot sa uban.; Ang mga butang nga iyang gibuhat nagpakita sa iyang pagkababaye nga walay pagduda.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>(euphemistic) to have sexual intercourse</t>
+          <t>femininity; womanhood, (euphemistic) virginity</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>[(b'molayag', 'VERB'), (b'sa', 'PART'), (b'kalipay', 'ADJ')]</t>
+          <t>[(b'pagkababaye', 'NOUN')]</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>to have sexual intercourse</t>
+        <v>0</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>femininity</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>paabang</t>
+          <t>rampa</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Gipahimutang ang iyang balay aron ipaabang sa mga bakasyonista.; Ang mga kwartong ipaabang kay dali ra kaayo mahurot ug ma-book.; Gipangita ang mga paabang nga balay nga duol sa eskwelahan.; Ang ilang negosyo nga paabang og sakyanan kay booming na kaayo karon.; Nagpaabang ug mga bisikleta ang resort para sa ilang mga bisita.</t>
+          <t>Nag-rampa si Ana sa fashion show ug nakadani sa mga manan-aw.; Ang mga modelo nag-rampa sa runway ug gipalakpakan sa tanan.; Si Juan ug Maria nag-rampa sa park aron mag-relax ug maglingaw-lingaw.; Ang mga dalaga ug ulitawo nag-rampa sa plaza atol sa pista.; Ang mga artista nag-rampa sa red carpet sa premiere night.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
-        <is>
-          <t>to rent out, (euphemistic, somewhat offensive) to prostitute</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>[(b'paabang', 'NOUN')]</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>to rent out</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>pabuto</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Ang mga bata malipay kaayo sa mga pabuto kada New Year.; Ang pabuto sa fiesta kay naghatag ug dako nga kahibulongan sa mga manan-aw.; Ang iyang surprise party kay murag pabuto nga naka-shock sa tanan.; Ang pabuto sa mga bulak sa garden kay nindot kaayo tan-awon.; Ang mga pabuto sa fireworks display kay giapil sa celebration sa Independence Day.</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>a firecracker, a firework, the wayside tuberose (Ruellia tuberosa) and its dehiscent seed capsules, any dehiscent seed capsule or pod, to light a firework or a firecracker, to make something explode, (euphemistic) to masturbate to ejaculation, (euphemistic) to have sexual intercourse</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>[(b'pabuto', 'VERB')]</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>a firecracker</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>rampa</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Nag-rampa si Ana sa fashion show ug nakadani sa mga manan-aw.; Ang mga modelo nag-rampa sa runway ug gipalakpakan sa tanan.; Si Juan ug Maria nag-rampa sa park aron mag-relax ug maglingaw-lingaw.; Ang mga dalaga ug ulitawo nag-rampa sa plaza atol sa pista.; Ang mga artista nag-rampa sa red carpet sa premiere night.</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
         <is>
           <t>ramp (inclined surface), cramp, a catwalk, a leisurely walk; a ramble; a stroll, to sashay, to go for a stroll, to leave one's abode to go to public places, (euphemistic) to cruise; to actively seek a romantic partner or casual sexual partner by moving about a particular area, platform, ramp, pad, lame (physically disabled), lame person or animal (one physically disabled), third-person singular past historic of ramper, indefinite accusative plural of rampur, indefinite genitive plural of rampur, lame, flight (of stairs), ramp, launchpad
 Synonym: rampa di lancio, definite feminine singular of rampe, definite feminine singular of rampe, ramp (inclined surface that connects two levels; incline), ramp
@@ -1804,138 +1762,217 @@
 Synonym: calambre, ramp, (especially fashion, colloquial) runway walk (like a runway model)</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>[(b'rampa', 'VERB')]</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ramp</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>sabong</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Ang sabong sa arena kay gitan-aw sa daghang mga tawo.; Ang mga manok nga ipangsabong kay gipangandaman ug maayo.; Ang mga sabong sa probinsya kasagaran ginadumog sa mga lokal nga residente.; Ang sabong sa mga manok kay paborito nga pastime sa mga kalalakin-an.; Ang mga sabong nagpakita sa abilidad sa mga magmamantala ug pag-atiman sa ilang mga manok.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>a contest, in a cockpit, between gamecocks fitted with cockspurs; a cockfight; cockfighting, (euphemistic) sexual intercourse, to pair off or pair up to fight, flower, flower, petal, flower, cockfight, attack of a cock against another
+Synonyms: salpok, pagsalpok, soap</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>[(b'sabong', 'VERB')]</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>a contest</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>taga</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Ang mga kawatan nga nadakpan kay gi-taga sa mga pulis.; Ang mga prutas gitaga ug maayo aron ma-preserve ug dili dali madaot.; Ang kahoy nga nagtapok sa likod gipangtaga para himoong kahoy pangsiga.; Ang mga kawatan nahadlok kay basin mataga sila sa mga tag-iya sa balay.; Ang mga batan-on nagpraktis ug taga sa kahoy para sa ilang project sa eskwelahan.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>slash; hack (from a sharp object), to attack, (preceding a place) from or denoting residency in or around a place, district, area, or region, (preceding a proper noun) denoting a resident or inhabitant of (the place denoted by the proper noun), to give, a fishhook, (euphemistic) the penis, to fish or catch with a hook, daily, diurnal, at the back</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>[(b'rampa', 'VERB')]</t>
+          <t>[(b'taga', 'ADV')]</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>ramp</t>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>slash</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>sabong</t>
+          <t>taliba</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ang sabong sa arena kay gitan-aw sa daghang mga tawo.; Ang mga manok nga ipangsabong kay gipangandaman ug maayo.; Ang mga sabong sa probinsya kasagaran ginadumog sa mga lokal nga residente.; Ang sabong sa mga manok kay paborito nga pastime sa mga kalalakin-an.; Ang mga sabong nagpakita sa abilidad sa mga magmamantala ug pag-atiman sa ilang mga manok.</t>
+          <t>Ang mga pulis nag-taliba sa mga salida aron protektahan ang mga bisita.; Ang mga magtutudlo nag-taliba sa mga estudyante sa ilang field trip.; Ang mga guwardiya nag-taliba sa building adlaw ug gabii.; Ang mga volunteers nag-taliba sa event para malikayan ang mga kagubot.; Ang mga barangay tanod nag-taliba sa ilang mga area kada gabii.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
-        <is>
-          <t>a contest, in a cockpit, between gamecocks fitted with cockspurs; a cockfight; cockfighting, (euphemistic) sexual intercourse, to pair off or pair up to fight, flower, flower, petal, flower, cockfight, attack of a cock against another
-Synonyms: salpok, pagsalpok, soap</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>[(b'sabong', 'VERB')]</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>a contest</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>taga</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Ang mga kawatan nga nadakpan kay gi-taga sa mga pulis.; Ang mga prutas gitaga ug maayo aron ma-preserve ug dili dali madaot.; Ang kahoy nga nagtapok sa likod gipangtaga para himoong kahoy pangsiga.; Ang mga kawatan nahadlok kay basin mataga sila sa mga tag-iya sa balay.; Ang mga batan-on nagpraktis ug taga sa kahoy para sa ilang project sa eskwelahan.</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>slash; hack (from a sharp object), to attack, (preceding a place) from or denoting residency in or around a place, district, area, or region, (preceding a proper noun) denoting a resident or inhabitant of (the place denoted by the proper noun), to give, a fishhook, (euphemistic) the penis, to fish or catch with a hook, daily, diurnal, at the back</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>[(b'taga', 'ADV')]</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>slash</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>taliba</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Ang mga pulis nag-taliba sa mga salida aron protektahan ang mga bisita.; Ang mga magtutudlo nag-taliba sa mga estudyante sa ilang field trip.; Ang mga guwardiya nag-taliba sa building adlaw ug gabii.; Ang mga volunteers nag-taliba sa event para malikayan ang mga kagubot.; Ang mga barangay tanod nag-taliba sa ilang mga area kada gabii.</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
         <is>
           <t>(chiefly humorous) the female genitalia; the vulva or vagina, sentinel; guard; vanguard
 Synonyms: guwardiya, tanod, bantay, sentinela, act of guarding
 Synonyms: guwardiya, pagguwardiya, tanod, pagtanod, one's turn or shift of guarding</t>
         </is>
       </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>[(b'taliba', 'VERB')]</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>the female genitalia</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>tinagoan</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ang mga tinagoan nga yaman sa lumang bahay kay nadiskubrehan.; Ang tinagoan nga lihim ni Juan kay nahibaw-an na sa tanan.; Ang tinagoan nga kwarta kay gikuha sa mga tulisan.; Ang tinagoan nga dokumento kay importante kaayo para sa kaso.; Ang tinagoan nga mga gamit kay kinahanglan pangitaan sa panahon sa inventory.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>hidden away; stashed away, that which is hidden, (euphemistic) the penis, (euphemistic) the vulva</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>[(b'tinagoan', 'NOUN')]</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>hidden away</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>toyi</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Ang iyang joke bahin sa toyi kay nakapatawa sa tanan.; Ang mga istorya nila bahin sa toyi kay walay kinutuban nga katawa.; Sa dihang nagbinuang siya, nagtoyi lang iyang mga amigo.; Ang ilang duwa nga toyi kay naghatag ug dako nga kalipay.; Ang iyang mga joke kay kasagaran tungkol sa toyi.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>(humorous, euphemistic) coitus; sexual intercourse, (humorous, euphemistic) to fuck; to have sex, indefinite dative of toy</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>[(b'taliba', 'VERB')]</t>
+          <t>[(b'toyi', 'VERB')]</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1947,79 +1984,78 @@
       <c r="G36" t="n">
         <v>1</v>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>the female genitalia</t>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>coitus</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>tinagoan</t>
+          <t>tuslok baki</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ang mga tinagoan nga yaman sa lumang bahay kay nadiskubrehan.; Ang tinagoan nga lihim ni Juan kay nahibaw-an na sa tanan.; Ang tinagoan nga kwarta kay gikuha sa mga tulisan.; Ang tinagoan nga dokumento kay importante kaayo para sa kaso.; Ang tinagoan nga mga gamit kay kinahanglan pangitaan sa panahon sa inventory.</t>
+          <t>Ang tuslok baki nga duwa kay paborito sa mga bata sa baryo.; Kada fiesta, magdula mi ug tuslok baki aron maglingaw-lingaw.; Ang tuslok baki nga dula kay naghatag ug dakong excitement sa mga bata.; Ang mga bata nagpraktis sa tuslok baki aron mahimong champion sa dula.; Ang tuslok baki kay usa ka traditional nga dula nga gipasa-pasa sa mga henerasyon.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>hidden away; stashed away, that which is hidden, (euphemistic) the penis, (euphemistic) the vulva</t>
+          <t>a game, (euphemistic) sexual intercourse</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>[(b'tinagoan', 'NOUN')]</t>
+          <t>[(b'tuslok', 'VERB'), (b'baki', 'OTH')]</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
         <v>1</v>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>hidden away</t>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>a game</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>toyi</t>
+          <t>ul-ol</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ang iyang joke bahin sa toyi kay nakapatawa sa tanan.; Ang mga istorya nila bahin sa toyi kay walay kinutuban nga katawa.; Sa dihang nagbinuang siya, nagtoyi lang iyang mga amigo.; Ang ilang duwa nga toyi kay naghatag ug dako nga kalipay.; Ang iyang mga joke kay kasagaran tungkol sa toyi.</t>
+          <t>Ang iyang buhat kay ul-ol kaayo, wala gyud maghunahuna.; Ayaw pag-ul-ol, kinahanglan naa kay respeto sa uban.; Ang mga ul-ol nga tawo kasagaran dili makuha ang tinuod nga punto.; Ang iyang mga ul-ol nga istorya kay naghatag ug kalibog sa tanan.; Dili maayo nga magsige ka ug ul-ol kay makadaot kini sa imong reputation.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>(humorous, euphemistic) coitus; sexual intercourse, (humorous, euphemistic) to fuck; to have sex, indefinite dative of toy</t>
+          <t>(humorous, euphemistic) to masturbate
+Synonyms: batil, jakol, lulo, Obsolete form of ulol., pain; ache</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>[(b'toyi', 'VERB')]</t>
+          <t>[(b'ul-ol', 'VERB')]</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -2031,174 +2067,168 @@
       <c r="G38" t="n">
         <v>1</v>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>coitus</t>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>to masturbate
+Synonyms: batil</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>tunga</t>
+          <t>wala nahilig</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ang tunga sa kalibutan kay naa sa Asia.; Ang tunga sa iyang kwarta gihatag niya sa iyang igsoon.; Ang mga magtiayon nagbahin sa ilang mga responsibilidad sa tunga.; Naa sila sa tunga sa ilang paglakaw padulong sa ilang destino.; Ang mga mananagat nagtrabaho sa tunga sa dagat para sa ilang panginabuhian.</t>
+          <t>Si Juan wala nahilig sa mga seryosong relasyon, ganahan ra ug fling.; Ang mga wala nahilig sa seryosong relasyon kasagaran ganahan lang ug lingaw-lingaw.; Ang mga wala nahilig mag-settle down kay kasagaran naglibut-libot lang.; Dili kinahanglan pugson ang wala nahilig sa mga seryosong relasyon.; Ang mga wala nahilig kay dili gyud magdugay sa usa ka relasyon.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>half, center; middle
-(geometry) the center of a circle
-(geometry) the center of a sphere
-the middle portion of something; the part well away from the edges
-(geometry) the point on a line that is midway between the ends
-(geometry) the point in the interior of any figure of any number of dimensions that has as its coordinates the arithmetic mean of the coordinates of all points on the perimeter of the figure (or of all points in the interior for a center of volume), (geometry) the center of a circle, (geometry) the center of a sphere, the middle portion of something; the part well away from the edges, (geometry) the point on a line that is midway between the ends, (geometry) the point in the interior of any figure of any number of dimensions that has as its coordinates the arithmetic mean of the coordinates of all points on the perimeter of the figure (or of all points in the interior for a center of volume), (slang, euphemistic) vagina, (geometry) the center of a circle, (geometry) the center of a sphere, the middle portion of something; the part well away from the edges, (geometry) the point on a line that is midway between the ends, (geometry) the point in the interior of any figure of any number of dimensions that has as its coordinates the arithmetic mean of the coordinates of all points on the perimeter of the figure (or of all points in the interior for a center of volume), to split into halves, to increase to halfway point, to show up, tongue (organ), mother tongue, language, tongue of land in a stream, the tongue of a shoe, lemon sole (Microstomus kitt), to build, (anatomy) a tongue, language, the tongue of a shoe, to sew, to build, to sew, to build, water</t>
+          <t>any man uninterested in committed relationships, (euphemistic) a closeted homosexual</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>[(b'tunga', 'VERB')]</t>
+          <t>[(b'wala', 'ADV'), (b'nahilig', 'VERB')]</t>
         </is>
       </c>
       <c r="E39" t="n">
         <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>half</t>
+        <v>0</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>any man uninterested in committed relationships</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>tuslok baki</t>
+          <t>abot na sa dukot</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ang tuslok baki nga duwa kay paborito sa mga bata sa baryo.; Kada fiesta, magdula mi ug tuslok baki aron maglingaw-lingaw.; Ang tuslok baki nga dula kay naghatag ug dakong excitement sa mga bata.; Ang mga bata nagpraktis sa tuslok baki aron mahimong champion sa dula.; Ang tuslok baki kay usa ka traditional nga dula nga gipasa-pasa sa mga henerasyon.</t>
+          <t>Ang iyang mga problema murag abot na sa dukot, grabe na kaayo.; Ang ilang resources abot na sa dukot, kinahanglan na gyud ug tabang.; Ang mga suplay sa tindahan abot na sa dukot, hapit na mahurot.; Sa kadugay nga paghulat, ang iyang pasensya abot na sa dukot.; Ang mga isyu sa opisina abot na sa dukot, kinahanglan na gyud sulbaron.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>a game, (euphemistic) sexual intercourse</t>
+          <t xml:space="preserve"> scrape the bottom of the barrel</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>[(b'tuslok', 'VERB'), (b'baki', 'OTH')]</t>
+          <t>[(b'abot', 'VERB'), (b'na', 'ADV'), (b'sa', 'PART'), (b'dukot', 'VERB')]</t>
         </is>
       </c>
       <c r="E40" t="n">
         <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
         <v>1</v>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>a game</t>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>scrape the bottom of the barrel</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ul-ol</t>
+          <t>abot sa dalunggan ang ngisi</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ang iyang buhat kay ul-ol kaayo, wala gyud maghunahuna.; Ayaw pag-ul-ol, kinahanglan naa kay respeto sa uban.; Ang mga ul-ol nga tawo kasagaran dili makuha ang tinuod nga punto.; Ang iyang mga ul-ol nga istorya kay naghatag ug kalibog sa tanan.; Dili maayo nga magsige ka ug ul-ol kay makadaot kini sa imong reputation.</t>
+          <t>Pagkahuman sa eksam, abot sa dalunggan ang ngisi ni Juan kay nakapasar siya.; Sa dihang nadawat siya sa trabaho, abot sa dalunggan ang ngisi ni Maria.; Ang bata, abot sa dalunggan ang ngisi sa dihang gihatagan ug dako nga regalo.; Abot sa dalunggan ang ngisi sa mga ginikanan sa ilang anak nga nag-graduate.; Sa dihang nagkita sila, abot sa dalunggan ang ngisi ni Pedro ug Ana.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>(humorous, euphemistic) to masturbate
-Synonyms: batil, jakol, lulo, Obsolete form of ulol., pain; ache</t>
+          <t>(hyperhole, idiomatic) to be overjoyed, extremely happy</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>[(b'ul-ol', 'VERB')]</t>
+          <t>[(b'abot', 'VERB'), (b'sa', 'PART'), (b'dalunggan', 'VERB'), (b'ang', 'DET'), (b'ngisi', 'VERB')]</t>
         </is>
       </c>
       <c r="E41" t="n">
         <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>1</v>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>to masturbate
-Synonyms: batil</t>
+          <t>abot</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>to be overjoyed</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>abli ang Gaisano</t>
+          <t>abot sa dunggan ang ngisi</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Si Juan wala kabantay nga abli ang Gaisano, maong giingnan siya sa iyang higala.; Ang abli ang Gaisano nga pantalon kay nakakatawa kaayo sa mga kakuyog.; Kung abli ang Gaisano, kinahanglan dayon sirad-an aron dili magkatawa ang uban.; Ang mga tao nga abli ang Gaisano kasagaran walay pakialam sa ilang itsura.; Ayaw kalimti nga tan-awon kung abli ba ang Gaisano aron malikayan ang uwaw.</t>
+          <t>Ang among boss, abot sa dunggan ang ngisi sa dihang nadawat ang dagkong proyekto.; Abot sa dunggan ang ngisi ni Lito pagkakita sa iyang paboritong artista.; Sa dihang gihatagan siya ug award, abot sa dunggan ang ngisi ni Carla.; Ang mga bata, abot sa dunggan ang ngisi sa dihang nagkaon og ice cream.; Abot sa dunggan ang ngisi ni Manang Ines pagkakita sa iyang mga apo.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>(dated, humorous) having one's fly open (see usage notes)</t>
+          <t>(hyperhole, idiomatic) to be overjoyed, extremely happy</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>[(b'abli', 'ADJ'), (b'ang', 'DET'), (b'Gaisano', 'NOUN')]</t>
+          <t>[(b'abot', 'VERB'), (b'sa', 'PART'), (b'dunggan', 'VERB'), (b'ang', 'DET'), (b'ngisi', 'VERB')]</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -2206,121 +2236,122 @@
       <c r="G42" t="n">
         <v>1</v>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>having one's fly open</t>
+          <t>abot</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>to be overjoyed</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>abot na sa dukot</t>
+          <t>abot sa pikas bukid</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ang iyang mga problema murag abot na sa dukot, grabe na kaayo.; Ang ilang resources abot na sa dukot, kinahanglan na gyud ug tabang.; Ang mga suplay sa tindahan abot na sa dukot, hapit na mahurot.; Sa kadugay nga paghulat, ang iyang pasensya abot na sa dukot.; Ang mga isyu sa opisina abot na sa dukot, kinahanglan na gyud sulbaron.</t>
+          <t>Ang mga chismosa abot sa pikas bukid ang ilang mga istorya.; Bisan asa pa sila, abot sa pikas bukid ang ilang tingog.; Ang iyang reklamo abot sa pikas bukid, grabe kaayo ug kasaba.; Ang istorya ni Pedro abot sa pikas bukid bisan dili tinuod.; Ang mga away sa ilang pamilya abot sa pikas bukid, daghan nakahibalo.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve"> scrape the bottom of the barrel</t>
+          <t xml:space="preserve"> someone who talks loudly, laudmouth</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>[(b'abot', 'VERB'), (b'na', 'ADV'), (b'sa', 'PART'), (b'dukot', 'VERB')]</t>
+          <t>[(b'abot', 'VERB'), (b'sa', 'PART'), (b'pikas', 'ADJ'), (b'bukid', 'NOUN')]</t>
         </is>
       </c>
       <c r="E43" t="n">
         <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
         <v>1</v>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>scrape the bottom of the barrel</t>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>someone who talks loudly</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>abot sa dalunggan ang ngisi</t>
+          <t>agas og palad</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Pagkahuman sa eksam, abot sa dalunggan ang ngisi ni Juan kay nakapasar siya.; Sa dihang nadawat siya sa trabaho, abot sa dalunggan ang ngisi ni Maria.; Ang bata, abot sa dalunggan ang ngisi sa dihang gihatagan ug dako nga regalo.; Abot sa dalunggan ang ngisi sa mga ginikanan sa ilang anak nga nag-graduate.; Sa dihang nagkita sila, abot sa dalunggan ang ngisi ni Pedro ug Ana.</t>
+          <t>Si Juan agas og palad, walay kwarta magdugay sa iyang kamot.; Bisan unsa kadako ang sweldo, si Ana agas og palad, dili makatigom.; Ang mga tawo nga agas og palad kasagaran dili makatigom ug insakto.; Ang iyang kinaiya nga agas og palad nagdala ug kalisod sa iyang kinabuhi.; Kinahanglan ka mag-amping sa imong kwarta, dili ka mag-agas og palad.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>(hyperhole, idiomatic) to be overjoyed, extremely happy</t>
+          <t xml:space="preserve"> a spendthrift</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>[(b'abot', 'VERB'), (b'sa', 'PART'), (b'dalunggan', 'VERB'), (b'ang', 'DET'), (b'ngisi', 'VERB')]</t>
+          <t>[(b'agas', 'ADJ'), (b'og', 'CONJ'), (b'palad', 'NOUN')]</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>to be overjoyed</t>
+        <v>0</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>a spendthrift</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>abot sa dunggan ang ngisi</t>
+          <t>agi sa bangag sa dagom</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ang among boss, abot sa dunggan ang ngisi sa dihang nadawat ang dagkong proyekto.; Abot sa dunggan ang ngisi ni Lito pagkakita sa iyang paboritong artista.; Sa dihang gihatagan siya ug award, abot sa dunggan ang ngisi ni Carla.; Ang mga bata, abot sa dunggan ang ngisi sa dihang nagkaon og ice cream.; Abot sa dunggan ang ngisi ni Manang Ines pagkakita sa iyang mga apo.</t>
+          <t>Si Pedro agi sa bangag sa dagom aron lang makapasar sa eksam.; Ang ilang proyekto agi sa bangag sa dagom sa kalisod.; Ang iyang negosyo agi sa bangag sa dagom bago niyag napalambo.; Si Ana agi sa bangag sa dagom sa iyang pag-eskwela ug pagtrabaho.; Ang ilang relasyon agi sa bangag sa dagom sa daghang pagsulay.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>(hyperhole, idiomatic) to be overjoyed, extremely happy</t>
+          <t xml:space="preserve"> experience hardships in achieving one's goal or dream</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>[(b'abot', 'VERB'), (b'sa', 'PART'), (b'dunggan', 'VERB'), (b'ang', 'DET'), (b'ngisi', 'VERB')]</t>
+          <t>[(b'agi', 'VERB'), (b'sa', 'PART'), (b'bangag', 'VERB'), (b'sa', 'PART'), (b'dagom', 'NOUN')]</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -2332,37 +2363,40 @@
       <c r="G45" t="n">
         <v>1</v>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>to be overjoyed</t>
+          <t>agi</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>experience hardships in achieving one's goal or dream</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>abot sa pikas bukid</t>
+          <t>awas og palad</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ang mga chismosa abot sa pikas bukid ang ilang mga istorya.; Bisan asa pa sila, abot sa pikas bukid ang ilang tingog.; Ang iyang reklamo abot sa pikas bukid, grabe kaayo ug kasaba.; Ang istorya ni Pedro abot sa pikas bukid bisan dili tinuod.; Ang mga away sa ilang pamilya abot sa pikas bukid, daghan nakahibalo.</t>
+          <t>Si Lito awas og palad, dili gyud makatigom bisan unsa ka dako ang kita.; Ang mga awas og palad kasagaran maglisod sa pagplano sa ilang kaugmaon.; Si Pedro awas og palad, pirmi lang mag-antos kay dili magtigom.; Ang mga awas og palad kasagaran maglisod sa kinabuhi kay dili kabalo magtipid.; Si Ana awas og palad, maong pirmi lang maglisod bisan taas ang sweldo.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve"> someone who talks loudly, laudmouth</t>
+          <t>• awasan og palad, • agas og palad,  a spendthrift, extravagant</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>[(b'abot', 'VERB'), (b'sa', 'PART'), (b'pikas', 'ADJ'), (b'bukid', 'NOUN')]</t>
+          <t>[(b'awas', 'VERB'), (b'og', 'CONJ'), (b'palad', 'NOUN')]</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -2374,37 +2408,36 @@
       <c r="G46" t="n">
         <v>1</v>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>someone who talks loudly</t>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>• awasan og palad</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>agi sa bangag sa dagom</t>
+          <t>bantay pari</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Si Pedro agi sa bangag sa dagom aron lang makapasar sa eksam.; Ang ilang proyekto agi sa bangag sa dagom sa kalisod.; Ang iyang negosyo agi sa bangag sa dagom bago niyag napalambo.; Si Ana agi sa bangag sa dagom sa iyang pag-eskwela ug pagtrabaho.; Ang ilang relasyon agi sa bangag sa dagom sa daghang pagsulay.</t>
+          <t>Si Pedro bantay pari sa ilang balay kay wala'y makalusot nga problema.; Ang mga ginikanan kasagaran bantay pari sa ilang mga anak.; Si Maria bantay pari sa iyang mga kauban sa trabaho aron dili magbinulantoy.; Ang mga bantay pari nga tawo kasagaran mahimong lider sa ilang komunidad.; Ang iyang bantay pari nga kinaiya nakapahimo nga malampuson ang ilang proyekto.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve"> experience hardships in achieving one's goal or dream</t>
+          <t xml:space="preserve"> to keep a close watch on somebody/something.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>[(b'agi', 'VERB'), (b'sa', 'PART'), (b'bangag', 'VERB'), (b'sa', 'PART'), (b'dagom', 'NOUN')]</t>
+          <t>[(b'bantay', 'VERB'), (b'pari', 'NOUN')]</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -2416,165 +2449,161 @@
       <c r="G47" t="n">
         <v>1</v>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>experience hardships in achieving one's goal or dream</t>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>to keep a close watch on somebody/something</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>anak sa sala</t>
+          <t>bukhad og palad</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Si Lito kay anak sa sala, pero walay kabilinggan ang iyang amahan sa pag-atiman kaniya.; Ang anak sa sala nga si Maria kay ginaatiman gihapon sa iyang lola ug lolo.; Ang mga anak sa sala kasagaran nagdako nga adunay mga pagsulay sa ilang kinabuhi.; Si Juan nga anak sa sala kay giatiman sa iyang inahan bisan walay suporta sa iyang amahan.; Ang anak sa sala kasagaran maglisod sa pagsulod sa mga respetadong institusyon.</t>
+          <t>Si Ana bukhad og palad, pirmi lang maghatag bisan sa mga dili kaila.; Ang mga tao nga bukhad og palad kasagaran daghan ug mga amigo.; Si Juan bukhad og palad, bisan sa iyang kalisod, pirmi lang magtabang.; Ang iyang pamilya bukhad og palad, maong daghan ang nagmahal kanila.; Ang mga tawo nga bukhad og palad kasagaran masinabtanon ug mapinanggaon.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve"> an illegitimate child; a child born out of wedlock
-Synonyms: pinaangkan, anak sa gawas
-Antonyms: anak sa sakramento, anak sa kasal</t>
+          <t xml:space="preserve"> generous
+Synonyms: manggihatagon, mahatagon</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>[(b'anak', 'NOUN'), (b'sa', 'PART'), (b'sala', 'VERB')]</t>
+          <t>[(b'bukhad', 'VERB'), (b'og', 'CONJ'), (b'palad', 'NOUN')]</t>
         </is>
       </c>
       <c r="E48" t="n">
         <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>an illegitimate child</t>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>generous
+Synonyms: manggihatagon</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ander da bunal</t>
+          <t>buotan ra og matulog</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Si Juan kay ander da bunal, bisan unsa isugo sa iyang asawa kay tumanon.; Ang mga ander da bunal kasagaran magpailalom sa mga buot-buoton nga asawa.; Si Pedro nga ander da bunal kay wala'y laing mabuhat kundi musunod sa misis.; Ang ander da bunal nga bana kay kasagaran magpaubos ug musunod sa asawa.; Ang relasyon nila kay ander da bunal, maong klaro kaayo kinsa ang nagbuot.</t>
+          <t>Si Pedro buotan ra og matulog, kay pirmi lang magbinuang sa klase.; Ang iyang anak buotan ra og matulog, kay pirmi lang mangaway sa mga silingan.; Si Juan buotan ra og matulog, kay dili gyud mahimutang kung magmata.; Ang mga bata nga buotan ra og matulog kasagaran magdala ug kasamok sa balay.; Si Ana buotan ra og matulog, kay pirmi lang magbinuang sa iyang mga igsoon.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>henpecked, Pussywhipped, a henpecked husband or boyfriend</t>
+          <t xml:space="preserve"> mischievous,  a troublemaker</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>[(b'ander', 'ADJ'), (b'da', 'PART'), (b'bunal', 'VERB')]</t>
+          <t>[(b'buotan', 'ADJ'), (b'ra', 'ADV'), (b'og', 'CONJ'), (b'matulog', 'VERB')]</t>
         </is>
       </c>
       <c r="E49" t="n">
         <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>henpecked</t>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>mischievous</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ander de bunal</t>
+          <t>dila ray way labod</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Si Pedro kay ander de bunal, kay pirmi lang musunod sa iyang asawa bisan unsa pa.; Ang ander de bunal nga mga bana kay wala gyud lain nga mahimo kung dili musunod sa misis.; Si Juan nga ander de bunal kay pirmi nag-atiman sa mga gusto sa iyang asawa.; Ang ander de bunal nga relasyon kay klaro kaayo kinsa ang nagbuot.; Ang mga ander de bunal kay dili na maghunahuna sa ilang kaugalingong gusto.</t>
+          <t>Si Juan dila ray way labod, kay pirmi lang magsige ug kaon bisan sakit na iyang tiyan.; Ang mga bata dila ray way labod kung naa sa handaan.; Si Pedro dila ray way labod, bisan unsa na lang ang kaon nga dili na healthy.; Ang mga tawo nga dila ray way labod kasagaran maglisod sa ilang lawas.; Si Maria dila ray way labod, pirmi lang magpataka ug kaon sa mga events.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>henpecked, a henpecked husband or boyfriend</t>
+          <t xml:space="preserve"> extremely hurt; badly beaten up</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>[(b'ander', 'ADJ'), (b'de', 'ADV'), (b'bunal', 'VERB')]</t>
+          <t>[(b'dila', 'NOUN'), (b'ray', 'ADV'), (b'way', 'ADV'), (b'labod', 'NOUN')]</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>henpecked</t>
+        <v>0</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>extremely hurt</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>awas og palad</t>
+          <t>dili madala og rosaryo</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Si Lito awas og palad, dili gyud makatigom bisan unsa ka dako ang kita.; Ang mga awas og palad kasagaran maglisod sa pagplano sa ilang kaugmaon.; Si Pedro awas og palad, pirmi lang mag-antos kay dili magtigom.; Ang mga awas og palad kasagaran maglisod sa kinabuhi kay dili kabalo magtipid.; Si Ana awas og palad, maong pirmi lang maglisod bisan taas ang sweldo.</t>
+          <t>Ang iyang problema dili madala og rosaryo, kinahanglan gyud ug aksyon.; Si Pedro nag-atubang sa mga pagsulay nga dili madala og rosaryo.; Ang mga tawo nga naa sa kalisod kasagaran dili madala og rosaryo ilang mga problema.; Si Maria nag-antos sa mga butang nga dili madala og rosaryo.; Ang ilang sitwasyon sa negosyo dili madala og rosaryo, kinahanglan ug solusyon.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>• awasan og palad, • agas og palad,  a spendthrift, extravagant</t>
+          <t xml:space="preserve"> an utterly hopeless situation</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>[(b'awas', 'VERB'), (b'og', 'CONJ'), (b'palad', 'NOUN')]</t>
+          <t>[(b'dili', 'ADV'), (b'madala', 'VERB'), (b'og', 'CONJ'), (b'rosaryo', 'NOUN')]</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -2586,121 +2615,118 @@
       <c r="G51" t="n">
         <v>1</v>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>• awasan og palad</t>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>an utterly hopeless situation</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>baba sa atay</t>
+          <t>dili makaon og iro</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ang baba sa atay kinahanglan ampingan ug atimanon para sa maayong panglawas.; Ang problema sa baba sa atay kasagaran makuha pinaagi sa dili maayong pagkaon.; Ang mga tambal para sa baba sa atay kay kinahanglan sa pag-maintain sa maayong kondisyon.; Ang mga problema sa baba sa atay kasagaran magsugod sa dili maayong lifestyle.; Ang pag-amping sa baba sa atay usa ka importante nga parte sa pag-atiman sa lawas.</t>
+          <t>Ang iyang batasan dili makaon og iro, maong walay ganahan makighangyo niya.; Si Juan dili makaon og iro, kay pirmi lang maghimo ug gubot.; Ang mga tawo nga dili makaon og iro kasagaran walay respeto sa uban.; Si Maria dili makaon og iro, bisan unsa pa nga istorya, walay muuban niya.; Ang iyang batasan kay dili makaon og iro, maong nag-inusara siya pirmi.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>(anatomy, idiomatic) diaphragm</t>
+          <t xml:space="preserve"> appalling, revolting, inciting disgust,  a despicable person, a piece of shit</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>[(b'baba', 'VERB'), (b'sa', 'PART'), (b'atay', 'NOUN')]</t>
+          <t>[(b'dili', 'ADV'), (b'makaon', 'VERB'), (b'og', 'CONJ'), (b'iro', 'NOUN')]</t>
         </is>
       </c>
       <c r="E52" t="n">
         <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>diaphragm</t>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>appalling</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>babayeng ikogan</t>
+          <t>dobleg suwab ang dila</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ang babayeng ikogan nga si Juanita kay giilhan sa ilang baryo.; Si Pedro kay permi magbuang sa mga babayeng ikogan.; Ang babayeng ikogan kasagaran magdala ug kalisod sa ilang mga pamilya.; Si Ana nga babayeng ikogan kay walay klaro nga direksyon sa kinabuhi.; Ang mga istorya bahin sa mga babayeng ikogan kasagaran puno sa drama.</t>
+          <t>Si Pedro dobleg suwab ang dila, pirmi lang mangaway bisan walay hinungdan.; Ang iyang amiga dobleg suwab ang dila, pirmi lang maglagot ug mangaway.; Si Juan dobleg suwab ang dila, bisan gamay nga butang, dakuon gyud.; Ang mga tawo nga dobleg suwab ang dila kasagaran magbuhat ug samok sa grupo.; Si Maria dobleg suwab ang dila, maong walay ganahan makig-istorya niya.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>(offensive) a transgender, transsexual or transvestite man, (often offensive, humorous) a woman with mistakable transsexual facial or physical features</t>
+          <t>(idiomatic, of a person) inclined to use harsh or hurtful words</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>[(b'babayeng', 'NOUN'), (b'ikogan', 'VERB')]</t>
+          <t>[(b'dobleg', 'ADJ'), (b'suwab', 'OTH'), (b'ang', 'DET'), (b'dila', 'NOUN')]</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
         <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>a transgender</t>
+        <v>0</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>inclined to use harsh or hurtful words</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bag-ong haon</t>
+          <t>dugay pay manguros</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ang iyang bag-ong haon nga cellphone kay nindot kaayo ug daghan ug features.; Ang bag-ong haon nga kotse ni Pedro kay makahatag ug dako nga garbo.; Si Ana permi mangita ug bag-ong haon nga mga gamit para sa balay.; Ang mga bata nagpaabot sa bag-ong haon nga mga dulaan nga gi-order online.; Ang bag-ong haon nga balay ni Maria kay puno sa modernong mga kagamitan.</t>
+          <t>Ang iyang trabaho dugay pay manguros, pirmi lang maghinay-hinay.; Si Juan dugay pay manguros kung magtrabaho sa opisina.; Ang mga tawo nga dugay pay manguros kasagaran maglisod sa ilang mga deadline.; Si Pedro dugay pay manguros, bisan unsa nga butang, hinay kaayo mahuman.; Ang iyang proyekto dugay pay manguros, walay klaro nga mahuman.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve"> recently produced, brand new, hot off the press,  a new model of something</t>
+          <t xml:space="preserve"> a piece of cake, cakewalk</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>[(b'bag-ong', 'VERB'), (b'haon', 'VERB')]</t>
+          <t>[(b'dugay', 'ADJ'), (b'pay', 'OTH'), (b'manguros', 'VERB')]</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -2712,125 +2738,122 @@
       <c r="G54" t="n">
         <v>1</v>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>recently produced</t>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>a piece of cake</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bahong biyuda</t>
+          <t>dula og panit</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Si Juan bahong biyuda kay wala gyud maligo ug maayo.; Ang iyang kwarto kay bahong biyuda, wala gyud linisan ug maayo.; Ang mga tawo nga dili mag-atiman sa ilang kaugalingon kasagaran bahong biyuda.; Si Pedro bahong biyuda kay bisan unsaon ug ligo, dili mawala ang baho.; Ang iyang gamit nga wala giayo kay bahong biyuda.</t>
+          <t>Si Pedro pirmi lang mag-dula og panit, bisan walay buhaton nga maayo.; Ang mga bata nga dula og panit kasagaran wala’y klaro nga padulngan.; Si Juan dula og panit, pirmi lang magtambay ug magbuot-buot.; Ang iyang barkada kay dula og panit, bisan unsa na lang nga kalipay ang gihimo.; Si Maria nagbuot-buot kay gusto siya magdula og panit pirmi.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>(humorous) having a strong musky or balmy smell, as opposed to the light and fresh smell of cologne</t>
+          <t xml:space="preserve"> to masturbate, jack off, to fap</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>[(b'bahong', 'VERB'), (b'biyuda', 'VERB')]</t>
+          <t>[(b'dula', 'VERB'), (b'og', 'CONJ'), (b'panit', 'NOUN')]</t>
         </is>
       </c>
       <c r="E55" t="n">
         <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>having a strong musky or balmy smell</t>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>to masturbate</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bahong biyudo</t>
+          <t>duwa og panit</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ang iyang sinina nga bahong biyudo kay dili nimo malapasan.; Ang mga tawo nga dili maghugas sa ilang mga gamit kasagaran bahong biyudo.; Si Juan bahong biyudo kay walay tarong nga pag-atiman sa iyang kaugalingon.; Ang iyang sapatos nga bahong biyudo kay reklamo sa tanan nga makaduol.; Ang mga gamit sa balay nga wala gipanumbaling kay bahong biyudo.</t>
+          <t>Si Juan pirmi lang mag-duwa og panit sa iyang kwarto.; Ang iyang mga kauban sa trabaho pirmi lang magbinuang ug magduwa og panit.; Si Pedro walay laing gihimo kundi magduwa og panit pirmi.; Ang mga bata nga nagdula sa internet pirmi lang magduwa og panit.; Si Maria naglagot kay si Juan pirmi lang magduwa og panit bisan kinahanglanon siya.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>(humorous) having a strong musky or balmy smell, as opposed to the light and fresh smell of cologne</t>
+          <t>(slang, idiomatic) to masturbate</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>[(b'bahong', 'VERB'), (b'biyudo', 'OTH')]</t>
+          <t>[(b'duwa', 'VERB'), (b'og', 'CONJ'), (b'panit', 'NOUN')]</t>
         </is>
       </c>
       <c r="E56" t="n">
         <v>1</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>having a strong musky or balmy smell</t>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>to masturbate</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bantay pari</t>
+          <t>gadalag ulan</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Si Pedro bantay pari sa ilang balay kay wala'y makalusot nga problema.; Ang mga ginikanan kasagaran bantay pari sa ilang mga anak.; Si Maria bantay pari sa iyang mga kauban sa trabaho aron dili magbinulantoy.; Ang mga bantay pari nga tawo kasagaran mahimong lider sa ilang komunidad.; Ang iyang bantay pari nga kinaiya nakapahimo nga malampuson ang ilang proyekto.</t>
+          <t>Si Juan kay gadalag ulan, maong daghan ang naglikay niya.; Ang iyang amigo gadalag ulan, maong dili siya ganahan kauban.; Si Pedro gadalag ulan, bisan unsa pa nga sitwasyon.; Ang mga tawo nga gadalag ulan kasagaran naglisod sa pagdawat sa uban.; Si Maria gadalag ulan, maong pirmi siya nag-inusara.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve"> to keep a close watch on somebody/something.</t>
+          <t xml:space="preserve"> a male homosexual</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>[(b'bantay', 'VERB'), (b'pari', 'NOUN')]</t>
+          <t>[(b'gadalag', 'ADJ'), (b'ulan', 'NOUN')]</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -2838,41 +2861,44 @@
       <c r="G57" t="n">
         <v>1</v>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="n">
+        <v>1</v>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>to keep a close watch on somebody/something</t>
+          <t>nagdala</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>a male homosexual</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>basa ang tingog</t>
+          <t>gadalag uwan</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Si Pedro basa ang tingog tungod sa iyang sip-on.; Ang singer nga basa ang tingog naglisod ug kanta sa concert.; Ang announcer basa ang tingog tungod sa pagkapoy sa iyang trabaho.; Si Juan basa ang tingog sa iyang speech tungod sa kabugnaw.; Ang tigbantay basa ang tingog tungod sa paghilak sa iyang pag-istorya.</t>
+          <t>Si Lito gadalag uwan, pero gihigugma gihapon sa iyang pamilya.; Ang iyang silingan gadalag uwan, pero respetado gihapon sa ilang lugar.; Si Juan gadalag uwan, bisan unsa pa nga istorya, wala magpailalom.; Ang mga tao nga gadalag uwan kasagaran adunay mga pagsulay sa kinabuhi.; Si Maria gadalag uwan, pero walay mopauli sa iyang pagkatawo.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve"> raspy in voice</t>
+          <t xml:space="preserve"> a male homosexual</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>[(b'basa', 'ADJ'), (b'ang', 'DET'), (b'tingog', 'VERB')]</t>
+          <t>[(b'gadalag', 'ADJ'), (b'uwan', 'ADJ')]</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -2880,83 +2906,85 @@
       <c r="G58" t="n">
         <v>1</v>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="n">
+        <v>1</v>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>raspy in voice</t>
+          <t>nagdala</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>a male homosexual</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>basa og baba</t>
+          <t>gi-indian</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Si Maria basa og baba kay pirmi lang mag-yawyaw bisan wala’y pulos.; Ang mga bata nga basa og baba kasagaran maglikay sa mga tahimik nga lugar.; Si Juan basa og baba ug permi magdala ug kasaba sa opisina.; Ang iyang mga amiga permi magbinuang sa iyang basa og baba nga kinaiya.; Ang mga tawo nga basa og baba kasagaran dili ganahan makakita sa mga tahimik nga tao.</t>
+          <t>Si Pedro gi-indian sa iyang uyab sa ilang sabot nga date.; Ang mga estudyante na gi-indian sa ilang maestra sa klase karon.; Si Maria nasuko kay gi-indian siya sa iyang amigo.; Ang iyang kauban sa trabaho gi-indian siya sa ilang meeting.; Si Juan gi-indian sa iyang kliyente sa ilang appointment.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve"> noisy; talkative</t>
+          <t>to fail to meet an appointment intentionally, to no-show</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>[(b'basa', 'ADJ'), (b'og', 'CONJ'), (b'baba', 'VERB')]</t>
+          <t>[(b'gi-indian', 'VERB')]</t>
         </is>
       </c>
       <c r="E59" t="n">
         <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" t="n">
         <v>1</v>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>noisy</t>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>to fail to meet an appointment intentionally</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>basag baba</t>
+          <t>gibati og kaanyag</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ang mga bata basag baba kung magdula sa gawas ug magkinantyawan.; Si Juan basag baba kung naa sa mga barkada ug magbinuang.; Ang mga estudyante basag baba kung magtapok sa kantina.; Si Maria basag baba kung magstorya sa telepono sa iyang amiga.; Ang mga tawo sa kanto basag baba kung magtapok ug magbinuang.</t>
+          <t>Si Ana gibati og kaanyag, maong pirmi siya nagbuot-buot.; Ang mga tawo nga gibati og kaanyag kasagaran magdala ug samok sa grupo.; Si Maria gibati og kaanyag, bisan unsa nga sugo, dili gyud mutuman.; Ang iyang amiga gibati og kaanyag, maong pirmi mag-away sa iyang bana.; Si Pedro gibati og kaanyag, maong pirmi magbuot sa ilang opisina.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve"> noisy; talkative</t>
+          <t xml:space="preserve"> prima donna; entitled person,  entitled</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>[(b'basag', 'ADJ'), (b'baba', 'VERB')]</t>
+          <t>[(b'gibati', 'NOUN'), (b'og', 'CONJ'), (b'kaanyag', 'ADV')]</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -2964,247 +2992,245 @@
       <c r="G60" t="n">
         <v>1</v>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="n">
+        <v>1</v>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>noisy</t>
+          <t>gibati</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>prima donna</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>batang murag korek</t>
+          <t>gigukod sa plansa</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Si Ana batang murag korek kay bisan bata pa, daghan na ug nahibaw-an.; Ang batang murag korek nga si Lito pirmi lang nagbuot-buot.; Si Maria batang murag korek ug maayo kaayo magdisiplina sa iyang mga igsoon.; Ang batang murag korek nga si Juan kasagaran mag-atubang sa mga problema sa balay.; Si Pedro batang murag korek kay bisan gamay pa, maayo na kaayo sa klase.</t>
+          <t>Si Juan pirmi lang gigukod sa plansa, kay dili siya ganahan magplantsa.; Ang iyang sinina pirmi lang gigukod sa plansa, maong bati tan-awon.; Si Pedro pirmi lang gigukod sa plansa, bisan unsa nga sinina dili mahimutang.; Ang mga tawo nga gigukod sa plansa kasagaran dili mag-atiman sa ilang kaugalingon.; Si Maria gigukod sa plansa, bisan unsa nga okasyon, dili gyud magplantsa.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>precocious, a precocious child</t>
+          <t xml:space="preserve"> someone who's wearing wrinkly clothes</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>[(b'batang', 'VERB'), (b'murag', 'ADJ'), (b'korek', 'ADJ')]</t>
+          <t>[(b'gigukod', 'VERB'), (b'sa', 'PART'), (b'plansa', 'NOUN')]</t>
         </is>
       </c>
       <c r="E61" t="n">
         <v>1</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G61" t="n">
         <v>1</v>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>precocious</t>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>someone who's wearing wrinkly clothes</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bato og kasingkasing</t>
+          <t>gigukod sa sudlay</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ang iyang amo kay bato og kasingkasing, wala gyud malumo bisan naghangyo na.; Si Juan bato og kasingkasing, wala gyud motabang bisan klaro nga nagkinahanglan ug tabang.; Ang mga tao nga bato og kasingkasing kasagaran maglisod sa relasyon sa uban.; Si Pedro bato og kasingkasing, dili gyud siya malumo bisan sa mga bata.; Ang iyang inahan bato og kasingkasing, dili malumo bisan klaro nga luoy na kaayo.</t>
+          <t>Si Ana pirmi lang gigukod sa sudlay, kay dili siya ganahan mag-comb sa iyang buhok.; Ang iyang buhok pirmi lang gigukod sa sudlay, maong bati kaayo tan-awon.; Si Pedro pirmi lang gigukod sa sudlay, bisan unsa nga event, dili mag-comb.; Ang mga tawo nga gigukod sa sudlay kasagaran dili mag-atiman sa ilang buhok.; Si Juan gigukod sa sudlay, bisan unsa nga party, dili gyud mag-comb.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>pitiless; heartless</t>
+          <t xml:space="preserve"> to have unkempt hair</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>[(b'bato', 'VERB'), (b'og', 'CONJ'), (b'kasingkasing', 'ADV')]</t>
+          <t>[(b'gigukod', 'VERB'), (b'sa', 'PART'), (b'sudlay', 'NOUN')]</t>
         </is>
       </c>
       <c r="E62" t="n">
         <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G62" t="n">
         <v>1</v>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>pitiless</t>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>to have unkempt hair</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bibingkang liki</t>
+          <t>gilawog sa tirong</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ang mga bata nagkatawa kay nakita nila ang bibingkang liki sa tindahan.; Ang bibingkang liki kay uso kaayo sa mga binuang ug katawa sa mga barkada.; Si Pedro nagpakatawa sa mga barkada gamit ang bibingkang liki nga istorya.; Ang mga istorya bahin sa bibingkang liki kasagaran makapakatawa sa tanan.; Ang mga binuang sa bibingkang liki kay naghatag ug daghang kalipay sa grupo.</t>
+          <t>Si Pedro gilawog sa tirong sa iyang kauban, maong nasakpan sa ilang boss.; Ang iyang amiga gilawog sa tirong, maong nahimong scapegoat sa problema.; Si Maria gilawog sa tirong sa iyang mga kauban sa trabaho.; Ang mga tawo nga gilawog sa tirong kasagaran mag-antos sa mga consequences.; Si Juan gilawog sa tirong, bisan wala siya naghimo sa sayop.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>(humorous, idiomatic) the female genitalia; the vulva or vagina</t>
+          <t xml:space="preserve"> to endanger someone especially on purpose,  to betray someone,  to throw under the bus</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>[(b'bibingkang', 'NOUN'), (b'liki', 'VERB')]</t>
+          <t>[(b'gilawog', 'VERB'), (b'sa', 'PART'), (b'tirong', 'NOUN')]</t>
         </is>
       </c>
       <c r="E63" t="n">
         <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" t="n">
         <v>1</v>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>the female genitalia</t>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>to endanger someone especially on purpose</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>buak ang pakwan</t>
+          <t>giluto sa kaugalingong mantika</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Sa ilang honeymoon, buak ang pakwan ni Maria ug Pedro.; Si Ana naghulat nga buak ang pakwan sa iyang first night sa kasal.; Ang buak ang pakwan nga experience kasagaran memorable para sa magtiayon.; Si Juan ug Maria nag-istorya bahin sa ilang buak ang pakwan nga kasinatian.; Ang mga magtiayon kasagaran maghulat nga buak ang pakwan human sa ilang kasal.</t>
+          <t>Si Pedro giluto sa kaugalingong mantika sa iyang mga sala.; Ang iyang kauban giluto sa kaugalingong mantika tungod sa iyang binuhatan.; Si Maria giluto sa kaugalingong mantika sa iyang mga desisyon.; Ang mga tawo nga magbuhat ug dautan kasagaran giluto sa kaugalingong mantika.; Si Juan giluto sa kaugalingong mantika, kay nagpadayon sa iyang sayop.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve"> to pop the cherry (lose ones virginity)</t>
+          <t xml:space="preserve"> to dig one's own grave</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>[(b'buak', 'ADJ'), (b'ang', 'DET'), (b'pakwan', 'NOUN')]</t>
+          <t>[(b'giluto', 'VERB'), (b'sa', 'PART'), (b'kaugalingong', 'OTH'), (b'mantika', 'NOUN')]</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64" t="n">
         <v>1</v>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>to pop the cherry</t>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>to dig one's own grave</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>buhi pay ginamos</t>
+          <t>giprito sa kaugalingong mantika</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Si Lito buhi pay ginamos, wala na’y paglaom sa iyang kahimtang.; Ang mga tawo nga buhi pay ginamos kasagaran naglisod sa kinabuhi.; Si Juan buhi pay ginamos, walay klaro nga padulngan.; Ang iyang negosyo buhi pay ginamos, halos wala na gyud kita.; Si Pedro buhi pay ginamos, permi lang mag-antos sa iyang sitwasyon.</t>
+          <t>Si Ana giprito sa kaugalingong mantika tungod sa iyang mga aksyon.; Ang mga tao nga magbuhat ug dautan kasagaran giprito sa kaugalingong mantika.; Si Pedro giprito sa kaugalingong mantika sa iyang mga desisyon.; Ang iyang kauban giprito sa kaugalingong mantika sa iyang mga sala.; Si Juan giprito sa kaugalingong mantika, kay nagpadayon sa iyang sayop.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve"> dead as a doornail, undoubtedly dead</t>
+          <t>Alternative form of giluto sa kaugalingong mantika</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>[(b'buhi', 'ADJ'), (b'pay', 'OTH'), (b'ginamos', 'VERB')]</t>
+          <t>[(b'giprito', 'VERB'), (b'sa', 'PART'), (b'kaugalingong', 'OTH'), (b'mantika', 'NOUN')]</t>
         </is>
       </c>
       <c r="E65" t="n">
         <v>1</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65" t="n">
         <v>1</v>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>dead as a doornail</t>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Alternative form of giluto sa kaugalingong mantika</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>bukad og ngabil</t>
+          <t>gisulod sa bulsa</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ang iyang amiga bukad og ngabil, pirmi lang magyawyaw ug wala’y hunong.; Si Juan bukad og ngabil, bisan unsa nga istorya, pirmi lang magsige ug sulti.; Ang mga tao nga bukad og ngabil kasagaran dili maayo magsekreto.; Si Pedro bukad og ngabil, bisan unsa pa nga sekreto, isulti gyud.; Ang iyang kauban bukad og ngabil, bisan unsa nga balita, pirmi lang magpaabot.</t>
+          <t>Si Juan gisulod sa bulsa sa iyang kauban, maong nawala ang iyang kwarta.; Ang iyang kauban gisulod sa bulsa sa ilang boss, maong napromote siya.; Si Pedro gisulod sa bulsa sa mga sindikato, maong naglisod siya karon.; Ang mga tawo nga masaligan kasagaran dili gisulod sa bulsa.; Si Maria gisulod sa bulsa, maong nag-antos siya sa iyang mga desisyon.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve"> thick-lipped; having a thick lip</t>
+          <t>to trick, to beguile; to deceive, to put one over</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>[(b'bukad', 'VERB'), (b'og', 'CONJ'), (b'ngabil', 'NOUN')]</t>
+          <t>[(b'gisulod', 'VERB'), (b'sa', 'PART'), (b'bulsa', 'NOUN')]</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -3216,38 +3242,36 @@
       <c r="G66" t="n">
         <v>1</v>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>thick-lipped</t>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="n">
+        <v>1</v>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>to trick</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>bukhad og palad</t>
+          <t>gwapa kon magtalikod</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Si Ana bukhad og palad, pirmi lang maghatag bisan sa mga dili kaila.; Ang mga tao nga bukhad og palad kasagaran daghan ug mga amigo.; Si Juan bukhad og palad, bisan sa iyang kalisod, pirmi lang magtabang.; Ang iyang pamilya bukhad og palad, maong daghan ang nagmahal kanila.; Ang mga tawo nga bukhad og palad kasagaran masinabtanon ug mapinanggaon.</t>
+          <t>Si Ana gwapa kon magtalikod, pero pagtan-aw sa iyang nawong, lahi gyud diay.; Ang iyang kauban sa trabaho gwapa kon magtalikod, pero pag-atubang, dili na diay.; Si Maria pirmi lang ginatawgon nga gwapa kon magtalikod sa iyang mga amigo.; Ang mga tao nga gwapa kon magtalikod kasagaran maulaw kung mag-atubang.; Si Pedro pirmi lang magbuot-buot ug sulti nga gwapa kon magtalikod.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve"> generous
-Synonyms: manggihatagon, mahatagon</t>
+          <t>(idiomatic, of a person) pretty to look at from behind, as if good-looking but actually has an ugly face; a butterface</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>[(b'bukhad', 'VERB'), (b'og', 'CONJ'), (b'palad', 'NOUN')]</t>
+          <t>[(b'gwapa', 'ADJ'), (b'kon', 'CONJ'), (b'magtalikod', 'VERB')]</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -3259,38 +3283,36 @@
       <c r="G67" t="n">
         <v>1</v>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>generous
-Synonyms: manggihatagon</t>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>pretty to look at from behind</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>buotan ra og matulog</t>
+          <t>gwapo kon magtalikod</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Si Pedro buotan ra og matulog, kay pirmi lang magbinuang sa klase.; Ang iyang anak buotan ra og matulog, kay pirmi lang mangaway sa mga silingan.; Si Juan buotan ra og matulog, kay dili gyud mahimutang kung magmata.; Ang mga bata nga buotan ra og matulog kasagaran magdala ug kasamok sa balay.; Si Ana buotan ra og matulog, kay pirmi lang magbinuang sa iyang mga igsoon.</t>
+          <t>Si Juan gwapo kon magtalikod, pero dili na kaayo pag-atubang.; Ang iyang amigo gwapo kon magtalikod, pero bati diay pagtan-aw sa iyang nawong.; Si Pedro pirmi lang ginatawgon nga gwapo kon magtalikod sa iyang barkada.; Ang mga tao nga gwapo kon magtalikod kasagaran dili magdugay sa ilang relasyon.; Si Maria pirmi lang magbuot-buot ug sulti nga gwapo kon magtalikod.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve"> mischievous,  a troublemaker</t>
+          <t>(of a person) pretty to look at from behind, as if good-looking but actually has an ugly face</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>[(b'buotan', 'ADJ'), (b'ra', 'ADV'), (b'og', 'CONJ'), (b'matulog', 'VERB')]</t>
+          <t>[(b'gwapo', 'ADJ'), (b'kon', 'CONJ'), (b'magtalikod', 'VERB')]</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -3302,79 +3324,77 @@
       <c r="G68" t="n">
         <v>1</v>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>mischievous</t>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>pretty to look at from behind</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Chona Mae</t>
+          <t>habwa ang kinaon</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Si Chona Mae pirmi lang magbinuang sa eskwelahan.; Ang mga kauban ni Chona Mae kasagaran magkatawa sa iyang mga kalaki.; Si Pedro nagbuot-buot nga tawgon si Ana ug Chona Mae.; Ang mga bata nga nagdula sa park pirmi lang mag-Chona Mae.; Si Juan nagpaka-Chona Mae kay gusto niya magpatawa sa iyang mga amigo.</t>
+          <t>Si Juan habwa ang kinaon pagkalibang tungod sa hilab.; Ang iyang amiga naghabwa ang kinaon kay nasubraan ug kaon.; Si Pedro naghabwa ang kinaon kay nasuka.; Ang mga tawo nga magkaon ug daghan kasagaran maghabwa ang kinaon pagkalibang.; Si Maria naghabwa ang kinaon kay nagkalibanga.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>(humorous) tsunami!</t>
+          <t xml:space="preserve"> to vomit; puke one's guts out</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>[(b'Chona', 'VERB'), (b'Mae', 'NOUN')]</t>
+          <t>[(b'habwa', 'VERB'), (b'ang', 'DET'), (b'kinaon', 'VERB')]</t>
         </is>
       </c>
       <c r="E69" t="n">
         <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
         <v>1</v>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>tsunami!</t>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>to vomit</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>dawat limpyo</t>
+          <t>hangyo kabayo</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Si Juan dawat limpyo lang pirmi, dili man lang mutabang sa trabaho.; Ang iyang kauban sa balay dawat limpyo, pirmi lang mag-abot sa oras sa kaon.; Si Pedro dawat limpyo, bisan unsa na lang ang ipaabot nga libre.; Ang mga tawo nga dawat limpyo kasagaran dili gusto magtrabaho para sa ilang gusto.; Si Maria dawat limpyo, pirmi lang maghuwat sa grasya nga walay gibuhat.</t>
+          <t>Si Juan hangyo kabayo, maong nakuha niya ang diskwento.; Ang iyang amiga hangyo kabayo, bisan unsa nga butang iyang makuha.; Si Pedro hangyo kabayo, maong naangkon niya ang iyang gusto.; Ang mga tawo nga hangyo kabayo kasagaran magmalampuson sa ilang mga plano.; Si Maria hangyo kabayo, maong walay makatanggi sa iyang mga pangutana.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve"> one who does not contribute or pay appropriately; a freeloader, to accomplish a task without much effort but with much dependence on or assistance from other people, to freeload, to ride on someone's coattails</t>
+          <t>a shrewd way of acquiring something</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>[(b'dawat', 'VERB'), (b'limpyo', 'OTH')]</t>
+          <t>[(b'hangyo', 'VERB'), (b'kabayo', 'NOUN')]</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -3386,37 +3406,36 @@
       <c r="G70" t="n">
         <v>1</v>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>one who does not contribute or pay appropriately</t>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>a shrewd way of acquiring something</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>dili madala og rosaryo</t>
+          <t>hangyo lubo</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ang iyang problema dili madala og rosaryo, kinahanglan gyud ug aksyon.; Si Pedro nag-atubang sa mga pagsulay nga dili madala og rosaryo.; Ang mga tawo nga naa sa kalisod kasagaran dili madala og rosaryo ilang mga problema.; Si Maria nag-antos sa mga butang nga dili madala og rosaryo.; Ang ilang sitwasyon sa negosyo dili madala og rosaryo, kinahanglan ug solusyon.</t>
+          <t>Si Ana hangyo lubo, maong nakuha niya ang iyang gusto.; Ang iyang kauban hangyo lubo, bisan unsa nga butang iyang makuha.; Si Pedro hangyo lubo, maong naangkon niya ang iyang gipangayo.; Ang mga tawo nga hangyo lubo kasagaran magmalampuson sa ilang mga plano.; Si Maria hangyo lubo, maong walay makatanggi sa iyang mga pangutana.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve"> an utterly hopeless situation</t>
+          <t xml:space="preserve"> a request made in such a way it cannot be turned down</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>[(b'dili', 'ADV'), (b'madala', 'VERB'), (b'og', 'CONJ'), (b'rosaryo', 'NOUN')]</t>
+          <t>[(b'hangyo', 'VERB'), (b'lubo', 'VERB')]</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -3428,37 +3447,36 @@
       <c r="G71" t="n">
         <v>1</v>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>an utterly hopeless situation</t>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>a request made in such a way it cannot be turned down</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>dili makaon og iro</t>
+          <t>hatod og lubong</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ang iyang batasan dili makaon og iro, maong walay ganahan makighangyo niya.; Si Juan dili makaon og iro, kay pirmi lang maghimo ug gubot.; Ang mga tawo nga dili makaon og iro kasagaran walay respeto sa uban.; Si Maria dili makaon og iro, bisan unsa pa nga istorya, walay muuban niya.; Ang iyang batasan kay dili makaon og iro, maong nag-inusara siya pirmi.</t>
+          <t>Si Juan hatod og lubong sa iyang paryente nga namatay.; Ang mga tawo nga hatod og lubong kasagaran nagpakita ug respeto sa namatay.; Si Pedro hatod og lubong sa iyang kauban sa trabaho.; Ang mga kauban sa barangay naghatod og lubong sa ilang lider.; Si Maria hatod og lubong sa iyang silingan nga namatay.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve"> appalling, revolting, inciting disgust,  a despicable person, a piece of shit</t>
+          <t xml:space="preserve"> to attend a funeral or memorial service</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>[(b'dili', 'ADV'), (b'makaon', 'VERB'), (b'og', 'CONJ'), (b'iro', 'NOUN')]</t>
+          <t>[(b'hatod', 'VERB'), (b'og', 'CONJ'), (b'lubong', 'VERB')]</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -3470,37 +3488,36 @@
       <c r="G72" t="n">
         <v>1</v>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>appalling</t>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>to attend a funeral or memorial service</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>dugay pay manguros</t>
+          <t>hatod og patay</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ang iyang trabaho dugay pay manguros, pirmi lang maghinay-hinay.; Si Juan dugay pay manguros kung magtrabaho sa opisina.; Ang mga tawo nga dugay pay manguros kasagaran maglisod sa ilang mga deadline.; Si Pedro dugay pay manguros, bisan unsa nga butang, hinay kaayo mahuman.; Ang iyang proyekto dugay pay manguros, walay klaro nga mahuman.</t>
+          <t>Si Juan hatod og patay sa iyang paryente nga namatay.; Ang mga tawo nga hatod og patay kasagaran nagpakita ug respeto sa namatay.; Si Pedro hatod og patay sa iyang kauban sa trabaho.; Ang mga kauban sa barangay naghatod og patay sa ilang lider.; Si Maria hatod og patay sa iyang silingan nga namatay.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve"> a piece of cake, cakewalk</t>
+          <t xml:space="preserve"> to attend a funeral or memorial service</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>[(b'dugay', 'ADJ'), (b'pay', 'OTH'), (b'manguros', 'VERB')]</t>
+          <t>[(b'hatod', 'VERB'), (b'og', 'CONJ'), (b'patay', 'VERB')]</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -3512,37 +3529,36 @@
       <c r="G73" t="n">
         <v>1</v>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>a piece of cake</t>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>to attend a funeral or memorial service</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>dula og panit</t>
+          <t>higda sa lubi</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Si Pedro pirmi lang mag-dula og panit, bisan walay buhaton nga maayo.; Ang mga bata nga dula og panit kasagaran wala’y klaro nga padulngan.; Si Juan dula og panit, pirmi lang magtambay ug magbuot-buot.; Ang iyang barkada kay dula og panit, bisan unsa na lang nga kalipay ang gihimo.; Si Maria nagbuot-buot kay gusto siya magdula og panit pirmi.</t>
+          <t>Si Pedro pirmi lang higda sa lubi kung mag-inom.; Ang iyang mga kauban pirmi lang mag-higda sa lubi kung mag-party.; Si Juan higda sa lubi, pirmi lang maghubog-hubog.; Ang mga tawo nga pirmi lang mag-higda sa lubi kasagaran maglisod sa kinabuhi.; Si Maria nasuko kay si Pedro pirmi lang mag-higda sa lubi.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve"> to masturbate, jack off, to fap</t>
+          <t xml:space="preserve"> to be wasted (very drunk)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>[(b'dula', 'VERB'), (b'og', 'CONJ'), (b'panit', 'NOUN')]</t>
+          <t>[(b'higda', 'VERB'), (b'sa', 'PART'), (b'lubi', 'NOUN')]</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -3554,37 +3570,36 @@
       <c r="G74" t="n">
         <v>1</v>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>to masturbate</t>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>to be wasted</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>duwa og panit</t>
+          <t>hinaw</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Si Juan pirmi lang mag-duwa og panit sa iyang kwarto.; Ang iyang mga kauban sa trabaho pirmi lang magbinuang ug magduwa og panit.; Si Pedro walay laing gihimo kundi magduwa og panit pirmi.; Ang mga bata nga nagdula sa internet pirmi lang magduwa og panit.; Si Maria naglagot kay si Juan pirmi lang magduwa og panit bisan kinahanglanon siya.</t>
+          <t>Si Pedro naghinaw sa iyang responsibilidad pagkahuman sa proyekto.; Ang iyang kauban naghinaw sa problema kay dili siya gusto maapil.; Si Juan naghinaw sa iyang sala sa trabaho.; Ang mga tawo nga naghinaw sa ilang responsibilidad kasagaran maglisod sa pag-uli sa ilang kasal-anan.; Si Maria naghinaw sa iyang obligasyon sa pamilya.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>(slang, idiomatic) to masturbate</t>
+          <t>to wash one's hands or another's,  to wash one's hands of; to absolve oneself of responsibility or future blame for; to refuse to have any further involvement with, washing of one's hands or feet</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>[(b'duwa', 'VERB'), (b'og', 'CONJ'), (b'panit', 'NOUN')]</t>
+          <t>[(b'hinaw', 'VERB')]</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -3596,79 +3611,77 @@
       <c r="G75" t="n">
         <v>1</v>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>to masturbate</t>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>to wash one's hands or another's</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>gadalag ulan</t>
+          <t>hunaw</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Si Juan kay gadalag ulan, maong daghan ang naglikay niya.; Ang iyang amigo gadalag ulan, maong dili siya ganahan kauban.; Si Pedro gadalag ulan, bisan unsa pa nga sitwasyon.; Ang mga tawo nga gadalag ulan kasagaran naglisod sa pagdawat sa uban.; Si Maria gadalag ulan, maong pirmi siya nag-inusara.</t>
+          <t>Si Pedro naghunaw sa iyang mga sayop kay dili siya gusto ma-blame.; Ang iyang kauban naghunaw sa mga problema aron dili siya maapil.; Si Juan naghunaw sa iyang responsibilidad sa trabaho.; Ang mga tawo nga maghunaw sa ilang obligasyon kasagaran maglisod sa ilang relasyon sa uban.; Si Maria naghunaw sa iyang mga sala aron dili siya mahatagan ug parusa.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve"> a male homosexual</t>
+          <t>to wash one's hands or another's,  to wash one's hands of; to absolve oneself of responsibility or future blame for; to refuse to have any further involvement with</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>[(b'gadalag', 'ADJ'), (b'ulan', 'NOUN')]</t>
+          <t>[(b'hunaw', 'VERB')]</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G76" t="n">
         <v>1</v>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>a male homosexual</t>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>to wash one's hands or another's</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>gadalag uwan</t>
+          <t>igputi sa uwak</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Si Lito gadalag uwan, pero gihigugma gihapon sa iyang pamilya.; Ang iyang silingan gadalag uwan, pero respetado gihapon sa ilang lugar.; Si Juan gadalag uwan, bisan unsa pa nga istorya, wala magpailalom.; Ang mga tao nga gadalag uwan kasagaran adunay mga pagsulay sa kinabuhi.; Si Maria gadalag uwan, pero walay mopauli sa iyang pagkatawo.</t>
+          <t>Mahitabo lang na igputi sa uwak, dili gyud na matinuod.; Ang iyang pangandoy mahimong realidad igputi sa uwak pa.; Si Pedro musugot igputi sa uwak pa, dili gyud karon.; Ang mga tawo magduda sa iyang mga plano, ingnon nila nga igputi sa uwak pa na matuman.; Si Maria mutuman sa iyang sugo igputi sa uwak pa, dili gyud karon.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve"> a male homosexual</t>
+          <t>never; not in this lifetime or a time in the unforeseeably distant future; not a chance, when pigs fly</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>[(b'gadalag', 'ADJ'), (b'uwan', 'ADJ')]</t>
+          <t>[(b'igputi', 'ADJ'), (b'sa', 'PART'), (b'uwak', 'NOUN')]</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -3678,291 +3691,308 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>1</v>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="n">
+        <v>1</v>
+      </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>a male homosexual</t>
+          <t>igputi</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>never</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>gi-indian</t>
+          <t>ikasuga ang ihi</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Si Pedro gi-indian sa iyang uyab sa ilang sabot nga date.; Ang mga estudyante na gi-indian sa ilang maestra sa klase karon.; Si Maria nasuko kay gi-indian siya sa iyang amigo.; Ang iyang kauban sa trabaho gi-indian siya sa ilang meeting.; Si Juan gi-indian sa iyang kliyente sa ilang appointment.</t>
+          <t>Si Ana ikasuga ang ihi sa iyang kaanyag.; Ang iyang amiga ikasuga ang ihi sa iyang hitsura.; Si Pedro ikasuga ang ihi sa iyang pagkagwapo.; Ang mga tawo nga ikasuga ang ihi kasagaran daghan ug mga admirers.; Si Maria ikasuga ang ihi sa iyang pagkamahinhin.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>to fail to meet an appointment intentionally, to no-show</t>
+          <t xml:space="preserve"> for a woman to be very beautiful</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>[(b'gi-indian', 'VERB')]</t>
+          <t>[(b'ikasuga', 'NOUN'), (b'ang', 'DET'), (b'ihi', 'NOUN')]</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F78" t="n">
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="n">
+        <v>1</v>
+      </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>to fail to meet an appointment intentionally</t>
+          <t>ikasuga</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>for a woman to be very beautiful</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>gibati og kaanyag</t>
+          <t>kakha tuka</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Si Ana gibati og kaanyag, maong pirmi siya nagbuot-buot.; Ang mga tawo nga gibati og kaanyag kasagaran magdala ug samok sa grupo.; Si Maria gibati og kaanyag, bisan unsa nga sugo, dili gyud mutuman.; Ang iyang amiga gibati og kaanyag, maong pirmi mag-away sa iyang bana.; Si Pedro gibati og kaanyag, maong pirmi magbuot sa ilang opisina.</t>
+          <t>Si Pedro kakha tuka, walay savings ug pirmi lang magkaproblema sa kwarta.; Ang ilang pamilya kakha tuka, pirmi lang maglisod sa pagkaon.; Si Maria nagkinabuhi nga kakha tuka, walay nahabilin nga kwarta.; Ang mga tawo nga kakha tuka kasagaran maglisod sa kinabuhi.; Si Juan pirmi lang kakha tuka, walay nahabilin nga budget.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve"> prima donna; entitled person,  entitled</t>
+          <t>hand-to-mouth; involving immediate consumption (especially of food) with no provision for the future; having barely enough to survive, being close to poverty, to live hand-to-mouth</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>[(b'gibati', 'NOUN'), (b'og', 'CONJ'), (b'kaanyag', 'ADV')]</t>
+          <t>[(b'kakha', 'VERB'), (b'tuka', 'VERB')]</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G79" t="n">
         <v>1</v>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>prima donna</t>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="n">
+        <v>1</v>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>hand-to-mouth</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>gigukod sa plansa</t>
+          <t>kapugngan pa ang baha, dili ang biga</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Si Juan pirmi lang gigukod sa plansa, kay dili siya ganahan magplantsa.; Ang iyang sinina pirmi lang gigukod sa plansa, maong bati tan-awon.; Si Pedro pirmi lang gigukod sa plansa, bisan unsa nga sinina dili mahimutang.; Ang mga tawo nga gigukod sa plansa kasagaran dili mag-atiman sa ilang kaugalingon.; Si Maria gigukod sa plansa, bisan unsa nga okasyon, dili gyud magplantsa.</t>
+          <t>Si Pedro dili mapugngan sa iyang gusto, kapugngan pa ang baha, dili ang biga.; Ang iyang determinasyon dili mapugngan, kapugngan pa ang baha, dili ang biga.; Si Juan adunay grabe kaayo nga pagnanasa, kapugngan pa ang baha, dili ang biga.; Ang iyang kalagot dili mapugngan, kapugngan pa ang baha, dili ang biga.; Si Maria adunay dakong pangandoy nga dili mapugngan, kapugngan pa ang baha, dili ang biga.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve"> someone who's wearing wrinkly clothes</t>
+          <t>unstoppable</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>[(b'gigukod', 'VERB'), (b'sa', 'PART'), (b'plansa', 'NOUN')]</t>
+          <t>[(b'kapugngan', 'ADJ'), (b'pa', 'ADV'), (b'ang', 'DET'), (b'baha', 'NOUN'), (b',', 'SYM'), (b'dili', 'ADV'), (b'ang', 'DET'), (b'biga', 'NOUN')]</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
         <v>1</v>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="n">
+        <v>1</v>
+      </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>someone who's wearing wrinkly clothes</t>
+          <t>kapugngan</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>unstoppable</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>gigukod sa sudlay</t>
+          <t>kasab-itag bukag ang simod</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Si Ana pirmi lang gigukod sa sudlay, kay dili siya ganahan mag-comb sa iyang buhok.; Ang iyang buhok pirmi lang gigukod sa sudlay, maong bati kaayo tan-awon.; Si Pedro pirmi lang gigukod sa sudlay, bisan unsa nga event, dili mag-comb.; Ang mga tawo nga gigukod sa sudlay kasagaran dili mag-atiman sa ilang buhok.; Si Juan gigukod sa sudlay, bisan unsa nga party, dili gyud mag-comb.</t>
+          <t>Si Ana pirmi lang kasab-itag bukag ang simod kung naay problema.; Ang iyang anak pirmi lang kasab-itag bukag ang simod kung walay makuha nga gusto.; Si Pedro pirmi lang kasab-itag bukag ang simod kung naa'y magbuot kaniya.; Ang mga tawo nga kasab-itag bukag ang simod kasagaran dili ganahan makig-istorya.; Si Maria pirmi lang kasab-itag bukag ang simod kung naa'y maglagot kaniya.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve"> to have unkempt hair</t>
+          <t xml:space="preserve"> sullen; having a brooding ill temper; sulky</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>[(b'gigukod', 'VERB'), (b'sa', 'PART'), (b'sudlay', 'NOUN')]</t>
+          <t>[(b'kasab-itag', 'OTH'), (b'bukag', 'NOUN'), (b'ang', 'DET'), (b'simod', 'NOUN')]</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>1</v>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="n">
+        <v>1</v>
+      </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>to have unkempt hair</t>
+          <t>kasab-itan</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>sullen</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>gilawog sa tirong</t>
+          <t>katagakon ang mata</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Si Pedro gilawog sa tirong sa iyang kauban, maong nasakpan sa ilang boss.; Ang iyang amiga gilawog sa tirong, maong nahimong scapegoat sa problema.; Si Maria gilawog sa tirong sa iyang mga kauban sa trabaho.; Ang mga tawo nga gilawog sa tirong kasagaran mag-antos sa mga consequences.; Si Juan gilawog sa tirong, bisan wala siya naghimo sa sayop.</t>
+          <t>Si Juan katagakon ang mata human sa taas nga gabii.; Ang iyang anak katagakon ang mata human magbilar sa pagduwa sa computer.; Si Pedro katagakon ang mata human sa taas nga trabaho sa opisina.; Ang mga tawo nga katagakon ang mata kasagaran dili makamata ug sayo.; Si Maria katagakon ang mata human sa pila ka gabii nga trabaho.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve"> to endanger someone especially on purpose,  to betray someone,  to throw under the bus</t>
+          <t xml:space="preserve"> sleepy, drowsy</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>[(b'gilawog', 'VERB'), (b'sa', 'PART'), (b'tirong', 'NOUN')]</t>
+          <t>[(b'katagakon', 'NOUN'), (b'ang', 'DET'), (b'mata', 'VERB')]</t>
         </is>
       </c>
       <c r="E82" t="n">
         <v>1</v>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
         <v>1</v>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="n">
+        <v>1</v>
+      </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>to endanger someone especially on purpose</t>
+          <t>katagakon</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>sleepy</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>giluto sa kaugalingong mantika</t>
+          <t>kilatan</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Si Pedro giluto sa kaugalingong mantika sa iyang mga sala.; Ang iyang kauban giluto sa kaugalingong mantika tungod sa iyang binuhatan.; Si Maria giluto sa kaugalingong mantika sa iyang mga desisyon.; Ang mga tawo nga magbuhat ug dautan kasagaran giluto sa kaugalingong mantika.; Si Juan giluto sa kaugalingong mantika, kay nagpadayon sa iyang sayop.</t>
+          <t>Si Pedro kilatan kay nangawat siya sa tindahan.; Ang iyang amigo kilatan kay nagbinuang sa iyang ginikanan.; Si Juan kilatan sa iyang mga kauban kay nagsumbong sa boss.; Ang mga tawo nga kilatan kasagaran magbasol sa ilang binuhatan.; Si Maria kilatan kay wala mutuman sa sugo sa iyang inahan.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve"> to dig one's own grave</t>
+          <t>to be struck by lightning, to be exacted punishment (see usage notes), (idiomatic, of food) to disappear off the plate fast</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>[(b'giluto', 'VERB'), (b'sa', 'PART'), (b'kaugalingong', 'OTH'), (b'mantika', 'NOUN')]</t>
+          <t>[(b'kilatan', 'NOUN')]</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F83" t="n">
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="n">
+        <v>1</v>
+      </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>to dig one's own grave</t>
+          <t>kilatan</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>to be struck by lightning</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>giprito sa kaugalingong mantika</t>
+          <t>kirig</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Si Ana giprito sa kaugalingong mantika tungod sa iyang mga aksyon.; Ang mga tao nga magbuhat ug dautan kasagaran giprito sa kaugalingong mantika.; Si Pedro giprito sa kaugalingong mantika sa iyang mga desisyon.; Ang iyang kauban giprito sa kaugalingong mantika sa iyang mga sala.; Si Juan giprito sa kaugalingong mantika, kay nagpadayon sa iyang sayop.</t>
+          <t>Si Ana kirig sa iyang sakit nga epilepsy.; Ang iyang lola kirig tungod sa iyang katigulangon.; Si Pedro kirig human nalipong sa init.; Ang mga tawo nga naay sakit kasagaran kirig kung dili mag-amping.; Si Juan kirig sa kahadlok pagkakita sa aksidente.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Alternative form of giluto sa kaugalingong mantika</t>
+          <t>to convulse, to have a seizure, to seize,  to die</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>[(b'giprito', 'VERB'), (b'sa', 'PART'), (b'kaugalingong', 'OTH'), (b'mantika', 'NOUN')]</t>
+          <t>[(b'kirig', 'VERB')]</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -3974,37 +4004,36 @@
       <c r="G84" t="n">
         <v>1</v>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>Alternative form of giluto sa kaugalingong mantika</t>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="n">
+        <v>1</v>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>to convulse</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>gisulod sa bulsa</t>
+          <t>kulang sa dukol</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Si Juan gisulod sa bulsa sa iyang kauban, maong nawala ang iyang kwarta.; Ang iyang kauban gisulod sa bulsa sa ilang boss, maong napromote siya.; Si Pedro gisulod sa bulsa sa mga sindikato, maong naglisod siya karon.; Ang mga tawo nga masaligan kasagaran dili gisulod sa bulsa.; Si Maria gisulod sa bulsa, maong nag-antos siya sa iyang mga desisyon.</t>
+          <t>Si Pedro kulang sa dukol, maong pirmi lang magbinuang.; Ang iyang anak kulang sa dukol, dili gyud magtinarong sa pag-eskwela.; Si Juan kulang sa dukol, pirmi lang magtambay sa kanto.; Ang mga tawo nga kulang sa dukol kasagaran maglisod sa pagtrabaho.; Si Maria kulang sa dukol, pirmi lang magbulakbol.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>to trick, to beguile; to deceive, to put one over</t>
+          <t xml:space="preserve"> a stupid person, dunce</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>[(b'gisulod', 'VERB'), (b'sa', 'PART'), (b'bulsa', 'NOUN')]</t>
+          <t>[(b'kulang', 'ADJ'), (b'sa', 'PART'), (b'dukol', 'VERB')]</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -4016,37 +4045,36 @@
       <c r="G85" t="n">
         <v>1</v>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>to trick</t>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="n">
+        <v>1</v>
+      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>a stupid person</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>gwapa kon magtalikod</t>
+          <t>kulang sa tagad</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Si Ana gwapa kon magtalikod, pero pagtan-aw sa iyang nawong, lahi gyud diay.; Ang iyang kauban sa trabaho gwapa kon magtalikod, pero pag-atubang, dili na diay.; Si Maria pirmi lang ginatawgon nga gwapa kon magtalikod sa iyang mga amigo.; Ang mga tao nga gwapa kon magtalikod kasagaran maulaw kung mag-atubang.; Si Pedro pirmi lang magbuot-buot ug sulti nga gwapa kon magtalikod.</t>
+          <t>Si Pedro kulang sa tagad, maong pirmi lang magpakitkit ug magpasikat.; Ang iyang amiga kulang sa tagad, maong pirmi lang mag-agi-agi sa ilang lugar.; Si Juan kulang sa tagad, pirmi lang magpasikat sa mga tao.; Ang mga tawo nga kulang sa tagad kasagaran magbuhat ug dautan para makuha ang attention sa uban.; Si Maria kulang sa tagad, pirmi lang magbinuang aron makuha ang atensyon sa iyang mga kauban.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>(idiomatic, of a person) pretty to look at from behind, as if good-looking but actually has an ugly face; a butterface</t>
+          <t>characteristic of an attention seeker, (often preceded by ang) an attention seeker</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>[(b'gwapa', 'ADJ'), (b'kon', 'CONJ'), (b'magtalikod', 'VERB')]</t>
+          <t>[(b'kulang', 'ADJ'), (b'sa', 'PART'), (b'tagad', 'VERB')]</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -4058,79 +4086,81 @@
       <c r="G86" t="n">
         <v>1</v>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>pretty to look at from behind</t>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="n">
+        <v>1</v>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>characteristic of an attention seeker</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>gwapo kon magtalikod</t>
+          <t>kulban sa kaldero</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Si Juan gwapo kon magtalikod, pero dili na kaayo pag-atubang.; Ang iyang amigo gwapo kon magtalikod, pero bati diay pagtan-aw sa iyang nawong.; Si Pedro pirmi lang ginatawgon nga gwapo kon magtalikod sa iyang barkada.; Ang mga tao nga gwapo kon magtalikod kasagaran dili magdugay sa ilang relasyon.; Si Maria pirmi lang magbuot-buot ug sulti nga gwapo kon magtalikod.</t>
+          <t>Si Juan pirmi lang kulban sa kaldero kung makiglalis sa iyang kauban.; Ang iyang amigo kulban sa kaldero kung naa sa meeting.; Si Pedro pirmi lang kulban sa kaldero kung mag-istorya sa iyang boss.; Ang mga tawo nga kulban sa kaldero kasagaran dili makapanalipod sa ilang kaugalingon.; Si Maria pirmi lang kulban sa kaldero kung naa sa public speaking.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>(of a person) pretty to look at from behind, as if good-looking but actually has an ugly face</t>
+          <t xml:space="preserve"> to silence dismissively; to prevent from talking further with a shutdown</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>[(b'gwapo', 'ADJ'), (b'kon', 'CONJ'), (b'magtalikod', 'VERB')]</t>
+          <t>[(b'kulban', 'ADJ'), (b'sa', 'PART'), (b'kaldero', 'NOUN')]</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F87" t="n">
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="n">
+        <v>1</v>
+      </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>pretty to look at from behind</t>
+          <t>kulban</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>to silence dismissively</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>habwa ang kinaon</t>
+          <t>kuskos balungos</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Si Juan habwa ang kinaon pagkalibang tungod sa hilab.; Ang iyang amiga naghabwa ang kinaon kay nasubraan ug kaon.; Si Pedro naghabwa ang kinaon kay nasuka.; Ang mga tawo nga magkaon ug daghan kasagaran maghabwa ang kinaon pagkalibang.; Si Maria naghabwa ang kinaon kay nagkalibanga.</t>
+          <t>Si Pedro pirmi lang kuskos balungos sa iyang trabaho.; Ang iyang anak kuskos balungos sa eskwela, bisan walay hinungdan.; Si Maria kuskos balungos sa balay, walay undang ang trabaho.; Ang mga tawo nga kuskos balungos kasagaran maglisod ug kapahulayan.; Si Juan pirmi lang kuskos balungos sa mga problema nga walay solusyon.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve"> to vomit; puke one's guts out</t>
+          <t xml:space="preserve"> fuss; excessive activity, worry, bother, or talk about something</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>[(b'habwa', 'VERB'), (b'ang', 'DET'), (b'kinaon', 'VERB')]</t>
+          <t>[(b'kuskos', 'VERB'), (b'balungos', 'NOUN')]</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -4142,795 +4172,793 @@
       <c r="G88" t="n">
         <v>1</v>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>to vomit</t>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>fuss</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>halinon og aping</t>
+          <t>kuskos-balungos</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Si Ana halinon og aping, daghan kaayo siya ug mga manliligaw.; Ang mga artista kasagaran halinon og aping tungod sa ilang hitsura.; Si Pedro halinon og aping, daghan kaayo siya ug mga fans.; Ang mga tawo nga halinon og aping kasagaran sikat ug ilado.; Si Maria halinon og aping, daghan kaayo siya ug admirers.</t>
+          <t>Si Ana pirmi lang kuskos-balungos kung naay buhaton nga dili siya ganahan.; Ang iyang amahan kuskos-balungos sa mga butang nga wala'y hinungdan.; Si Pedro kuskos-balungos pirmi, bisan gamay nga problema.; Ang mga tawo nga kuskos-balungos kasagaran magpaluya sa ilang mga kauban.; Si Maria pirmi lang kuskos-balungos bisan unsa nga buhaton.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> extremely good-looking</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>[(b'halinon', 'VERB'), (b'og', 'CONJ'), (b'aping', 'NOUN')]</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>1</v>
-      </c>
-      <c r="F89" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" t="n">
-        <v>1</v>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>extremely good-looking</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>hangyo kabayo</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Si Juan hangyo kabayo, maong nakuha niya ang diskwento.; Ang iyang amiga hangyo kabayo, bisan unsa nga butang iyang makuha.; Si Pedro hangyo kabayo, maong naangkon niya ang iyang gusto.; Ang mga tawo nga hangyo kabayo kasagaran magmalampuson sa ilang mga plano.; Si Maria hangyo kabayo, maong walay makatanggi sa iyang mga pangutana.</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>a shrewd way of acquiring something</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>[(b'hangyo', 'VERB'), (b'kabayo', 'NOUN')]</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
-        <v>1</v>
-      </c>
-      <c r="F90" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" t="n">
-        <v>1</v>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>a shrewd way of acquiring something</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>hangyo lubo</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Si Ana hangyo lubo, maong nakuha niya ang iyang gusto.; Ang iyang kauban hangyo lubo, bisan unsa nga butang iyang makuha.; Si Pedro hangyo lubo, maong naangkon niya ang iyang gipangayo.; Ang mga tawo nga hangyo lubo kasagaran magmalampuson sa ilang mga plano.; Si Maria hangyo lubo, maong walay makatanggi sa iyang mga pangutana.</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> a request made in such a way it cannot be turned down</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>[(b'hangyo', 'VERB'), (b'lubo', 'VERB')]</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v>1</v>
-      </c>
-      <c r="F91" t="n">
-        <v>1</v>
-      </c>
-      <c r="G91" t="n">
-        <v>1</v>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>a request made in such a way it cannot be turned down</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>hatod og lubong</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Si Juan hatod og lubong sa iyang paryente nga namatay.; Ang mga tawo nga hatod og lubong kasagaran nagpakita ug respeto sa namatay.; Si Pedro hatod og lubong sa iyang kauban sa trabaho.; Ang mga kauban sa barangay naghatod og lubong sa ilang lider.; Si Maria hatod og lubong sa iyang silingan nga namatay.</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> to attend a funeral or memorial service</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>[(b'hatod', 'VERB'), (b'og', 'CONJ'), (b'lubong', 'VERB')]</t>
-        </is>
-      </c>
-      <c r="E92" t="n">
-        <v>1</v>
-      </c>
-      <c r="F92" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" t="n">
-        <v>1</v>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>to attend a funeral or memorial service</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>hatod og patay</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Si Juan hatod og patay sa iyang paryente nga namatay.; Ang mga tawo nga hatod og patay kasagaran nagpakita ug respeto sa namatay.; Si Pedro hatod og patay sa iyang kauban sa trabaho.; Ang mga kauban sa barangay naghatod og patay sa ilang lider.; Si Maria hatod og patay sa iyang silingan nga namatay.</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> to attend a funeral or memorial service</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>[(b'hatod', 'VERB'), (b'og', 'CONJ'), (b'patay', 'VERB')]</t>
-        </is>
-      </c>
-      <c r="E93" t="n">
-        <v>1</v>
-      </c>
-      <c r="F93" t="n">
-        <v>1</v>
-      </c>
-      <c r="G93" t="n">
-        <v>1</v>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>to attend a funeral or memorial service</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>higda sa lubi</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Si Pedro pirmi lang higda sa lubi kung mag-inom.; Ang iyang mga kauban pirmi lang mag-higda sa lubi kung mag-party.; Si Juan higda sa lubi, pirmi lang maghubog-hubog.; Ang mga tawo nga pirmi lang mag-higda sa lubi kasagaran maglisod sa kinabuhi.; Si Maria nasuko kay si Pedro pirmi lang mag-higda sa lubi.</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> to be wasted (very drunk)</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>[(b'higda', 'VERB'), (b'sa', 'PART'), (b'lubi', 'NOUN')]</t>
-        </is>
-      </c>
-      <c r="E94" t="n">
-        <v>1</v>
-      </c>
-      <c r="F94" t="n">
-        <v>1</v>
-      </c>
-      <c r="G94" t="n">
-        <v>1</v>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>to be wasted</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>hinaw</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Si Pedro naghinaw sa iyang responsibilidad pagkahuman sa proyekto.; Ang iyang kauban naghinaw sa problema kay dili siya gusto maapil.; Si Juan naghinaw sa iyang sala sa trabaho.; Ang mga tawo nga naghinaw sa ilang responsibilidad kasagaran maglisod sa pag-uli sa ilang kasal-anan.; Si Maria naghinaw sa iyang obligasyon sa pamilya.</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>to wash one's hands or another's,  to wash one's hands of; to absolve oneself of responsibility or future blame for; to refuse to have any further involvement with, washing of one's hands or feet</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>[(b'hinaw', 'VERB')]</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>1</v>
-      </c>
-      <c r="F95" t="n">
-        <v>1</v>
-      </c>
-      <c r="G95" t="n">
-        <v>1</v>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>to wash one's hands or another's</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>hugot sa bakos</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Si Ana hugot sa bakos kay gusto niya makatipid para sa future.; Ang iyang pamilya naghugot sa bakos tungod sa financial crisis.; Si Pedro naghugot sa bakos para makaipon ug kwarta.; Ang mga tawo nga naghugot sa bakos kasagaran maglisod sa ilang mga plano.; Si Juan naghugot sa bakos tungod sa daghang gastuhon.</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> to tighten one's belt</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>[(b'hugot', 'ADJ'), (b'sa', 'PART'), (b'bakos', 'NOUN')]</t>
-        </is>
-      </c>
-      <c r="E96" t="n">
-        <v>0</v>
-      </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="n">
-        <v>1</v>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>to tighten one's belt</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>hunaw</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Si Pedro naghunaw sa iyang mga sayop kay dili siya gusto ma-blame.; Ang iyang kauban naghunaw sa mga problema aron dili siya maapil.; Si Juan naghunaw sa iyang responsibilidad sa trabaho.; Ang mga tawo nga maghunaw sa ilang obligasyon kasagaran maglisod sa ilang relasyon sa uban.; Si Maria naghunaw sa iyang mga sala aron dili siya mahatagan ug parusa.</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>to wash one's hands or another's,  to wash one's hands of; to absolve oneself of responsibility or future blame for; to refuse to have any further involvement with</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>[(b'hunaw', 'VERB')]</t>
-        </is>
-      </c>
-      <c r="E97" t="n">
-        <v>1</v>
-      </c>
-      <c r="F97" t="n">
-        <v>1</v>
-      </c>
-      <c r="G97" t="n">
-        <v>1</v>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>to wash one's hands or another's</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>istorya ilalom sa dagat</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Ang giingon ni Pedro istorya ilalom sa dagat, dili gyud matinuod.; Ang iyang pangatarungan kay istorya ilalom sa dagat, walay klaro.; Si Maria pirmi lang maghatag ug istorya ilalom sa dagat kung mag-explain.; Ang mga tawo nga dili tinuod pirmi lang mag-istorya ilalom sa dagat.; Si Juan naglagot kay ang nadungog niya puro istorya ilalom sa dagat.</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> a load of crap, nonsense</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>[(b'istorya', 'NOUN'), (b'ilalom', 'OTH'), (b'sa', 'PART'), (b'dagat', 'NOUN')]</t>
-        </is>
-      </c>
-      <c r="E98" t="n">
-        <v>0</v>
-      </c>
-      <c r="F98" t="n">
-        <v>0</v>
-      </c>
-      <c r="G98" t="n">
-        <v>1</v>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>a load of crap</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>kakha tuka</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Si Pedro kakha tuka, walay savings ug pirmi lang magkaproblema sa kwarta.; Ang ilang pamilya kakha tuka, pirmi lang maglisod sa pagkaon.; Si Maria nagkinabuhi nga kakha tuka, walay nahabilin nga kwarta.; Ang mga tawo nga kakha tuka kasagaran maglisod sa kinabuhi.; Si Juan pirmi lang kakha tuka, walay nahabilin nga budget.</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>hand-to-mouth; involving immediate consumption (especially of food) with no provision for the future; having barely enough to survive, being close to poverty, to live hand-to-mouth</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>[(b'kakha', 'VERB'), (b'tuka', 'VERB')]</t>
-        </is>
-      </c>
-      <c r="E99" t="n">
-        <v>1</v>
-      </c>
-      <c r="F99" t="n">
-        <v>1</v>
-      </c>
-      <c r="G99" t="n">
-        <v>1</v>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>hand-to-mouth</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>kapugngan pa ang baha, dili ang biga</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Si Pedro dili mapugngan sa iyang gusto, kapugngan pa ang baha, dili ang biga.; Ang iyang determinasyon dili mapugngan, kapugngan pa ang baha, dili ang biga.; Si Juan adunay grabe kaayo nga pagnanasa, kapugngan pa ang baha, dili ang biga.; Ang iyang kalagot dili mapugngan, kapugngan pa ang baha, dili ang biga.; Si Maria adunay dakong pangandoy nga dili mapugngan, kapugngan pa ang baha, dili ang biga.</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>unstoppable</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>[(b'kapugngan', 'ADJ'), (b'pa', 'ADV'), (b'ang', 'DET'), (b'baha', 'NOUN'), (b',', 'SYM'), (b'dili', 'ADV'), (b'ang', 'DET'), (b'biga', 'NOUN')]</t>
-        </is>
-      </c>
-      <c r="E100" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" t="n">
-        <v>1</v>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>unstoppable</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>katagakon ang mata</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Si Juan katagakon ang mata human sa taas nga gabii.; Ang iyang anak katagakon ang mata human magbilar sa pagduwa sa computer.; Si Pedro katagakon ang mata human sa taas nga trabaho sa opisina.; Ang mga tawo nga katagakon ang mata kasagaran dili makamata ug sayo.; Si Maria katagakon ang mata human sa pila ka gabii nga trabaho.</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> sleepy, drowsy</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>[(b'katagakon', 'NOUN'), (b'ang', 'DET'), (b'mata', 'VERB')]</t>
-        </is>
-      </c>
-      <c r="E101" t="n">
-        <v>1</v>
-      </c>
-      <c r="F101" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" t="n">
-        <v>1</v>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>sleepy</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>kirig</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Si Ana kirig sa iyang sakit nga epilepsy.; Ang iyang lola kirig tungod sa iyang katigulangon.; Si Pedro kirig human nalipong sa init.; Ang mga tawo nga naay sakit kasagaran kirig kung dili mag-amping.; Si Juan kirig sa kahadlok pagkakita sa aksidente.</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>to convulse, to have a seizure, to seize,  to die</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>[(b'kirig', 'VERB')]</t>
-        </is>
-      </c>
-      <c r="E102" t="n">
-        <v>1</v>
-      </c>
-      <c r="F102" t="n">
-        <v>1</v>
-      </c>
-      <c r="G102" t="n">
-        <v>1</v>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>to convulse</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>kulang sa dukol</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Si Pedro kulang sa dukol, maong pirmi lang magbinuang.; Ang iyang anak kulang sa dukol, dili gyud magtinarong sa pag-eskwela.; Si Juan kulang sa dukol, pirmi lang magtambay sa kanto.; Ang mga tawo nga kulang sa dukol kasagaran maglisod sa pagtrabaho.; Si Maria kulang sa dukol, pirmi lang magbulakbol.</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> a stupid person, dunce</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>[(b'kulang', 'ADJ'), (b'sa', 'PART'), (b'dukol', 'VERB')]</t>
-        </is>
-      </c>
-      <c r="E103" t="n">
-        <v>1</v>
-      </c>
-      <c r="F103" t="n">
-        <v>1</v>
-      </c>
-      <c r="G103" t="n">
-        <v>1</v>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>a stupid person</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>kulang sa tagad</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Si Pedro kulang sa tagad, maong pirmi lang magpakitkit ug magpasikat.; Ang iyang amiga kulang sa tagad, maong pirmi lang mag-agi-agi sa ilang lugar.; Si Juan kulang sa tagad, pirmi lang magpasikat sa mga tao.; Ang mga tawo nga kulang sa tagad kasagaran magbuhat ug dautan para makuha ang attention sa uban.; Si Maria kulang sa tagad, pirmi lang magbinuang aron makuha ang atensyon sa iyang mga kauban.</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>characteristic of an attention seeker, (often preceded by ang) an attention seeker</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>[(b'kulang', 'ADJ'), (b'sa', 'PART'), (b'tagad', 'VERB')]</t>
-        </is>
-      </c>
-      <c r="E104" t="n">
-        <v>1</v>
-      </c>
-      <c r="F104" t="n">
-        <v>1</v>
-      </c>
-      <c r="G104" t="n">
-        <v>1</v>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>characteristic of an attention seeker</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>kuskos balungos</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Si Pedro pirmi lang kuskos balungos sa iyang trabaho.; Ang iyang anak kuskos balungos sa eskwela, bisan walay hinungdan.; Si Maria kuskos balungos sa balay, walay undang ang trabaho.; Ang mga tawo nga kuskos balungos kasagaran maglisod ug kapahulayan.; Si Juan pirmi lang kuskos balungos sa mga problema nga walay solusyon.</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> fuss; excessive activity, worry, bother, or talk about something</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>[(b'kuskos', 'VERB'), (b'balungos', 'NOUN')]</t>
-        </is>
-      </c>
-      <c r="E105" t="n">
-        <v>1</v>
-      </c>
-      <c r="F105" t="n">
-        <v>1</v>
-      </c>
-      <c r="G105" t="n">
-        <v>1</v>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>fuss</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>kuskos-balungos</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Si Ana pirmi lang kuskos-balungos kung naay buhaton nga dili siya ganahan.; Ang iyang amahan kuskos-balungos sa mga butang nga wala'y hinungdan.; Si Pedro kuskos-balungos pirmi, bisan gamay nga problema.; Ang mga tawo nga kuskos-balungos kasagaran magpaluya sa ilang mga kauban.; Si Maria pirmi lang kuskos-balungos bisan unsa nga buhaton.</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
         <is>
           <t>alternative spelling of kuskos balungos, fuss; excessive activity, worry, talk, complaint, or details about something (that causes delay)
 Synonyms: kuntil-butil, rekobeko, kesyo-kesyo
 1998, Rogelio L. Ordoñez, Saan papunta ang mga putok ?:Inaasahan naming pagdating sa bahaging ito ay “napagsaluhan” na natin ang “ piging” - isang masaganang hapag ng mga putaheng pampanitikan na handog sa  atin ni Ka Roger. Nang wala nang marami pang pasakalye at kuskos-balungos.We expect at this part, we will "share" the "feast" - a lavish table of literary recipes out brother Roger provided us. [But], without lots of introductory ceremonies and fuss., 1998, Rogelio L. Ordoñez, Saan papunta ang mga putok ?:Inaasahan naming pagdating sa bahaging ito ay “napagsaluhan” na natin ang “ piging” - isang masaganang hapag ng mga putaheng pampanitikan na handog sa  atin ni Ka Roger. Nang wala nang marami pang pasakalye at kuskos-balungos.We expect at this part, we will "share" the "feast" - a lavish table of literary recipes out brother Roger provided us. [But], without lots of introductory ceremonies and fuss.</t>
         </is>
       </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>[(b'kuskos-balungos', 'OTH')]</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="n">
+        <v>1</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>kuskos</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>alternative spelling of kuskos balungos</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>kusog mokaon og gasolina</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Ang sakyanan ni Juan kusog mokaon og gasolina, maong mahal kaayo ang gasto.; Ang iyang motor kusog mokaon og gasolina, pirmi lang magpailis.; Si Pedro ganahan ug sakyanan nga dili kusog mokaon og gasolina.; Ang mga tawo nga mag-drive ug sakyanan nga kusog mokaon og gasolina kasagaran maglisod sa gasto.; Si Maria dili ganahan ug sakyanan nga kusog mokaon og gasolina kay mahal ang maintenance.</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>gas-guzzling</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>[(b'kusog', 'ADJ'), (b'mokaon', 'VERB'), (b'og', 'CONJ'), (b'gasolina', 'NOUN')]</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="n">
+        <v>1</v>
+      </c>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>gas-guzzling</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>kuwang sa tagad</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Si Ana kuwang sa tagad, maong pirmi lang magpahipi sa kanto.; Ang iyang kauban sa trabaho kuwang sa tagad, maong pirmi lang magpabida.; Si Pedro kuwang sa tagad, bisan unsa nga event ganahan magpakita.; Ang mga tawo nga kuwang sa tagad kasagaran magbuhat ug mga butang aron makuha ang atensyon.; Si Juan pirmi lang magpakita sa mga tao kay kuwang sa tagad.</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>characteristic of an attention seeker, (often preceded by ang) an attention seeker</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>[(b'kuwang', 'NOUN'), (b'sa', 'PART'), (b'tagad', 'VERB')]</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="n">
+        <v>1</v>
+      </c>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>characteristic of an attention seeker</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>kuyog baboy</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Si Maria pirmi lang kuyog baboy, bisan asa moadto iyang best friend naa gyud.; Ang iyang igsuon kuyog baboy pirmi kung maglakaw-lakaw.; Si Pedro dili ganahan ug kuyog baboy kay samok kaayo.; Ang mga tawo nga kuyog baboy kasagaran magpalisod sa ilang mga kauban.; Si Juan pirmi lang kuyog baboy bisan unsa nga lakaw.</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> a tagalong; one that persistently follows another,  a hanger-on; someone who trails behind, especially uninvited or unwanted, characteristic of a tagalong or hanger-on</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>[(b'kuyog', 'VERB'), (b'baboy', 'NOUN')]</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>a tagalong</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>lapas na sa kalendaryo</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Si Ana lapas na sa kalendaryo, pero dili gihapon magminyo.; Ang iyang igsuon lapas na sa kalendaryo, pero dili gihapon magka-anak.; Si Pedro lapas na sa kalendaryo, pero wala gihapon trabaho.; Ang mga tawo nga lapas na sa kalendaryo kasagaran magpanikad sa ilang mga plano.; Si Juan lapas na sa kalendaryo, pero wala gihapon magtarong sa kinabuhi.</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> a person over the age of 31</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>[(b'lapas', 'VERB'), (b'na', 'ADV'), (b'sa', 'PART'), (b'kalendaryo', 'NOUN')]</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="n">
+        <v>1</v>
+      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>a person over the age of 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>lapos sa pikas dunggan</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Ang tambag sa iyang ginikanan lapos ra sa pikas dunggan.; Si Pedro pirmi lang lapos sa pikas dunggan ang mga lectures sa eskwela.; Ang mga sugo sa iyang boss kay lapos ra sa pikas dunggan.; Ang mga tawo nga dili magtagad kasagaran maglapos ra sa pikas dunggan ang mga pulong sa uban.; Si Maria pirmi lang maglapos ra sa pikas dunggan ang mga tambag sa iyang mga amiga.</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> to go in one ear and out the other</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>[(b'lapos', 'VERB'), (b'sa', 'PART'), (b'pikas', 'ADJ'), (b'dunggan', 'VERB')]</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="n">
+        <v>1</v>
+      </c>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>to go in one ear and out the other</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>litik</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Si Juan naglitik sa iyang mga kalagot sa iyang kauban.; Ang iyang anak naglitik ug sugilanon nga makalipay.; Si Pedro naglitik sa iyang mga plano sa negosyo.; Ang mga tawo nga naglitik sa ilang mga pangandoy kasagaran magmalampuson.; Si Maria naglitik sa iyang mga pangandoy sa kinabuhi.</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>to flick with the finger, to whiplash; to lash as if with a whip,  to understand or comprehend, a flick using one's finger, (anatomy) pulse beat
+Synonyms: pulso, pintig, tibok</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>[(b'litik', 'VERB')]</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="n">
+        <v>1</v>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>to flick with the finger</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>lunod patay</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Si Pedro lunod patay sa iyang prinsipyo, dili gyud magbag-o.; Ang iyang amigo lunod patay sa iyang pagtuo bisan pa sa mga pagsulay.; Si Juan lunod patay sa pagsuporta sa iyang pamilya.; Ang mga tawo nga lunod patay kasagaran adunay baruganan nga dili matay-og.; Si Maria lunod patay sa pagpanalipod sa iyang mga kauban.</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> diehard, a diehard</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>[(b'lunod', 'VERB'), (b'patay', 'VERB')]</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="n">
+        <v>1</v>
+      </c>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>diehard</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>lupig pay ungo</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Si Ana lupig pay ungo nga kalit lang nagpakita sa party.; Ang iyang kauban lupig pay ungo nga kalit lang moabot kung naay problema.; Si Pedro lupig pay ungo nga kalit lang makita sa mga event.; Ang mga tawo nga lupig pay ungo kasagaran maghatag ug katingalahan sa uban.; Si Juan lupig pay ungo nga kalit lang nagpakita sa ilang balay.</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> someone who turns up unexpectedly</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>[(b'lupig', 'ADJ'), (b'pay', 'OTH'), (b'ungo', 'VERB')]</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="n">
+        <v>1</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>lupig</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>someone who turns up unexpectedly</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>maabot sa luwa</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Ang lugar nga ilang giadtoan kay maabot ra sa luwa, dili layo.; Ang iyang balay maabot ra sa luwa gikan sa simbahan.; Si Pedro pirmi lang maglakaw kay ang eskwelahan maabot ra sa luwa.; Ang mga tindahan nga ilang gusto adtoan kay maabot ra sa luwa gikan sa ilang lugar.; Si Maria nag-invite ug friends kay ilang balay maabot ra sa luwa.</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> near not far</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>[(b'maabot', 'VERB'), (b'sa', 'PART'), (b'luwa', 'VERB')]</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" t="n">
+        <v>1</v>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="n">
+        <v>1</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>maabot</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>near not far</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>mag-ihaw og lata</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Si Ana pirmi lang mag-ihaw og lata kung walay sud-an.; Ang iyang pamilya mag-ihaw og lata kung walay kwarta.; Si Pedro mag-ihaw og lata kung walay luto nga pagkaon.; Ang mga estudyante kasagaran mag-ihaw og lata kung nagtipid.; Si Juan pirmi lang mag-ihaw og lata sa boarding house.</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> to cook canned food</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>[(b'mag-ihaw', 'VERB'), (b'og', 'CONJ'), (b'lata', 'ADJ')]</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" t="n">
+        <v>1</v>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="n">
+        <v>1</v>
+      </c>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>to cook canned food</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>mag-ugbok og mohon</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Si Pedro nagplano nga mag-ugbok og mohon human sa kasal.; Ang magtiayon nagdecide nga mag-ugbok og mohon sa ilang honeymoon.; Si Maria ug ang iyang bana mag-ugbok og mohon sa ilang balay.; Ang mga magtiayon nga mag-ugbok og mohon kasagaran magmalipay sa ilang relasyon.; Si Ana nagplano nga mag-ugbok og mohon sa iyang birthday.</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> to have sexual intercourse</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>[(b'mag-ugbok', 'VERB'), (b'og', 'CONJ'), (b'mohon', 'NOUN')]</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" t="n">
+        <v>1</v>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="n">
+        <v>1</v>
+      </c>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>to have sexual intercourse</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>magbiko og pink</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Si Pedro magbiko og pink sa iyang birthday.; Ang iyang amiga magbiko og pink sa ilang reunion.; Si Maria magbiko og pink sa ilang party sa balay.; Ang mga tawo nga magbiko og pink kasagaran maglipay sa ilang celebration.; Si Juan magbiko og pink sa iyang graduation.</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> to celebrate</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>[(b'magbiko', 'VERB'), (b'og', 'CONJ'), (b'pink', 'OTH')]</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="n">
+        <v>1</v>
+      </c>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>to celebrate</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>maghilak ang adlaw</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Si Ana nagtan-aw sa bintana samtang naghilak ang adlaw.; Ang iyang pamilya nag-istorya samtang naghilak ang adlaw.; Si Pedro nagbasa ug libro samtang naghilak ang adlaw.; Ang mga tawo nag-relax sa balay samtang naghilak ang adlaw.; Si Juan naghunahuna sa iyang mga pangandoy samtang naghilak ang adlaw.</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> boring; monotonous; uneventful</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>[(b'maghilak', 'VERB'), (b'ang', 'DET'), (b'adlaw', 'NOUN')]</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="n">
+        <v>1</v>
+      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>boring</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>magpalapad og papel</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Si Pedro magpalapad og papel bisan dili siya ang nagbuhat sa proyekto.; Ang iyang kauban sa trabaho pirmi magpalapad og papel sa mga achievements sa uban.; Si Juan magpalapad og papel aron lang makakuha ug promotion.; Ang mga tawo nga magpalapad og papel kasagaran dili tinood nga maayong magtrabaho.; Si Maria magpalapad og papel bisan dili siya ang nagtrabaho sa project.</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> to take credit of other people's work</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>[(b'magpalapad', 'VERB'), (b'og', 'CONJ'), (b'papel', 'NOUN')]</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" t="n">
+        <v>1</v>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="n">
+        <v>1</v>
+      </c>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>to take credit of other people's work</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>magtumba og baka</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Si Pedro magtumba og baka para sa fiesta sa ilang baryo.; Ang ilang pamilya magtumba og baka kung naa’y dako nga celebration.; Si Juan nagplano nga magtumba og baka para sa birthday sa iyang anak.; Ang mga tawo nga magtumba og baka kasagaran nagselebrar ug dako nga event.; Si Maria nalipay kay magtumba og baka ang iyang pamilya para sa pasko.</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>to slaughter a cow</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>[(b'magtumba', 'VERB'), (b'og', 'CONJ'), (b'baka', 'NOUN')]</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="n">
+        <v>1</v>
+      </c>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>to slaughter a cow</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>maibtan sa tunok</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Si Ana maibtan sa tunok human siya makapasar sa board exam.; Ang iyang pamilya maibtan sa tunok human makabayad sa ilang utang.; Si Pedro maibtan sa tunok human ma-clear ang iyang pangalan sa kaso.; Ang mga tawo nga maibtan sa tunok kasagaran magmalipay ug magrelax.; Si Maria maibtan sa tunok human magkauli ang ilang pamilya.</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> to relieve of suffering or worry,  to exonerate</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>[(b'maibtan', 'OTH'), (b'sa', 'PART'), (b'tunok', 'NOUN')]</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="n">
+        <v>1</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>maibtan</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>to relieve of suffering or worry</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>makabugto og bra</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Si Pedro makabugto og bra tungod sa iyang pagka-sexy.; Ang artista nga iyang nakita sa TV makabugto og bra gyud.; Si Juan ganahan kaayo sa iyang uyab kay makabugto og bra.; Ang mga modelo sa magazine kasagaran makabugto og bra sa ilang porma.; Si Maria makaingon nga makabugto og bra ang iyang crush.</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>physically or sexually attractive, a hottie; a physically or sexually attractive person</t>
+        </is>
+      </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>[(b'kuskos-balungos', 'OTH')]</t>
+          <t>[(b'makabugto', 'VERB'), (b'og', 'CONJ'), (b'bra', 'NOUN')]</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G106" t="n">
         <v>1</v>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>alternative spelling of kuskos balungos</t>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="n">
+        <v>1</v>
+      </c>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>physically or sexually attractive</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kusog mokaon og gasolina</t>
+          <t>makabugto og panty</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ang sakyanan ni Juan kusog mokaon og gasolina, maong mahal kaayo ang gasto.; Ang iyang motor kusog mokaon og gasolina, pirmi lang magpailis.; Si Pedro ganahan ug sakyanan nga dili kusog mokaon og gasolina.; Ang mga tawo nga mag-drive ug sakyanan nga kusog mokaon og gasolina kasagaran maglisod sa gasto.; Si Maria dili ganahan ug sakyanan nga kusog mokaon og gasolina kay mahal ang maintenance.</t>
+          <t>Si Ana makabugto og panty sa iyang pagka-sexy.; Ang artista nga iyang nakita sa sine makabugto og panty gyud.; Si Pedro ganahan kaayo sa iyang uyab kay makabugto og panty.; Ang mga modelo sa fashion show kasagaran makabugto og panty sa ilang porma.; Si Maria makaingon nga makabugto og panty ang iyang crush.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>gas-guzzling</t>
+          <t>physically or sexually attractive, a hottie; a physically or sexually attractive person</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>[(b'kusog', 'ADJ'), (b'mokaon', 'VERB'), (b'og', 'CONJ'), (b'gasolina', 'NOUN')]</t>
+          <t>[(b'makabugto', 'VERB'), (b'og', 'CONJ'), (b'panty', 'OTH')]</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -4942,37 +4970,36 @@
       <c r="G107" t="n">
         <v>1</v>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>gas-guzzling</t>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="n">
+        <v>1</v>
+      </c>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>physically or sexually attractive</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kuwang sa tagad</t>
+          <t>makabuhi og patay</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Si Ana kuwang sa tagad, maong pirmi lang magpahipi sa kanto.; Ang iyang kauban sa trabaho kuwang sa tagad, maong pirmi lang magpabida.; Si Pedro kuwang sa tagad, bisan unsa nga event ganahan magpakita.; Ang mga tawo nga kuwang sa tagad kasagaran magbuhat ug mga butang aron makuha ang atensyon.; Si Juan pirmi lang magpakita sa mga tao kay kuwang sa tagad.</t>
+          <t>Si Juan makabuhi og patay sa iyang mga istorya.; Ang iyang amigo makabuhi og patay kung mag-suggest ug ideas.; Si Pedro makabuhi og patay sa iyang mga jokes.; Ang mga tawo nga makabuhi og patay kasagaran maayo kaayo moistorya.; Si Maria makabuhi og patay kung mag-explain sa iyang mga pangandoy.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>characteristic of an attention seeker, (often preceded by ang) an attention seeker</t>
+          <t xml:space="preserve"> a convincing lie or story</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>[(b'kuwang', 'NOUN'), (b'sa', 'PART'), (b'tagad', 'VERB')]</t>
+          <t>[(b'makabuhi', 'VERB'), (b'og', 'CONJ'), (b'patay', 'VERB')]</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -4984,41 +5011,40 @@
       <c r="G108" t="n">
         <v>1</v>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>characteristic of an attention seeker</t>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="n">
+        <v>1</v>
+      </c>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>a convincing lie or story</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kuyog baboy</t>
+          <t>makagisi og pitaka</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Si Maria pirmi lang kuyog baboy, bisan asa moadto iyang best friend naa gyud.; Ang iyang igsuon kuyog baboy pirmi kung maglakaw-lakaw.; Si Pedro dili ganahan ug kuyog baboy kay samok kaayo.; Ang mga tawo nga kuyog baboy kasagaran magpalisod sa ilang mga kauban.; Si Juan pirmi lang kuyog baboy bisan unsa nga lakaw.</t>
+          <t>Ang restaurant nga ilang giadtoan makagisi og pitaka kaayo.; Ang iyang bag-ong sapatos makagisi og pitaka tungod sa kamahal.; Si Pedro nagreklamo kay ang tuition fee sa eskwelahan makagisi og pitaka.; Ang mga luxury items kasagaran makagisi og pitaka sa ilang presyo.; Si Maria nakapalit ug bag nga makagisi og pitaka tungod sa kamahal.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> a tagalong; one that persistently follows another,  a hanger-on; someone who trails behind, especially uninvited or unwanted, characteristic of a tagalong or hanger-on</t>
+          <t xml:space="preserve"> extremely expensive</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>[(b'kuyog', 'VERB'), (b'baboy', 'NOUN')]</t>
+          <t>[(b'makagisi', 'OTH'), (b'og', 'CONJ'), (b'pitaka', 'NOUN')]</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F109" t="n">
         <v>1</v>
@@ -5026,37 +5052,40 @@
       <c r="G109" t="n">
         <v>1</v>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="n">
+        <v>1</v>
+      </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>a tagalong</t>
+          <t>makagisi</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>extremely expensive</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>lapas na sa kalendaryo</t>
+          <t>makakutaw og utok</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Si Ana lapas na sa kalendaryo, pero dili gihapon magminyo.; Ang iyang igsuon lapas na sa kalendaryo, pero dili gihapon magka-anak.; Si Pedro lapas na sa kalendaryo, pero wala gihapon trabaho.; Ang mga tawo nga lapas na sa kalendaryo kasagaran magpanikad sa ilang mga plano.; Si Juan lapas na sa kalendaryo, pero wala gihapon magtarong sa kinabuhi.</t>
+          <t>Ang math problems nga iyang gi-atubang makakutaw og utok gyud.; Ang explanation sa iyang professor makakutaw og utok kaayo.; Si Pedro naglibog kay ang project makakutaw og utok.; Ang mga puzzles nga iyang gi-solve makakutaw og utok kaayo.; Si Maria nagreklamo kay ang instructions makakutaw og utok.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> a person over the age of 31</t>
+          <t xml:space="preserve"> confusing, baffling</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>[(b'lapas', 'VERB'), (b'na', 'ADV'), (b'sa', 'PART'), (b'kalendaryo', 'NOUN')]</t>
+          <t>[(b'makakutaw', 'VERB'), (b'og', 'CONJ'), (b'utok', 'NOUN')]</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -5068,80 +5097,77 @@
       <c r="G110" t="n">
         <v>1</v>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>a person over the age of 31</t>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>confusing</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>lapos sa pikas dunggan</t>
+          <t>makamala og sapa</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Ang tambag sa iyang ginikanan lapos ra sa pikas dunggan.; Si Pedro pirmi lang lapos sa pikas dunggan ang mga lectures sa eskwela.; Ang mga sugo sa iyang boss kay lapos ra sa pikas dunggan.; Ang mga tawo nga dili magtagad kasagaran maglapos ra sa pikas dunggan ang mga pulong sa uban.; Si Maria pirmi lang maglapos ra sa pikas dunggan ang mga tambag sa iyang mga amiga.</t>
+          <t>Si Juan makamala og sapa sa iyang mga tiil.; Ang iyang amigo makamala og sapa tungod sa kadako sa tiil.; Si Pedro makamala og sapa kay grabe kaayo kadako ang tiil.; Ang mga tawo nga dagko ug tiil kasagaran makamala og sapa.; Si Maria nagkatawa kay ang iyang igsuon makamala og sapa sa kadako sa tiil.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> to go in one ear and out the other</t>
+          <t xml:space="preserve"> someone with large feet</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>[(b'lapos', 'VERB'), (b'sa', 'PART'), (b'pikas', 'ADJ'), (b'dunggan', 'VERB')]</t>
+          <t>[(b'makamala', 'VERB'), (b'og', 'CONJ'), (b'sapa', 'NOUN')]</t>
         </is>
       </c>
       <c r="E111" t="n">
         <v>1</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G111" t="n">
         <v>1</v>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>to go in one ear and out the other</t>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="n">
+        <v>1</v>
+      </c>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>someone with large feet</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>litik</t>
+          <t>makawat</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Si Juan naglitik sa iyang mga kalagot sa iyang kauban.; Ang iyang anak naglitik ug sugilanon nga makalipay.; Si Pedro naglitik sa iyang mga plano sa negosyo.; Ang mga tawo nga naglitik sa ilang mga pangandoy kasagaran magmalampuson.; Si Maria naglitik sa iyang mga pangandoy sa kinabuhi.</t>
+          <t>Ang bata ni Maria makawat kaayo, bisan kinsa lang pwede makagunit niya.; Si Pedro makawat kaayo, dali ra siya madala bisan kinsa.; Ang anak ni Juan makawat, bisan kinsa ra magpadede niya.; Si Ana makawat nga bata, dili siya mohilak bisan kinsa ang magbitbit.; Ang ilang baby makawat kaayo, bisan kinsa nga tawo dili niya kahadlukan.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>to flick with the finger, to whiplash; to lash as if with a whip,  to understand or comprehend, a flick using one's finger, (anatomy) pulse beat
-Synonyms: pulso, pintig, tibok</t>
+          <t>can be stolen, (idiomatic, of a baby) lets new people hold him or her; doesn't cry when held by others or taken away from parents, especially the mother</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>[(b'litik', 'VERB')]</t>
+          <t>[(b'makawat', 'VERB')]</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -5153,37 +5179,36 @@
       <c r="G112" t="n">
         <v>1</v>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>to flick with the finger</t>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="n">
+        <v>1</v>
+      </c>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>can be stolen</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>lunod patay</t>
+          <t>maliso pay buko sa kawayan</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Si Pedro lunod patay sa iyang prinsipyo, dili gyud magbag-o.; Ang iyang amigo lunod patay sa iyang pagtuo bisan pa sa mga pagsulay.; Si Juan lunod patay sa pagsuporta sa iyang pamilya.; Ang mga tawo nga lunod patay kasagaran adunay baruganan nga dili matay-og.; Si Maria lunod patay sa pagpanalipod sa iyang mga kauban.</t>
+          <t>Ang batasan ni Pedro maliso pay buko sa kawayan, dili gyud siya magbag-o.; Ang iyang pagtuo maliso pay buko sa kawayan, dili gyud mausab.; Si Juan maliso pay buko sa kawayan ang iyang determinasyon sa paghuman sa iyang kurso.; Ang iyang kauban sa trabaho maliso pay buko sa kawayan sa pagka-strikto.; Si Maria maliso pay buko sa kawayan ang iyang pagtuo sa Diyos.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> diehard, a diehard</t>
+          <t xml:space="preserve"> immutable; unable to be changed without exception; unchangeable</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>[(b'lunod', 'VERB'), (b'patay', 'VERB')]</t>
+          <t>[(b'maliso', 'VERB'), (b'pay', 'OTH'), (b'buko', 'VERB'), (b'sa', 'PART'), (b'kawayan', 'NOUN')]</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -5193,43 +5218,46 @@
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>1</v>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="n">
+        <v>1</v>
+      </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>diehard</t>
+          <t>maliso</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>immutable</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>maabot sa luwa</t>
+          <t>mamalit og kaso</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ang lugar nga ilang giadtoan kay maabot ra sa luwa, dili layo.; Ang iyang balay maabot ra sa luwa gikan sa simbahan.; Si Pedro pirmi lang maglakaw kay ang eskwelahan maabot ra sa luwa.; Ang mga tindahan nga ilang gusto adtoan kay maabot ra sa luwa gikan sa ilang lugar.; Si Maria nag-invite ug friends kay ilang balay maabot ra sa luwa.</t>
+          <t>Si Ana mamalit og kaso aron lang magka-datu.; Ang abogado mamalit og kaso bisan asa nga hospital.; Si Pedro mamalit og kaso aron makakwarta sa mga biktima sa aksidente.; Ang mga tawo nga mamalit og kaso kasagaran mga abogado nga gustong magpasikat.; Si Juan mamalit og kaso aron lang magka-daghan ang iyang kliyente.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> near not far</t>
+          <t>to be an ambulance chaser, to engage in ambulance chasing</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>[(b'maabot', 'VERB'), (b'sa', 'PART'), (b'luwa', 'VERB')]</t>
+          <t>[(b'mamalit', 'OTH'), (b'og', 'CONJ'), (b'kaso', 'NOUN')]</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F114" t="n">
         <v>0</v>
@@ -5237,37 +5265,40 @@
       <c r="G114" t="n">
         <v>1</v>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="n">
+        <v>1</v>
+      </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>near not far</t>
+          <t>mamalit</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>to be an ambulance chaser</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>mabaw og kibot</t>
+          <t>manakop og ligid</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Si Ana mabaw og kibot, dali ra kaayo masuko.; Ang iyang kauban mabaw og kibot, bisan gamay lang nga butang maglagot na.; Si Pedro mabaw og kibot, pirmi lang magyawyaw kung naay di siya ganahan.; Ang mga tawo nga mabaw og kibot kasagaran maglisod sa pagdawat ug kritisismo.; Si Juan mabaw og kibot, dali ra kaayo ma-offend.</t>
+          <t>Si Ana nasuko kay siya manakop og ligid tungod sa iyang pagkadula.; Ang iyang kauban sa trabaho pirmi lang manakop og ligid kay walay tarong nga pag-amping.; Si Pedro manakop og ligid kay nagdagan-dagan sa kalsada.; Ang mga tawo nga dili mag-amping sa dalan kasagaran manakop og ligid.; Si Juan nakasulay nga manakop og ligid human nag-away sa iyang amigo.; "Ayaw pag manakop og ligid, klaroha imong gibuhat."; "Manakop og ligid kaayo imong mga plano, walay klaro."; "Si Pedro, manakop og ligid ug walay klaro."; "Ayaw pag manakop og ligid, siguroha imong mga desisyon."; "Manakop og ligid imong mga ideas, kinahanglan pa nimo ug focus."</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve"> easily offended</t>
+          <t>(humorous) to have oneself ran over by a vehicle (see usage notes)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>[(b'mabaw', 'ADJ'), (b'og', 'CONJ'), (b'kibot', 'VERB')]</t>
+          <t>[(b'manakop', 'VERB'), (b'og', 'CONJ'), (b'ligid', 'VERB')]</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -5279,37 +5310,40 @@
       <c r="G115" t="n">
         <v>1</v>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="n">
+        <v>1</v>
+      </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>easily offended</t>
+          <t>manakop</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>to have oneself ran over by a vehicle</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>mag-ihaw og lata</t>
+          <t>mangayo og manghod</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Si Ana pirmi lang mag-ihaw og lata kung walay sud-an.; Ang iyang pamilya mag-ihaw og lata kung walay kwarta.; Si Pedro mag-ihaw og lata kung walay luto nga pagkaon.; Ang mga estudyante kasagaran mag-ihaw og lata kung nagtipid.; Si Juan pirmi lang mag-ihaw og lata sa boarding house.</t>
+          <t>Si Ana pirmi mangayo og manghod kung magdula.; Ang iyang anak mangayo og manghod kung gutom na.; Si Pedro nakakita sa iyang anak nga mangayo og manghod sa iyang tiil.; Ang mga bata nga mangayo og manghod kasagaran mga healthy nga bata.; Si Juan nalipay kay ang iyang baby nakakat-on nga mangayo og manghod.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve"> to cook canned food</t>
+          <t>an instance of a baby sucking on or chewing its toes</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>[(b'mag-ihaw', 'VERB'), (b'og', 'CONJ'), (b'lata', 'ADJ')]</t>
+          <t>[(b'mangayo', 'VERB'), (b'og', 'CONJ'), (b'manghod', 'NOUN')]</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -5321,37 +5355,36 @@
       <c r="G116" t="n">
         <v>1</v>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>to cook canned food</t>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="n">
+        <v>1</v>
+      </c>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>an instance of a baby sucking on or chewing its toes</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>mag-ugbok og mohon</t>
+          <t>manglutasay</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Si Pedro nagplano nga mag-ugbok og mohon human sa kasal.; Ang magtiayon nagdecide nga mag-ugbok og mohon sa ilang honeymoon.; Si Maria ug ang iyang bana mag-ugbok og mohon sa ilang balay.; Ang mga magtiayon nga mag-ugbok og mohon kasagaran magmalipay sa ilang relasyon.; Si Ana nagplano nga mag-ugbok og mohon sa iyang birthday.</t>
+          <t>Si Pedro pirmi manglutasay ug uyab nga mga batan-on.; Ang iyang kauban sa trabaho manglutasay sa mga kabataan.; Si Juan giingnan nga manglutasay kay ang iyang uyab mas bata kaayo.; Ang mga tawo nga manglutasay kasagaran magkatawa sa ilang kalaki.; Si Maria nalipay kay ang iyang kauban dili manglutasay.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve"> to have sexual intercourse</t>
+          <t>(often humorous, derogatory) a cradle robber</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>[(b'mag-ugbok', 'VERB'), (b'og', 'CONJ'), (b'mohon', 'NOUN')]</t>
+          <t>[(b'manglutasay', 'VERB')]</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -5363,37 +5396,36 @@
       <c r="G117" t="n">
         <v>1</v>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>to have sexual intercourse</t>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="n">
+        <v>1</v>
+      </c>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>a cradle robber</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>magbiko og pink</t>
+          <t>mangnukos</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Si Pedro magbiko og pink sa iyang birthday.; Ang iyang amiga magbiko og pink sa ilang reunion.; Si Maria magbiko og pink sa ilang party sa balay.; Ang mga tawo nga magbiko og pink kasagaran maglipay sa ilang celebration.; Si Juan magbiko og pink sa iyang graduation.</t>
+          <t>Si Ana nalipay kay ang iyang kauban dili mangnukos sa mga event.; Ang iyang kauban sa trabaho pirmi lang mangnukos sa mga party.; Si Pedro mangnukos sa mga events nga walay imbitasyon.; Ang mga tawo nga mangnukos kasagaran magpahimulos sa libre nga pagkaon.; Si Juan giingnan nga dili mangnukos sa party sa iyang amiga.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve"> to celebrate</t>
+          <t xml:space="preserve"> to gatecrash a feast, party, etc.</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>[(b'magbiko', 'VERB'), (b'og', 'CONJ'), (b'pink', 'OTH')]</t>
+          <t>[(b'mangnukos', 'VERB')]</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -5405,205 +5437,216 @@
       <c r="G118" t="n">
         <v>1</v>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>to celebrate</t>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="n">
+        <v>1</v>
+      </c>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>to gatecrash a feast</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>maghilak ang adlaw</t>
+          <t>manira sa dalan</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Si Ana nagtan-aw sa bintana samtang naghilak ang adlaw.; Ang iyang pamilya nag-istorya samtang naghilak ang adlaw.; Si Pedro nagbasa ug libro samtang naghilak ang adlaw.; Ang mga tawo nag-relax sa balay samtang naghilak ang adlaw.; Si Juan naghunahuna sa iyang mga pangandoy samtang naghilak ang adlaw.</t>
+          <t>Si Pedro pirmi manira sa dalan kada gabii.; Ang iyang barkada manira sa dalan hangtud sa kaadlawon.; Si Juan manira sa dalan kung walay klase.; Ang mga batan-on kasagaran manira sa dalan kung walay lingaw.; Si Maria ug ang iyang mga amiga manira sa dalan human sa trabaho.; "Ayaw pag manira sa dalan, naa pa kay buhaton."; "Si Ana, sige lang manira sa dalan walay klaro."; "Manira sa dalan imong mga plano, walay padulngan."; "Ayaw pag manira sa dalan, klaroha imong mga desisyon."; "Manira sa dalan kaayo ka, kinahanglan pa nimo ug focus."</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve"> boring; monotonous; uneventful</t>
+          <t>to stay up late, to drink or hang out by a street (see usage notes)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>[(b'maghilak', 'VERB'), (b'ang', 'DET'), (b'adlaw', 'NOUN')]</t>
+          <t>[(b'manira', 'OTH'), (b'sa', 'PART'), (b'dalan', 'NOUN')]</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G119" t="n">
         <v>1</v>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="n">
+        <v>1</v>
+      </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>boring</t>
+          <t>manira</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>to stay up late</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>magpalapad og papel</t>
+          <t>may tawo na ang payag</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Si Pedro magpalapad og papel bisan dili siya ang nagbuhat sa proyekto.; Ang iyang kauban sa trabaho pirmi magpalapad og papel sa mga achievements sa uban.; Si Juan magpalapad og papel aron lang makakuha ug promotion.; Ang mga tawo nga magpalapad og papel kasagaran dili tinood nga maayong magtrabaho.; Si Maria magpalapad og papel bisan dili siya ang nagtrabaho sa project.</t>
+          <t>Si Ana dili na pwede uyabon kay may tawo na ang payag.; Ang iyang crush may tawo na ang payag, mao nga dili na siya magpursige.; Si Pedro naay gipanguyaban nga may tawo na ang payag.; Ang mga batan-on kasagaran dili na mangita ug uyab kung may tawo na ang payag.; Si Maria niingon nga may tawo na ang payag mao nga dili siya ganahan sa uban.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve"> to take credit of other people's work</t>
+          <t xml:space="preserve"> for a girl to have a sweetheart, someone who is already committed to a relationship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>[(b'magpalapad', 'VERB'), (b'og', 'CONJ'), (b'papel', 'NOUN')]</t>
+          <t>[(b'may', 'VERB'), (b'tawo', 'NOUN'), (b'na', 'ADV'), (b'ang', 'DET'), (b'payag', 'NOUN')]</t>
         </is>
       </c>
       <c r="E120" t="n">
         <v>1</v>
       </c>
       <c r="F120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>1</v>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="n">
+        <v>1</v>
+      </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>to take credit of other people's work</t>
+          <t>may</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>for a girl to have a sweetheart</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>magtumba og baka</t>
+          <t>miulbo ang kaspa</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Si Pedro magtumba og baka para sa fiesta sa ilang baryo.; Ang ilang pamilya magtumba og baka kung naa’y dako nga celebration.; Si Juan nagplano nga magtumba og baka para sa birthday sa iyang anak.; Ang mga tawo nga magtumba og baka kasagaran nagselebrar ug dako nga event.; Si Maria nalipay kay magtumba og baka ang iyang pamilya para sa pasko.</t>
+          <t>Si Ana miulbo ang kaspa human nabal-an nga gilimbongan siya.; Ang iyang boss miulbo ang kaspa tungod sa sayop nga trabaho.; Si Pedro miulbo ang kaspa human naay nakig-away niya.; Ang mga tawo nga dali masuko kasagaran miulbo ang kaspa sa gamay nga rason.; Si Maria miulbo ang kaspa kay wala siya natagaan ug hustisya.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>to slaughter a cow</t>
+          <t>to fly into a rage, to fly off the handle</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>[(b'magtumba', 'VERB'), (b'og', 'CONJ'), (b'baka', 'NOUN')]</t>
+          <t>[(b'miulbo', 'OTH'), (b'ang', 'DET'), (b'kaspa', 'NOUN')]</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G121" t="n">
         <v>1</v>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="n">
+        <v>1</v>
+      </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>to slaughter a cow</t>
+          <t>miulbo</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>to fly into a rage</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>makabugto og bra</t>
+          <t>ang dili kaantos dili masantos</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Si Pedro makabugto og bra tungod sa iyang pagka-sexy.; Ang artista nga iyang nakita sa TV makabugto og bra gyud.; Si Juan ganahan kaayo sa iyang uyab kay makabugto og bra.; Ang mga modelo sa magazine kasagaran makabugto og bra sa ilang porma.; Si Maria makaingon nga makabugto og bra ang iyang crush.</t>
+          <t>Ang mga estudyante nga dili magtuon dili gayud makapasar.; Ang mga tawo nga dili magtrabaho dili makatagamtam sa bunga sa ilang pagpaningkamot.; Ang mga atleta nga dili mag-ensayo dili makadaug sa kompetisyon.; Ang mga negosyante nga dili mag-invest dili moasinso.; Ang mga magtutudlo nga dili magplano dili makalampus sa ilang mga estudyante.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>physically or sexually attractive, a hottie; a physically or sexually attractive person</t>
+          <t>no pain, no gain</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>[(b'makabugto', 'VERB'), (b'og', 'CONJ'), (b'bra', 'NOUN')]</t>
+          <t>[(b'ang', 'DET'), (b'dili', 'ADV'), (b'kaantos', 'NOUN'), (b'dili', 'ADV'), (b'masantos', 'ADJ')]</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F122" t="n">
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>1</v>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="n">
+        <v>1</v>
+      </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>physically or sexually attractive</t>
+          <t>makaantos, masantos</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>no pain</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>makabugto og panty</t>
+          <t>ang gaba dili magsaba</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Si Ana makabugto og panty sa iyang pagka-sexy.; Ang artista nga iyang nakita sa sine makabugto og panty gyud.; Si Pedro ganahan kaayo sa iyang uyab kay makabugto og panty.; Ang mga modelo sa fashion show kasagaran makabugto og panty sa ilang porma.; Si Maria makaingon nga makabugto og panty ang iyang crush.</t>
+          <t>Ang mga nagpakasala magulat lang kay ang gaba dili magsaba.; Si Pedro nabulabog kay nasuko ang iyang giilad, ang gaba dili magsaba.; Si Juan nakabalo nga ang iyang gibuhat nga dili maayo mibalik kaniya, ang gaba dili magsaba.; Ang mga tawo nga nagbuhat ug dautan maghulat sa ilang gaba kay ang gaba dili magsaba.; Si Ana nabulabog kay ang gaba dili magsaba sa iyang gibuhat nga sayop.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>physically or sexually attractive, a hottie; a physically or sexually attractive person</t>
+          <t>punishment for one's wrongdoings or transgressions will come unexpectedly</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>[(b'makabugto', 'VERB'), (b'og', 'CONJ'), (b'panty', 'OTH')]</t>
+          <t>[(b'ang', 'DET'), (b'gaba', 'NOUN'), (b'dili', 'ADV'), (b'magsaba', 'VERB')]</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -5615,121 +5658,122 @@
       <c r="G123" t="n">
         <v>1</v>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>physically or sexually attractive</t>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="n">
+        <v>1</v>
+      </c>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>punishment for one's wrongdoings or transgressions will come unexpectedly</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>makabuhi og patay</t>
+          <t>ayaw adto og gubat kon wala kay bala</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Si Juan makabuhi og patay sa iyang mga istorya.; Ang iyang amigo makabuhi og patay kung mag-suggest ug ideas.; Si Pedro makabuhi og patay sa iyang mga jokes.; Ang mga tawo nga makabuhi og patay kasagaran maayo kaayo moistorya.; Si Maria makabuhi og patay kung mag-explain sa iyang mga pangandoy.</t>
+          <t>Si Juan giingnan nga ayaw adto og gubat kon wala kay bala kay walay ayo.; Ang mga negosyante giingnan nga ayaw adto og gubat kon wala kay bala sa kompetisyon.; Si Pedro giandam ang tanan sa pag-adto sa exam, ayaw adto og gubat kon wala kay bala.; Ang mga estudyante kinahanglan magtuon kay ayaw adto og gubat kon wala kay bala.; Si Ana nagplano sa iyang project aron dili ma-unsa, ayaw adto og gubat kon wala kay bala.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve"> a convincing lie or story</t>
+          <t>do not do something unprepared</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>[(b'makabuhi', 'VERB'), (b'og', 'CONJ'), (b'patay', 'VERB')]</t>
+          <t>[(b'ayaw', 'VERB'), (b'adto', 'VERB'), (b'og', 'CONJ'), (b'gubat', 'NOUN'), (b'kon', 'CONJ'), (b'wala', 'ADV'), (b'kay', 'CONJ'), (b'bala', 'ADJ')]</t>
         </is>
       </c>
       <c r="E124" t="n">
         <v>1</v>
       </c>
       <c r="F124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G124" t="n">
         <v>1</v>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="n">
+        <v>1</v>
+      </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>a convincing lie or story</t>
+          <t>adto</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>do not do something unprepared</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>makagisi og pitaka</t>
+          <t>bisan ang kabaw nga naay upat ka tiil masipyat</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ang restaurant nga ilang giadtoan makagisi og pitaka kaayo.; Ang iyang bag-ong sapatos makagisi og pitaka tungod sa kamahal.; Si Pedro nagreklamo kay ang tuition fee sa eskwelahan makagisi og pitaka.; Ang mga luxury items kasagaran makagisi og pitaka sa ilang presyo.; Si Maria nakapalit ug bag nga makagisi og pitaka tungod sa kamahal.</t>
+          <t>Si Ana nakasala sa iyang trabaho, bisan ang kabaw nga naay upat ka tiil masipyat.; Ang iyang amigo nakalimot sa meeting, bisan ang kabaw nga naay upat ka tiil masipyat.; Si Pedro nasipyat sa exam, bisan ang kabaw nga naay upat ka tiil masipyat.; Ang mga tawo kasagaran maghimo og sayop, bisan ang kabaw nga naay upat ka tiil masipyat.; Si Maria nasipyat sa pagplano, bisan ang kabaw nga naay upat ka tiil masipyat.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve"> extremely expensive</t>
+          <t>we all make mistakes; nobody's perfect</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>[(b'makagisi', 'OTH'), (b'og', 'CONJ'), (b'pitaka', 'NOUN')]</t>
+          <t>[(b'bisan', 'ADV'), (b'ang', 'DET'), (b'kabaw', 'NOUN'), (b'nga', 'PART'), (b'naay', 'VERB'), (b'upat', 'NUM'), (b'ka', 'PRON'), (b'tiil', 'NOUN'), (b'masipyat', 'VERB')]</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G125" t="n">
         <v>1</v>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>extremely expensive</t>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="n">
+        <v>1</v>
+      </c>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>we all make mistakes</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>makakutaw og utok</t>
+          <t>buhat ang pasulti-on dili sulti ang pabuhaton</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ang math problems nga iyang gi-atubang makakutaw og utok gyud.; Ang explanation sa iyang professor makakutaw og utok kaayo.; Si Pedro naglibog kay ang project makakutaw og utok.; Ang mga puzzles nga iyang gi-solve makakutaw og utok kaayo.; Si Maria nagreklamo kay ang instructions makakutaw og utok.</t>
+          <t>Si Juan giingnan nga buhat ang pasulti-on dili sulti ang pabuhaton sa iyang trabaho.; Ang mga estudyante giingnan nga buhat ang pasulti-on dili sulti ang pabuhaton sa ilang proyekto.; Si Pedro nagpakita nga maayo siya sa trabaho, buhat ang pasulti-on dili sulti ang pabuhaton.; Ang mga tawo nga buhat ang pasulti-on dili sulti ang pabuhaton kasagaran magmalampuson.; Si Ana nagpakita sa iyang abilidad sa pagtrabaho, buhat ang pasulti-on dili sulti ang pabuhaton.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve"> confusing, baffling</t>
+          <t>walk the talk, let one's work speak for itself</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>[(b'makakutaw', 'VERB'), (b'og', 'CONJ'), (b'utok', 'NOUN')]</t>
+          <t>[(b'buhat', 'VERB'), (b'ang', 'DET'), (b'pasulti-on', 'VERB'), (b'dili', 'ADV'), (b'sulti', 'VERB'), (b'ang', 'DET'), (b'pabuhaton', 'VERB')]</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -5741,79 +5785,81 @@
       <c r="G126" t="n">
         <v>1</v>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="n">
+        <v>1</v>
+      </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>confusing</t>
+          <t>pasulti-on, pabuhaton</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>walk the talk</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>makamala og sapa</t>
+          <t>dili na mabalik ang baha paingon sa bukid</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Si Juan makamala og sapa sa iyang mga tiil.; Ang iyang amigo makamala og sapa tungod sa kadako sa tiil.; Si Pedro makamala og sapa kay grabe kaayo kadako ang tiil.; Ang mga tawo nga dagko ug tiil kasagaran makamala og sapa.; Si Maria nagkatawa kay ang iyang igsuon makamala og sapa sa kadako sa tiil.</t>
+          <t>Si Juan nasayod nga dili na mabalik ang baha paingon sa bukid, mao nga nagpadayon na siya.; Ang mga tawo giingnan nga dili na mabalik ang baha paingon sa bukid, mao nga nag-move on na.; Si Pedro giingnan nga dili na mabalik ang baha paingon sa bukid, mao nga naghinuktok na lang.; Ang mga estudyante nakabalo nga dili na mabalik ang baha paingon sa bukid, mao nga nagplano na sila pag-ayo.; Si Ana nakasabot nga dili na mabalik ang baha paingon sa bukid, mao nga nag-move on na sa iyang kinabuhi.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve"> someone with large feet</t>
+          <t>what's done cannot be undone</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>[(b'makamala', 'VERB'), (b'og', 'CONJ'), (b'sapa', 'NOUN')]</t>
+          <t>[(b'dili', 'ADV'), (b'na', 'ADV'), (b'mabalik', 'VERB'), (b'ang', 'DET'), (b'baha', 'NOUN'), (b'paingon', 'PART'), (b'sa', 'PART'), (b'bukid', 'NOUN')]</t>
         </is>
       </c>
       <c r="E127" t="n">
         <v>1</v>
       </c>
       <c r="F127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G127" t="n">
         <v>1</v>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>someone with large feet</t>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="n">
+        <v>1</v>
+      </c>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>what's done cannot be undone</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>makawat</t>
+          <t>dili na nimo mabalik ang baha sa bukid</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Ang bata ni Maria makawat kaayo, bisan kinsa lang pwede makagunit niya.; Si Pedro makawat kaayo, dali ra siya madala bisan kinsa.; Ang anak ni Juan makawat, bisan kinsa ra magpadede niya.; Si Ana makawat nga bata, dili siya mohilak bisan kinsa ang magbitbit.; Ang ilang baby makawat kaayo, bisan kinsa nga tawo dili niya kahadlukan.</t>
+          <t>Si Pedro giingnan nga dili na nimo mabalik ang baha sa bukid, mao nga naghinuktok na lang siya.; Ang mga estudyante nakabalo nga dili na nimo mabalik ang baha sa bukid, mao nga nagplano na sila pag-ayo.; Si Ana nakasabot nga dili na nimo mabalik ang baha sa bukid, mao nga nag-move on na siya.; Ang iyang pamilya giingnan nga dili na nimo mabalik ang baha sa bukid, mao nga nagplano na sila og tarong.; Si Maria giingnan nga dili na nimo mabalik ang baha sa bukid, mao nga nagpadayon na sa iyang mga plano.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>can be stolen, (idiomatic, of a baby) lets new people hold him or her; doesn't cry when held by others or taken away from parents, especially the mother</t>
+          <t>what's done is done</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>[(b'makawat', 'VERB')]</t>
+          <t>[(b'dili', 'ADV'), (b'na', 'ADV'), (b'nimo', 'PRON'), (b'mabalik', 'VERB'), (b'ang', 'DET'), (b'baha', 'NOUN'), (b'sa', 'PART'), (b'bukid', 'NOUN')]</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -5825,121 +5871,122 @@
       <c r="G128" t="n">
         <v>1</v>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>can be stolen</t>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="n">
+        <v>1</v>
+      </c>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>what's done is done</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>mamalit og kaso</t>
+          <t>dili tanang butang sili nga mohalang dayon</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Si Ana mamalit og kaso aron lang magka-datu.; Ang abogado mamalit og kaso bisan asa nga hospital.; Si Pedro mamalit og kaso aron makakwarta sa mga biktima sa aksidente.; Ang mga tawo nga mamalit og kaso kasagaran mga abogado nga gustong magpasikat.; Si Juan mamalit og kaso aron lang magka-daghan ang iyang kliyente.</t>
+          <t>Si Pedro naghinuktok nga dili tanang butang sili nga mohalang dayon, kinahanglan gyud og pagpaningkamot.; Ang mga estudyante giingnan nga dili tanang butang sili nga mohalang dayon, kinahanglan magtuon pag-ayo.; Si Ana nakasabot nga dili tanang butang sili nga mohalang dayon, mao nga nagplano og maayo.; Ang mga tawo nga dili tanang butang sili nga mohalang dayon kasagaran magmalampuson sa ilang mga plano.; Si Maria giingnan nga dili tanang butang sili nga mohalang dayon, kinahanglan gyud og pagpaningkamot.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>to be an ambulance chaser, to engage in ambulance chasing</t>
+          <t>not everything happens in an instant, it doesn't happen overnight; Rome wasn't built in a day</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>[(b'mamalit', 'OTH'), (b'og', 'CONJ'), (b'kaso', 'NOUN')]</t>
+          <t>[(b'dili', 'ADV'), (b'tanang', 'ADJ'), (b'butang', 'VERB'), (b'sili', 'NOUN'), (b'nga', 'PART'), (b'mohalang', 'VERB'), (b'dayon', 'CONJ')]</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G129" t="n">
         <v>1</v>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="n">
+        <v>1</v>
+      </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>to be an ambulance chaser</t>
+          <t>mohalang</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>not everything happens in an instant</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>manakop og ligid</t>
+          <t>maayo pa ang kwarta naay tawo, ang tawo wala</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Si Ana nasuko kay siya manakop og ligid tungod sa iyang pagkadula.; Ang iyang kauban sa trabaho pirmi lang manakop og ligid kay walay tarong nga pag-amping.; Si Pedro manakop og ligid kay nagdagan-dagan sa kalsada.; Ang mga tawo nga dili mag-amping sa dalan kasagaran manakop og ligid.; Si Juan nakasulay nga manakop og ligid human nag-away sa iyang amigo.; "Ayaw pag manakop og ligid, klaroha imong gibuhat."; "Manakop og ligid kaayo imong mga plano, walay klaro."; "Si Pedro, manakop og ligid ug walay klaro."; "Ayaw pag manakop og ligid, siguroha imong mga desisyon."; "Manakop og ligid imong mga ideas, kinahanglan pa nimo ug focus."</t>
+          <t>Si Juan nagpasalamat nga naa siyay kwarta kay lisod ang panahon, maayo pa ang kwarta naay tawo, ang tawo wala.; Si Pedro nagkalisod tungod kay walay kwarta, maayo pa ang kwarta naay tawo, ang tawo wala.; Ang pamilya naglisod tungod sa kawad-on, maayo pa ang kwarta naay tawo, ang tawo wala.; Si Ana nagstruggle kay walay kwarta, maayo pa ang kwarta naay tawo, ang tawo wala.; Ang mga negosyante nagkalisod tungod sa kawad-on, maayo pa ang kwarta naay tawo, ang tawo wala.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>(humorous) to have oneself ran over by a vehicle (see usage notes)</t>
+          <t>one may experience hard times; money will run out</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>[(b'manakop', 'VERB'), (b'og', 'CONJ'), (b'ligid', 'VERB')]</t>
+          <t>[(b'maayo', 'ADJ'), (b'pa', 'ADV'), (b'ang', 'DET'), (b'kwarta', 'NOUN'), (b'naay', 'VERB'), (b'tawo', 'NOUN'), (b',', 'SYM'), (b'ang', 'DET'), (b'tawo', 'NOUN'), (b'wala', 'ADV')]</t>
         </is>
       </c>
       <c r="E130" t="n">
         <v>1</v>
       </c>
       <c r="F130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G130" t="n">
-        <v>1</v>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>to have oneself ran over by a vehicle</t>
+        <v>0</v>
+      </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="n">
+        <v>1</v>
+      </c>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>one may experience hard times</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>mangayo og manghod</t>
+          <t>madala nimo ang baka sa suba apan dili nimo mainom</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Si Ana pirmi mangayo og manghod kung magdula.; Ang iyang anak mangayo og manghod kung gutom na.; Si Pedro nakakita sa iyang anak nga mangayo og manghod sa iyang tiil.; Ang mga bata nga mangayo og manghod kasagaran mga healthy nga bata.; Si Juan nalipay kay ang iyang baby nakakat-on nga mangayo og manghod.</t>
+          <t>Si Pedro giingnan nga bisan unsaon pagdasig, madala nimo ang baka sa suba apan dili nimo mainom.; Ang mga estudyante kinahanglan magtuon, madala nimo ang baka sa suba apan dili nimo mainom.; Si Ana giingnan nga kinahanglan siya magpursige, madala nimo ang baka sa suba apan dili nimo mainom.; Ang mga tawo nga dili magpaningkamot dili gyud magmalampuson, madala nimo ang baka sa suba apan dili nimo mainom.; Si Maria giingnan nga kinahanglan siya mag-uban sa pagpaningkamot, madala nimo ang baka sa suba apan dili nimo mainom.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>an instance of a baby sucking on or chewing its toes</t>
+          <t>you can lead a horse to water, but you can't make it drink</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>[(b'mangayo', 'VERB'), (b'og', 'CONJ'), (b'manghod', 'NOUN')]</t>
+          <t>[(b'madala', 'VERB'), (b'nimo', 'PRON'), (b'ang', 'DET'), (b'baka', 'NOUN'), (b'sa', 'PART'), (b'suba', 'NOUN'), (b'apan', 'CONJ'), (b'dili', 'ADV'), (b'nimo', 'PRON'), (b'mainom', 'VERB')]</t>
         </is>
       </c>
       <c r="E131" t="n">
@@ -5951,79 +5998,81 @@
       <c r="G131" t="n">
         <v>1</v>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>an instance of a baby sucking on or chewing its toes</t>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="n">
+        <v>1</v>
+      </c>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>you can lead a horse to water</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>manglutasay</t>
+          <t>sa usa ka bulig naa gayod usa ka buang</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Si Pedro pirmi manglutasay ug uyab nga mga batan-on.; Ang iyang kauban sa trabaho manglutasay sa mga kabataan.; Si Juan giingnan nga manglutasay kay ang iyang uyab mas bata kaayo.; Ang mga tawo nga manglutasay kasagaran magkatawa sa ilang kalaki.; Si Maria nalipay kay ang iyang kauban dili manglutasay.</t>
+          <t>Ang grupo nga magkatapok kasagaran naa gyud usa ka buang, sa usa ka bulig naa gayod usa ka buang.; Si Pedro nagpakatawa sa iyang grupo, sa usa ka bulig naa gayod usa ka buang.; Ang mga kauban sa trabaho kasagaran naa'y usa ka buang, sa usa ka bulig naa gayod usa ka buang.; Si Ana nagpakatawa sa iyang mga amiga, sa usa ka bulig naa gayod usa ka buang.; Ang pamilya kasagaran naa gyud usa ka buang nga magpatawa, sa usa ka bulig naa gayod usa ka buang.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>(often humorous, derogatory) a cradle robber</t>
+          <t>there's a rotten apple in every barrel</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>[(b'manglutasay', 'VERB')]</t>
+          <t>[(b'sa', 'PART'), (b'usa', 'NUM'), (b'ka', 'PRON'), (b'bulig', 'VERB'), (b'naa', 'ADV'), (b'gayod', 'ADV'), (b'usa', 'NUM'), (b'ka', 'PRON'), (b'buang', 'ADJ')]</t>
         </is>
       </c>
       <c r="E132" t="n">
         <v>1</v>
       </c>
       <c r="F132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>1</v>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="n">
+        <v>1</v>
+      </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>a cradle robber</t>
+          <t>naa</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>there's a rotten apple in every barrel</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>mangnukos</t>
+          <t>walay aso makumkom</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Si Ana nalipay kay ang iyang kauban dili mangnukos sa mga event.; Ang iyang kauban sa trabaho pirmi lang mangnukos sa mga party.; Si Pedro mangnukos sa mga events nga walay imbitasyon.; Ang mga tawo nga mangnukos kasagaran magpahimulos sa libre nga pagkaon.; Si Juan giingnan nga dili mangnukos sa party sa iyang amiga.</t>
+          <t>Si Pedro nasayod nga walay aso makumkom, mao nga nagmatngon siya sa iyang mga lihok.; Ang mga tawo giingnan nga walay aso makumkom, mao nga magmatngon sila sa ilang mga buhaton.; Si Ana nakasabot nga walay aso makumkom, mao nga nagbantay siya sa iyang mga desisyon.; Ang mga estudyante giingnan nga walay aso makumkom, mao nga magtuon sila pag-ayo.; Si Maria giingnan nga walay aso makumkom, mao nga nagmatngon siya sa iyang mga lihok.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> to gatecrash a feast, party, etc.</t>
+          <t>no secret remains secret; walls have ears, truth will out</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>[(b'mangnukos', 'VERB')]</t>
+          <t>[(b'walay', 'ADV'), (b'aso', 'NOUN'), (b'makumkom', 'VERB')]</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -6035,41 +6084,40 @@
       <c r="G133" t="n">
         <v>1</v>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>to gatecrash a feast</t>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="n">
+        <v>1</v>
+      </c>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>no secret remains secret</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>manira sa dalan</t>
+          <t>walay mahay nga gauna</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Si Pedro pirmi manira sa dalan kada gabii.; Ang iyang barkada manira sa dalan hangtud sa kaadlawon.; Si Juan manira sa dalan kung walay klase.; Ang mga batan-on kasagaran manira sa dalan kung walay lingaw.; Si Maria ug ang iyang mga amiga manira sa dalan human sa trabaho.; "Ayaw pag manira sa dalan, naa pa kay buhaton."; "Si Ana, sige lang manira sa dalan walay klaro."; "Manira sa dalan imong mga plano, walay padulngan."; "Ayaw pag manira sa dalan, klaroha imong mga desisyon."; "Manira sa dalan kaayo ka, kinahanglan pa nimo ug focus."</t>
+          <t>Si Pedro nakasabot nga walay mahay nga gauna, mao nga nagmatngon siya sa iyang mga desisyon.; Ang mga tawo giingnan nga walay mahay nga gauna, mao nga magmatngon sila sa ilang mga buhaton.; Si Ana nakasabot nga walay mahay nga gauna, mao nga nagbantay siya sa iyang mga desisyon.; Ang mga estudyante giingnan nga walay mahay nga gauna, mao nga magtuon sila pag-ayo.; Si Maria giingnan nga walay mahay nga gauna, mao nga nagmatngon siya sa iyang mga lihok.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>to stay up late, to drink or hang out by a street (see usage notes)</t>
+          <t>what's done cannot be undone</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>[(b'manira', 'OTH'), (b'sa', 'PART'), (b'dalan', 'NOUN')]</t>
+          <t>[(b'walay', 'ADV'), (b'mahay', 'VERB'), (b'nga', 'PART'), (b'gauna', 'ADV')]</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F134" t="n">
         <v>0</v>
@@ -6077,37 +6125,40 @@
       <c r="G134" t="n">
         <v>1</v>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="n">
+        <v>1</v>
+      </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>to stay up late</t>
+          <t>gauna</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>what's done cannot be undone</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>mingaw pa ang panagat</t>
+          <t>walay man kardaba mamunga og tundan</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Ang restaurant mingaw pa ang panagat sa buntag.; Ang tindahan mingaw pa ang panagat kung lunes sa buntag.; Si Pedro nag-abli sa iyang store nga mingaw pa ang panagat.; Ang mga negosyo kasagaran mingaw pa ang panagat sa mga sayong oras.; Si Ana nakabantay nga mingaw pa ang panagat ang ilang tindahan sa adlaw nga dili sweldo.</t>
+          <t>Si Pedro nasayod nga walay man kardaba mamunga og tundan, mao nga nagbantay siya sa iyang mga desisyon.; Ang mga tawo giingnan nga walay man kardaba mamunga og tundan, mao nga magmatngon sila sa ilang mga buhaton.; Si Ana nakasabot nga walay man kardaba mamunga og tundan, mao nga nagbantay siya sa iyang mga desisyon.; Ang mga estudyante giingnan nga walay man kardaba mamunga og tundan, mao nga magtuon sila pag-ayo.; Si Maria giingnan nga walay man kardaba mamunga og tundan, mao nga nagmatngon siya sa iyang mga lihok.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve"> time of the day when an establishment has fewer costumers and is not as busy,  period where business sales and profits are low</t>
+          <t>the apple does not fall far from the tree</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>[(b'mingaw', 'ADJ'), (b'pa', 'ADV'), (b'ang', 'DET'), (b'panagat', 'NOUN')]</t>
+          <t>[(b'walay', 'ADV'), (b'man', 'PART'), (b'kardaba', 'NOUN'), (b'mamunga', 'NOUN'), (b'og', 'CONJ'), (b'tundan', 'NOUN')]</t>
         </is>
       </c>
       <c r="E135" t="n">
@@ -6119,163 +6170,169 @@
       <c r="G135" t="n">
         <v>1</v>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="n">
+        <v>1</v>
+      </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>time of the day when an establishment has fewer costumers and is not as busy</t>
+          <t>mamunga</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>the apple does not fall far from the tree</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>mingaw pa sa Tirana</t>
+          <t>gidaman</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Ang ilang lugar mingaw pa sa Tirana kung adlaw sa piyesta.; Ang baryo ni Pedro mingaw pa sa Tirana kung gabii.; Si Ana nagtrabaho sa lugar nga mingaw pa sa Tirana.; Ang ilang balay mingaw pa sa Tirana human nilarga ang tanan nga miyembro sa pamilya.; Si Maria nagbakasyon sa lugar nga mingaw pa sa Tirana para magrelax.</t>
+          <t>"Gidaman na pud si Pedro, daghan kaayo siya og storya."; "Kung mangutana ka og ing-ana, murag gidaman ka."; "Gidaman na ba ka? Daghan kaayo kag opinion."; "Gidaman na si Juan, sige lang siya og panaway."; "Ayaw ko gidam-i, klaro kaayo imong mga istorya."</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> a very quiet and deserted place</t>
+          <t>to sleeptalk or sleepwalk, (sarcastic) (as a reply) could mean; 'You've got to be kidding!', 'Are you sure?', 'Really? or 'You're assuming things.'</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>[(b'mingaw', 'ADJ'), (b'pa', 'ADV'), (b'sa', 'PART'), (b'Tirana', 'NOUN')]</t>
+          <t>[(b'gidaman', 'VERB')]</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G136" t="n">
         <v>1</v>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>a very quiet and deserted place</t>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="n">
+        <v>1</v>
+      </c>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>to sleeptalk or sleepwalk</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>minyo og lawas</t>
+          <t>isdaa</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Si Ana minyo og lawas tungod sa iyang pagka-busy sa trabaho ug pamilya.; Ang iyang amiga giingnan nga minyo og lawas tungod sa kadako sa iyang tiyan.; Si Pedro nangita ug exercise routine kay minyo og lawas na siya.; Ang mga tawo nga minyo og lawas kasagaran mga inahan nga busy kaayo sa ilang mga anak.; Si Maria minyo og lawas human manganak ug duha ka anak.</t>
+          <t>"Isdaa, ngano magbuhat ka ana?"; "Isdaa, unsa may imong plano?"; "Isdaa, unsa man diay imong gusto mahibal-an?"; "Isdaa, nganong mangutana man ka ana?"; "Isdaa, walay klaro imong pangutana."</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>having a dad bod, having a mom bod</t>
+          <t>fish, a specific kind of fish, (sarcastic) a reason, cause (when asking a crowd as if they are shopping for fish)
+Unsang isdaa?What fish? (Why the crowd?) (What's the commotion?), a person or thing
+(in the phrase) Unsang isdaa...?What fish...?
+Unsang isdaa molupad?What type of fish flies?
+Unsang isdaa ang nanganak nimo?What fish gave birth to you?</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>[(b'minyo', 'ADJ'), (b'og', 'CONJ'), (b'lawas', 'NOUN')]</t>
+          <t>[(b'isdaa', 'VERB')]</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F137" t="n">
         <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>1</v>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>having a dad bod</t>
+        <v>0</v>
+      </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="n">
+        <v>1</v>
+      </c>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>fish</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>miulbo ang kaspa</t>
+          <t>lamoy</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Si Ana miulbo ang kaspa human nabal-an nga gilimbongan siya.; Ang iyang boss miulbo ang kaspa tungod sa sayop nga trabaho.; Si Pedro miulbo ang kaspa human naay nakig-away niya.; Ang mga tawo nga dali masuko kasagaran miulbo ang kaspa sa gamay nga rason.; Si Maria miulbo ang kaspa kay wala siya natagaan ug hustisya.</t>
+          <t>"Lamoya nalang na imong gibuhat, walay gamit."; "Si Ana, sige lang lamoy walay klaro."; "Lamoy nalang na imong giingon, walay unod."; "Lamoy kaayo ka, bisan asa nalang dapita."; "Lamoy imong mga plano, walay klaro."</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>to fly into a rage, to fly off the handle</t>
+          <t>to swallow
+Synonym: tulon, (sarcastic) to eat</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>[(b'miulbo', 'OTH'), (b'ang', 'DET'), (b'kaspa', 'NOUN')]</t>
+          <t>[(b'lamoy', 'VERB')]</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G138" t="n">
         <v>1</v>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>to fly into a rage</t>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="n">
+        <v>1</v>
+      </c>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>to swallow
+Synonym: tulon</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ang gaba dili magsaba</t>
+          <t>mura og halas nga nagluno</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Ang mga nagpakasala magulat lang kay ang gaba dili magsaba.; Si Pedro nabulabog kay nasuko ang iyang giilad, ang gaba dili magsaba.; Si Juan nakabalo nga ang iyang gibuhat nga dili maayo mibalik kaniya, ang gaba dili magsaba.; Ang mga tawo nga nagbuhat ug dautan maghulat sa ilang gaba kay ang gaba dili magsaba.; Si Ana nabulabog kay ang gaba dili magsaba sa iyang gibuhat nga sayop.</t>
+          <t>"Ang iyang mga sinina nagkatag mura og halas nga nagluno."; "Ang kwarto sa bata mura og halas nga nagluno, walay nasunod nga kalimpyo."; "Ang sala murag halas nga nagluno, kay gikalat niya tanan iyang mga butang."; "Ang balay ni Pedro mura og halas nga nagluno, nagkatag tanan."; "Ang silingan namo mura og halas nga nagluno, walay tarong pagbutang sa mga gamit."</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>punishment for one's wrongdoings or transgressions will come unexpectedly</t>
+          <t>(idiomatic, simile) someone who leaves their dirty clothes everywhere around the house</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>[(b'ang', 'DET'), (b'gaba', 'NOUN'), (b'dili', 'ADV'), (b'magsaba', 'VERB')]</t>
+          <t>[(b'mura', 'ADJ'), (b'og', 'CONJ'), (b'halas', 'NOUN'), (b'nga', 'PART'), (b'nagluno', 'VERB')]</t>
         </is>
       </c>
       <c r="E139" t="n">
@@ -6287,771 +6344,180 @@
       <c r="G139" t="n">
         <v>1</v>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>punishment for one's wrongdoings or transgressions will come unexpectedly</t>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="n">
+        <v>1</v>
+      </c>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>someone who leaves their dirty clothes everywhere around the house</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ang kalimot walay gahom</t>
+          <t>murag gitilapan og iring</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Si Pedro pirmi malimtan ang iyang mga appointments, ang kalimot walay gahom.; Si Ana naglisod sa iyang trabaho kay ang kalimot walay gahom.; Ang mga estudyante nga malimot maglisod sa exam, ang kalimot walay gahom.; Ang mga negosyante nga malimot sa due dates maglisod sa ilang negosyo, ang kalimot walay gahom.; Si Maria nagstruggle kay pirmi malimtan ang mga deadlines, ang kalimot walay gahom.</t>
+          <t>"Ang iyang sapatos murag gitilapan og iring, limpyo kaayo."; "Ang lamesa sa balay ni Ana murag gitilapan og iring, limpyo kaayo."; "Ang awto ni Pedro murag gitilapan og iring, walay bahid sa hugaw."; "Ang iyang kwarto murag gitilapan og iring, limpyo kaayo."; "Ang iyang mga gamit sa opisina murag gitilapan og iring, limpyo ug hapsay."</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>being forgetful gets you nowhere and does not benefit you</t>
+          <t>(simile) spotless; spick-and-span</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>[(b'ang', 'DET'), (b'kalimot', 'NOUN'), (b'walay', 'ADV'), (b'gahom', 'NOUN')]</t>
+          <t>[(b'murag', 'ADJ'), (b'gitilapan', 'VERB'), (b'og', 'CONJ'), (b'iring', 'NOUN')]</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G140" t="n">
         <v>1</v>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>being forgetful gets you nowhere and does not benefit you</t>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="n">
+        <v>1</v>
+      </c>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>spotless</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ayaw adto og gubat kon wala kay bala</t>
+          <t>murag langaw nga nakatugdon sa kabaw</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Si Juan giingnan nga ayaw adto og gubat kon wala kay bala kay walay ayo.; Ang mga negosyante giingnan nga ayaw adto og gubat kon wala kay bala sa kompetisyon.; Si Pedro giandam ang tanan sa pag-adto sa exam, ayaw adto og gubat kon wala kay bala.; Ang mga estudyante kinahanglan magtuon kay ayaw adto og gubat kon wala kay bala.; Si Ana nagplano sa iyang project aron dili ma-unsa, ayaw adto og gubat kon wala kay bala.</t>
+          <t>"Siya karon murag langaw nga nakatugdon sa kabaw, taas kaayo og pride."; "Ang bag-ong kwartahan murag langaw nga nakatugdon sa kabaw, wala pa kasuway sa kwarta."; "Si Ana, gikan sa pagka-pobre, murag langaw nga nakatugdon sa kabaw karon."; "Ang mga tawo nga bag-o rang nakuhaan ug jackpot murag langaw nga nakatugdon sa kabaw."; "Ang mga bag-o rang nigraduate ug ni trabaho, murag langaw nga nakatugdon sa kabaw."</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>do not do something unprepared</t>
+          <t>(simile, idiomatic) nouveau riche; new money; upstart</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>[(b'ayaw', 'VERB'), (b'adto', 'VERB'), (b'og', 'CONJ'), (b'gubat', 'NOUN'), (b'kon', 'CONJ'), (b'wala', 'ADV'), (b'kay', 'CONJ'), (b'bala', 'ADJ')]</t>
+          <t>[(b'murag', 'ADJ'), (b'langaw', 'NOUN'), (b'nga', 'PART'), (b'nakatugdon', 'VERB'), (b'sa', 'PART'), (b'kabaw', 'NOUN')]</t>
         </is>
       </c>
       <c r="E141" t="n">
         <v>1</v>
       </c>
       <c r="F141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G141" t="n">
         <v>1</v>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>do not do something unprepared</t>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="n">
+        <v>1</v>
+      </c>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>nouveau riche</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>bisan ang kabaw nga naay upat ka tiil masipyat</t>
+          <t>murag namatyag iring</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Si Ana nakasala sa iyang trabaho, bisan ang kabaw nga naay upat ka tiil masipyat.; Ang iyang amigo nakalimot sa meeting, bisan ang kabaw nga naay upat ka tiil masipyat.; Si Pedro nasipyat sa exam, bisan ang kabaw nga naay upat ka tiil masipyat.; Ang mga tawo kasagaran maghimo og sayop, bisan ang kabaw nga naay upat ka tiil masipyat.; Si Maria nasipyat sa pagplano, bisan ang kabaw nga naay upat ka tiil masipyat.</t>
+          <t>"Si Pedro murag namatyag iring, sige lang hilak."; "Ang bata murag namatyag iring, hilak kaayo pagnalaya."; "Si Ana murag namatyag iring, dili madala ang iyang hilak."; "Ang iyang asawa murag namatyag iring pagkahibalo nga naay problema."; "Ang mga bata murag namatyag iring pagkahuman sa dula."</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>we all make mistakes; nobody's perfect</t>
+          <t>used to describe someone who cries bawlingly or a bawling cry</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>[(b'bisan', 'ADV'), (b'ang', 'DET'), (b'kabaw', 'NOUN'), (b'nga', 'PART'), (b'naay', 'VERB'), (b'upat', 'NUM'), (b'ka', 'PRON'), (b'tiil', 'NOUN'), (b'masipyat', 'VERB')]</t>
+          <t>[(b'murag', 'ADJ'), (b'namatyag', 'VERB'), (b'iring', 'NOUN')]</t>
         </is>
       </c>
       <c r="E142" t="n">
         <v>1</v>
       </c>
       <c r="F142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G142" t="n">
         <v>1</v>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>we all make mistakes</t>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="n">
+        <v>1</v>
+      </c>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>used to describe someone who cries bawlingly or a bawling cry</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>buhat ang pasulti-on dili sulti ang pabuhaton</t>
+          <t>murag namiya og tai</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Si Juan giingnan nga buhat ang pasulti-on dili sulti ang pabuhaton sa iyang trabaho.; Ang mga estudyante giingnan nga buhat ang pasulti-on dili sulti ang pabuhaton sa ilang proyekto.; Si Pedro nagpakita nga maayo siya sa trabaho, buhat ang pasulti-on dili sulti ang pabuhaton.; Ang mga tawo nga buhat ang pasulti-on dili sulti ang pabuhaton kasagaran magmalampuson.; Si Ana nagpakita sa iyang abilidad sa pagtrabaho, buhat ang pasulti-on dili sulti ang pabuhaton.</t>
+          <t>"Siya kalit lang murag namiya og tai, wala na gani nagpahibalo."; "Ang bata murag namiya og tai, kalit lang nawala."; "Si Pedro murag namiya og tai, wala na gani nagpahibalo sa iyang mga kauban."; "Ang silingan murag namiya og tai, kalit lang wala."; "Si Ana murag namiya og tai, wala na gani nagpahibalo sa iyang mga plano."</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>walk the talk, let one's work speak for itself</t>
+          <t>(simile, idiomatic) someone who leaves unexpectedly without sa word</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>[(b'buhat', 'VERB'), (b'ang', 'DET'), (b'pasulti-on', 'VERB'), (b'dili', 'ADV'), (b'sulti', 'VERB'), (b'ang', 'DET'), (b'pabuhaton', 'VERB')]</t>
+          <t>[(b'murag', 'ADJ'), (b'namiya', 'OTH'), (b'og', 'CONJ'), (b'tai', 'NOUN')]</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G143" t="n">
         <v>1</v>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="n">
+        <v>1</v>
+      </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>walk the talk</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>dili na mabalik ang baha paingon sa bukid</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Si Juan nasayod nga dili na mabalik ang baha paingon sa bukid, mao nga nagpadayon na siya.; Ang mga tawo giingnan nga dili na mabalik ang baha paingon sa bukid, mao nga nag-move on na.; Si Pedro giingnan nga dili na mabalik ang baha paingon sa bukid, mao nga naghinuktok na lang.; Ang mga estudyante nakabalo nga dili na mabalik ang baha paingon sa bukid, mao nga nagplano na sila pag-ayo.; Si Ana nakasabot nga dili na mabalik ang baha paingon sa bukid, mao nga nag-move on na sa iyang kinabuhi.</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>what's done cannot be undone</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>[(b'dili', 'ADV'), (b'na', 'ADV'), (b'mabalik', 'VERB'), (b'ang', 'DET'), (b'baha', 'NOUN'), (b'paingon', 'PART'), (b'sa', 'PART'), (b'bukid', 'NOUN')]</t>
-        </is>
-      </c>
-      <c r="E144" t="n">
-        <v>1</v>
-      </c>
-      <c r="F144" t="n">
-        <v>0</v>
-      </c>
-      <c r="G144" t="n">
-        <v>1</v>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>what's done cannot be undone</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>dili na nimo mabalik ang baha sa bukid</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Si Pedro giingnan nga dili na nimo mabalik ang baha sa bukid, mao nga naghinuktok na lang siya.; Ang mga estudyante nakabalo nga dili na nimo mabalik ang baha sa bukid, mao nga nagplano na sila pag-ayo.; Si Ana nakasabot nga dili na nimo mabalik ang baha sa bukid, mao nga nag-move on na siya.; Ang iyang pamilya giingnan nga dili na nimo mabalik ang baha sa bukid, mao nga nagplano na sila og tarong.; Si Maria giingnan nga dili na nimo mabalik ang baha sa bukid, mao nga nagpadayon na sa iyang mga plano.</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>what's done is done</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>[(b'dili', 'ADV'), (b'na', 'ADV'), (b'nimo', 'PRON'), (b'mabalik', 'VERB'), (b'ang', 'DET'), (b'baha', 'NOUN'), (b'sa', 'PART'), (b'bukid', 'NOUN')]</t>
-        </is>
-      </c>
-      <c r="E145" t="n">
-        <v>1</v>
-      </c>
-      <c r="F145" t="n">
-        <v>1</v>
-      </c>
-      <c r="G145" t="n">
-        <v>1</v>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>what's done is done</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>dili tanang butang sili nga mohalang dayon</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Si Pedro naghinuktok nga dili tanang butang sili nga mohalang dayon, kinahanglan gyud og pagpaningkamot.; Ang mga estudyante giingnan nga dili tanang butang sili nga mohalang dayon, kinahanglan magtuon pag-ayo.; Si Ana nakasabot nga dili tanang butang sili nga mohalang dayon, mao nga nagplano og maayo.; Ang mga tawo nga dili tanang butang sili nga mohalang dayon kasagaran magmalampuson sa ilang mga plano.; Si Maria giingnan nga dili tanang butang sili nga mohalang dayon, kinahanglan gyud og pagpaningkamot.</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>not everything happens in an instant, it doesn't happen overnight; Rome wasn't built in a day</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>[(b'dili', 'ADV'), (b'tanang', 'ADJ'), (b'butang', 'VERB'), (b'sili', 'NOUN'), (b'nga', 'PART'), (b'mohalang', 'VERB'), (b'dayon', 'CONJ')]</t>
-        </is>
-      </c>
-      <c r="E146" t="n">
-        <v>1</v>
-      </c>
-      <c r="F146" t="n">
-        <v>1</v>
-      </c>
-      <c r="G146" t="n">
-        <v>1</v>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>not everything happens in an instant</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>madala nimo ang baka sa suba apan dili nimo mainom</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Si Pedro giingnan nga bisan unsaon pagdasig, madala nimo ang baka sa suba apan dili nimo mainom.; Ang mga estudyante kinahanglan magtuon, madala nimo ang baka sa suba apan dili nimo mainom.; Si Ana giingnan nga kinahanglan siya magpursige, madala nimo ang baka sa suba apan dili nimo mainom.; Ang mga tawo nga dili magpaningkamot dili gyud magmalampuson, madala nimo ang baka sa suba apan dili nimo mainom.; Si Maria giingnan nga kinahanglan siya mag-uban sa pagpaningkamot, madala nimo ang baka sa suba apan dili nimo mainom.</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>you can lead a horse to water, but you can't make it drink</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>[(b'madala', 'VERB'), (b'nimo', 'PRON'), (b'ang', 'DET'), (b'baka', 'NOUN'), (b'sa', 'PART'), (b'suba', 'NOUN'), (b'apan', 'CONJ'), (b'dili', 'ADV'), (b'nimo', 'PRON'), (b'mainom', 'VERB')]</t>
-        </is>
-      </c>
-      <c r="E147" t="n">
-        <v>1</v>
-      </c>
-      <c r="F147" t="n">
-        <v>1</v>
-      </c>
-      <c r="G147" t="n">
-        <v>1</v>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>you can lead a horse to water</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>walay aso makumkom</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Si Pedro nasayod nga walay aso makumkom, mao nga nagmatngon siya sa iyang mga lihok.; Ang mga tawo giingnan nga walay aso makumkom, mao nga magmatngon sila sa ilang mga buhaton.; Si Ana nakasabot nga walay aso makumkom, mao nga nagbantay siya sa iyang mga desisyon.; Ang mga estudyante giingnan nga walay aso makumkom, mao nga magtuon sila pag-ayo.; Si Maria giingnan nga walay aso makumkom, mao nga nagmatngon siya sa iyang mga lihok.</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>no secret remains secret; walls have ears, truth will out</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>[(b'walay', 'ADV'), (b'aso', 'NOUN'), (b'makumkom', 'VERB')]</t>
-        </is>
-      </c>
-      <c r="E148" t="n">
-        <v>1</v>
-      </c>
-      <c r="F148" t="n">
-        <v>1</v>
-      </c>
-      <c r="G148" t="n">
-        <v>1</v>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>no secret remains secret</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>walay mahay nga gauna</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Si Pedro nakasabot nga walay mahay nga gauna, mao nga nagmatngon siya sa iyang mga desisyon.; Ang mga tawo giingnan nga walay mahay nga gauna, mao nga magmatngon sila sa ilang mga buhaton.; Si Ana nakasabot nga walay mahay nga gauna, mao nga nagbantay siya sa iyang mga desisyon.; Ang mga estudyante giingnan nga walay mahay nga gauna, mao nga magtuon sila pag-ayo.; Si Maria giingnan nga walay mahay nga gauna, mao nga nagmatngon siya sa iyang mga lihok.</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>what's done cannot be undone</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>[(b'walay', 'ADV'), (b'mahay', 'VERB'), (b'nga', 'PART'), (b'gauna', 'ADV')]</t>
-        </is>
-      </c>
-      <c r="E149" t="n">
-        <v>1</v>
-      </c>
-      <c r="F149" t="n">
-        <v>0</v>
-      </c>
-      <c r="G149" t="n">
-        <v>1</v>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>what's done cannot be undone</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>walay man kardaba mamunga og tundan</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Si Pedro nasayod nga walay man kardaba mamunga og tundan, mao nga nagbantay siya sa iyang mga desisyon.; Ang mga tawo giingnan nga walay man kardaba mamunga og tundan, mao nga magmatngon sila sa ilang mga buhaton.; Si Ana nakasabot nga walay man kardaba mamunga og tundan, mao nga nagbantay siya sa iyang mga desisyon.; Ang mga estudyante giingnan nga walay man kardaba mamunga og tundan, mao nga magtuon sila pag-ayo.; Si Maria giingnan nga walay man kardaba mamunga og tundan, mao nga nagmatngon siya sa iyang mga lihok.</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>the apple does not fall far from the tree</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>[(b'walay', 'ADV'), (b'man', 'PART'), (b'kardaba', 'NOUN'), (b'mamunga', 'NOUN'), (b'og', 'CONJ'), (b'tundan', 'NOUN')]</t>
-        </is>
-      </c>
-      <c r="E150" t="n">
-        <v>0</v>
-      </c>
-      <c r="F150" t="n">
-        <v>0</v>
-      </c>
-      <c r="G150" t="n">
-        <v>1</v>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>the apple does not fall far from the tree</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>gidaman</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>"Gidaman na pud si Pedro, daghan kaayo siya og storya."; "Kung mangutana ka og ing-ana, murag gidaman ka."; "Gidaman na ba ka? Daghan kaayo kag opinion."; "Gidaman na si Juan, sige lang siya og panaway."; "Ayaw ko gidam-i, klaro kaayo imong mga istorya."</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>to sleeptalk or sleepwalk, (sarcastic) (as a reply) could mean; 'You've got to be kidding!', 'Are you sure?', 'Really? or 'You're assuming things.'</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>[(b'gidaman', 'VERB')]</t>
-        </is>
-      </c>
-      <c r="E151" t="n">
-        <v>1</v>
-      </c>
-      <c r="F151" t="n">
-        <v>1</v>
-      </c>
-      <c r="G151" t="n">
-        <v>1</v>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>to sleeptalk or sleepwalk</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>lamoy</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>"Lamoya nalang na imong gibuhat, walay gamit."; "Si Ana, sige lang lamoy walay klaro."; "Lamoy nalang na imong giingon, walay unod."; "Lamoy kaayo ka, bisan asa nalang dapita."; "Lamoy imong mga plano, walay klaro."</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>to swallow
-Synonym: tulon, (sarcastic) to eat</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>[(b'lamoy', 'VERB')]</t>
-        </is>
-      </c>
-      <c r="E152" t="n">
-        <v>1</v>
-      </c>
-      <c r="F152" t="n">
-        <v>1</v>
-      </c>
-      <c r="G152" t="n">
-        <v>1</v>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>to swallow
-Synonym: tulon</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>mura og halas nga nagluno</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>"Ang iyang mga sinina nagkatag mura og halas nga nagluno."; "Ang kwarto sa bata mura og halas nga nagluno, walay nasunod nga kalimpyo."; "Ang sala murag halas nga nagluno, kay gikalat niya tanan iyang mga butang."; "Ang balay ni Pedro mura og halas nga nagluno, nagkatag tanan."; "Ang silingan namo mura og halas nga nagluno, walay tarong pagbutang sa mga gamit."</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>(idiomatic, simile) someone who leaves their dirty clothes everywhere around the house</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>[(b'mura', 'ADJ'), (b'og', 'CONJ'), (b'halas', 'NOUN'), (b'nga', 'PART'), (b'nagluno', 'VERB')]</t>
-        </is>
-      </c>
-      <c r="E153" t="n">
-        <v>1</v>
-      </c>
-      <c r="F153" t="n">
-        <v>1</v>
-      </c>
-      <c r="G153" t="n">
-        <v>1</v>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>someone who leaves their dirty clothes everywhere around the house</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>murag gitilapan og iring</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>"Ang iyang sapatos murag gitilapan og iring, limpyo kaayo."; "Ang lamesa sa balay ni Ana murag gitilapan og iring, limpyo kaayo."; "Ang awto ni Pedro murag gitilapan og iring, walay bahid sa hugaw."; "Ang iyang kwarto murag gitilapan og iring, limpyo kaayo."; "Ang iyang mga gamit sa opisina murag gitilapan og iring, limpyo ug hapsay."</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>(simile) spotless; spick-and-span</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>[(b'murag', 'ADJ'), (b'gitilapan', 'VERB'), (b'og', 'CONJ'), (b'iring', 'NOUN')]</t>
-        </is>
-      </c>
-      <c r="E154" t="n">
-        <v>1</v>
-      </c>
-      <c r="F154" t="n">
-        <v>1</v>
-      </c>
-      <c r="G154" t="n">
-        <v>1</v>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>spotless</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>murag langaw nga nakatugdon sa kabaw</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>"Siya karon murag langaw nga nakatugdon sa kabaw, taas kaayo og pride."; "Ang bag-ong kwartahan murag langaw nga nakatugdon sa kabaw, wala pa kasuway sa kwarta."; "Si Ana, gikan sa pagka-pobre, murag langaw nga nakatugdon sa kabaw karon."; "Ang mga tawo nga bag-o rang nakuhaan ug jackpot murag langaw nga nakatugdon sa kabaw."; "Ang mga bag-o rang nigraduate ug ni trabaho, murag langaw nga nakatugdon sa kabaw."</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>(simile, idiomatic) nouveau riche; new money; upstart</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>[(b'murag', 'ADJ'), (b'langaw', 'NOUN'), (b'nga', 'PART'), (b'nakatugdon', 'VERB'), (b'sa', 'PART'), (b'kabaw', 'NOUN')]</t>
-        </is>
-      </c>
-      <c r="E155" t="n">
-        <v>1</v>
-      </c>
-      <c r="F155" t="n">
-        <v>1</v>
-      </c>
-      <c r="G155" t="n">
-        <v>1</v>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>nouveau riche</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>murag namatyag iring</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>"Si Pedro murag namatyag iring, sige lang hilak."; "Ang bata murag namatyag iring, hilak kaayo pagnalaya."; "Si Ana murag namatyag iring, dili madala ang iyang hilak."; "Ang iyang asawa murag namatyag iring pagkahibalo nga naay problema."; "Ang mga bata murag namatyag iring pagkahuman sa dula."</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>used to describe someone who cries bawlingly or a bawling cry</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>[(b'murag', 'ADJ'), (b'namatyag', 'VERB'), (b'iring', 'NOUN')]</t>
-        </is>
-      </c>
-      <c r="E156" t="n">
-        <v>1</v>
-      </c>
-      <c r="F156" t="n">
-        <v>1</v>
-      </c>
-      <c r="G156" t="n">
-        <v>1</v>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>used to describe someone who cries bawlingly or a bawling cry</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>murag namiya og tai</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>"Siya kalit lang murag namiya og tai, wala na gani nagpahibalo."; "Ang bata murag namiya og tai, kalit lang nawala."; "Si Pedro murag namiya og tai, wala na gani nagpahibalo sa iyang mga kauban."; "Ang silingan murag namiya og tai, kalit lang wala."; "Si Ana murag namiya og tai, wala na gani nagpahibalo sa iyang mga plano."</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>(simile, idiomatic) someone who leaves unexpectedly without sa word</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>[(b'murag', 'ADJ'), (b'namiya', 'OTH'), (b'og', 'CONJ'), (b'tai', 'NOUN')]</t>
-        </is>
-      </c>
-      <c r="E157" t="n">
-        <v>0</v>
-      </c>
-      <c r="F157" t="n">
-        <v>0</v>
-      </c>
-      <c r="G157" t="n">
-        <v>1</v>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr">
+          <t>namiya</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
         <is>
           <t>someone who leaves unexpectedly without sa word</t>
         </is>
